--- a/7936.T.xlsx
+++ b/7936.T.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BAA7C9-C1FA-4015-A306-ABCA626CEB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F869E951-9DD3-4030-AA9A-37E97678F34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{86C4971A-A7D1-48DA-A0F7-A80DD1620C15}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{86C4971A-A7D1-48DA-A0F7-A80DD1620C15}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t>Asics Group</t>
   </si>
@@ -254,6 +254,18 @@
   </si>
   <si>
     <t>FY25</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -736,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="3">
-        <v>4396</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -744,10 +756,10 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>714.69692599999996</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>54</v>
+        <v>708.70524699999999</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -759,7 +771,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>3141807.6866959999</v>
+        <v>3186338.7905119997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -770,10 +782,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>112267</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>54</v>
+        <v>119389</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -781,11 +793,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="3">
-        <f>2500+25000+10000</f>
-        <v>37500</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>54</v>
+        <f>10000+40000+25000</f>
+        <v>75000</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -797,7 +809,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>3067040.6866959999</v>
+        <v>3141949.7905119997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -830,7 +842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0781B03-897F-4FBF-8E19-27D8F6677ACE}">
-  <dimension ref="A1:BN318"/>
+  <dimension ref="A1:BR318"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -838,12 +850,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
@@ -880,29 +892,41 @@
       <c r="N2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="Z2" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>21</v>
@@ -911,7 +935,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>22</v>
@@ -920,11 +944,11 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>37</v>
@@ -941,7 +965,7 @@
         <v>79231</v>
       </c>
       <c r="F6" s="8">
-        <f>+T6-SUM(C6:E6)</f>
+        <f>+X6-SUM(C6:E6)</f>
         <v>58859</v>
       </c>
       <c r="G6" s="8">
@@ -956,7 +980,7 @@
         <v>87374</v>
       </c>
       <c r="J6" s="8">
-        <f>+U6-SUM(G6:I6)</f>
+        <f>+Y6-SUM(G6:I6)</f>
         <v>68659</v>
       </c>
       <c r="K6" s="8">
@@ -971,20 +995,23 @@
         <v>99341</v>
       </c>
       <c r="N6" s="8">
-        <f>+V6-SUM(K6:M6)</f>
+        <f>+Z6-SUM(K6:M6)</f>
         <v>79237</v>
       </c>
-      <c r="T6" s="8">
+      <c r="O6" s="8">
+        <v>116743</v>
+      </c>
+      <c r="X6" s="8">
         <v>285929</v>
       </c>
-      <c r="U6" s="8">
+      <c r="Y6" s="8">
         <v>326936</v>
       </c>
-      <c r="V6" s="8">
+      <c r="Z6" s="8">
         <v>363542</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>38</v>
@@ -1001,7 +1028,7 @@
         <v>20618</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:F24" si="0">+T7-SUM(C7:E7)</f>
+        <f t="shared" ref="F7:F24" si="0">+X7-SUM(C7:E7)</f>
         <v>11106</v>
       </c>
       <c r="G7" s="8">
@@ -1016,7 +1043,7 @@
         <v>22798</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" ref="J7:J24" si="1">+U7-SUM(G7:I7)</f>
+        <f t="shared" ref="J7:J24" si="1">+Y7-SUM(G7:I7)</f>
         <v>13736</v>
       </c>
       <c r="K7" s="8">
@@ -1031,20 +1058,23 @@
         <v>25488</v>
       </c>
       <c r="N7" s="8">
-        <f t="shared" ref="N7:N10" si="2">+V7-SUM(K7:M7)</f>
+        <f t="shared" ref="N7:N10" si="2">+Z7-SUM(K7:M7)</f>
         <v>16429</v>
       </c>
-      <c r="T7" s="8">
+      <c r="O7" s="8">
+        <v>30551</v>
+      </c>
+      <c r="X7" s="8">
         <v>72154</v>
       </c>
-      <c r="U7" s="8">
+      <c r="Y7" s="8">
         <v>78620</v>
       </c>
-      <c r="V7" s="8">
+      <c r="Z7" s="8">
         <v>86035</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -1094,17 +1124,20 @@
         <f t="shared" si="2"/>
         <v>9828</v>
       </c>
-      <c r="T8" s="8">
+      <c r="O8" s="8">
+        <v>14426</v>
+      </c>
+      <c r="X8" s="8">
         <v>36185</v>
       </c>
-      <c r="U8" s="8">
+      <c r="Y8" s="8">
         <v>38065</v>
       </c>
-      <c r="V8" s="8">
+      <c r="Z8" s="8">
         <v>42071</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>40</v>
@@ -1154,17 +1187,20 @@
         <f t="shared" si="2"/>
         <v>32280</v>
       </c>
-      <c r="T9" s="8">
+      <c r="O9" s="8">
+        <v>59621</v>
+      </c>
+      <c r="X9" s="8">
         <v>59257</v>
       </c>
-      <c r="U9" s="8">
+      <c r="Y9" s="8">
         <v>98425</v>
       </c>
-      <c r="V9" s="8">
+      <c r="Z9" s="8">
         <v>141324</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>41</v>
@@ -1214,17 +1250,20 @@
         <f t="shared" si="2"/>
         <v>36643</v>
       </c>
-      <c r="T10" s="8">
+      <c r="O10" s="8">
+        <v>37891</v>
+      </c>
+      <c r="X10" s="8">
         <v>60304</v>
       </c>
-      <c r="U10" s="8">
+      <c r="Y10" s="8">
         <v>95439</v>
       </c>
-      <c r="V10" s="8">
+      <c r="Z10" s="8">
         <v>136519</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
         <v>18</v>
@@ -1241,7 +1280,7 @@
         <v>158026</v>
       </c>
       <c r="F11" s="11">
-        <f>+T11-SUM(C11:E11)</f>
+        <f>+X11-SUM(C11:E11)</f>
         <v>122358</v>
       </c>
       <c r="G11" s="11">
@@ -1271,26 +1310,32 @@
         <v>222257</v>
       </c>
       <c r="N11" s="11">
-        <f>+V11-SUM(K11:M11)</f>
+        <f>+Z11-SUM(K11:M11)</f>
         <v>185861</v>
       </c>
-      <c r="R11" s="11">
+      <c r="O11" s="11">
+        <v>270265</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="V11" s="11">
         <v>404083</v>
       </c>
-      <c r="S11" s="11">
+      <c r="W11" s="11">
         <v>484601</v>
       </c>
-      <c r="T11" s="11">
+      <c r="X11" s="11">
         <v>570463</v>
       </c>
-      <c r="U11" s="11">
+      <c r="Y11" s="11">
         <v>678526</v>
       </c>
-      <c r="V11" s="11">
+      <c r="Z11" s="11">
         <v>810916</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>19</v>
@@ -1335,26 +1380,29 @@
         <v>97526</v>
       </c>
       <c r="N12" s="8">
-        <f>+V12-SUM(K12:M12)</f>
+        <f>+Z12-SUM(K12:M12)</f>
         <v>78401</v>
       </c>
-      <c r="R12" s="8">
+      <c r="O12" s="8">
+        <v>122746</v>
+      </c>
+      <c r="V12" s="8">
         <v>204205</v>
       </c>
-      <c r="S12" s="8">
+      <c r="W12" s="8">
         <v>243894</v>
       </c>
-      <c r="T12" s="8">
+      <c r="X12" s="8">
         <v>273566</v>
       </c>
-      <c r="U12" s="8">
+      <c r="Y12" s="8">
         <v>299648</v>
       </c>
-      <c r="V12" s="8">
+      <c r="Z12" s="8">
         <v>350283</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>20</v>
@@ -1388,7 +1436,7 @@
         <v>100830</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" ref="J13:N13" si="4">+J11-J12</f>
+        <f t="shared" ref="J13:O13" si="4">+J11-J12</f>
         <v>87957</v>
       </c>
       <c r="K13" s="8">
@@ -1407,28 +1455,32 @@
         <f t="shared" si="4"/>
         <v>107460</v>
       </c>
-      <c r="R13" s="8">
-        <f>+R11-R12</f>
-        <v>199878</v>
-      </c>
-      <c r="S13" s="8">
-        <f>+S11-S12</f>
-        <v>240707</v>
-      </c>
-      <c r="T13" s="8">
-        <f>+T11-T12</f>
-        <v>296897</v>
-      </c>
-      <c r="U13" s="8">
-        <f>+U11-U12</f>
-        <v>378878</v>
+      <c r="O13" s="8">
+        <f t="shared" si="4"/>
+        <v>147519</v>
       </c>
       <c r="V13" s="8">
         <f>+V11-V12</f>
+        <v>199878</v>
+      </c>
+      <c r="W13" s="8">
+        <f>+W11-W12</f>
+        <v>240707</v>
+      </c>
+      <c r="X13" s="8">
+        <f>+X11-X12</f>
+        <v>296897</v>
+      </c>
+      <c r="Y13" s="8">
+        <f>+Y11-Y12</f>
+        <v>378878</v>
+      </c>
+      <c r="Z13" s="8">
+        <f>+Z11-Z12</f>
         <v>460633</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>24</v>
@@ -1473,26 +1525,29 @@
         <v>78256</v>
       </c>
       <c r="N14" s="8">
-        <f>+V14-SUM(K14:M14)</f>
+        <f>+Z14-SUM(K14:M14)</f>
         <v>92546</v>
       </c>
-      <c r="R14" s="8">
+      <c r="O14" s="8">
+        <v>86755</v>
+      </c>
+      <c r="V14" s="8">
         <v>177932</v>
       </c>
-      <c r="S14" s="8">
+      <c r="W14" s="8">
         <v>206704</v>
       </c>
-      <c r="T14" s="8">
+      <c r="X14" s="8">
         <v>242680</v>
       </c>
-      <c r="U14" s="8">
+      <c r="Y14" s="8">
         <v>278766</v>
       </c>
-      <c r="V14" s="8">
+      <c r="Z14" s="8">
         <v>318112</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>25</v>
@@ -1526,7 +1581,7 @@
         <v>32527</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" ref="J15:N15" si="6">+J13-J14</f>
+        <f t="shared" ref="J15:O15" si="6">+J13-J14</f>
         <v>8588</v>
       </c>
       <c r="K15" s="8">
@@ -1545,28 +1600,32 @@
         <f t="shared" si="6"/>
         <v>14914</v>
       </c>
-      <c r="R15" s="8">
-        <f t="shared" ref="R15:S15" si="7">+R13-R14</f>
+      <c r="O15" s="8">
+        <f t="shared" si="6"/>
+        <v>60764</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" ref="V15:W15" si="7">+V13-V14</f>
         <v>21946</v>
       </c>
-      <c r="S15" s="8">
+      <c r="W15" s="8">
         <f t="shared" si="7"/>
         <v>34003</v>
       </c>
-      <c r="T15" s="8">
-        <f>+T13-T14</f>
+      <c r="X15" s="8">
+        <f>+X13-X14</f>
         <v>54217</v>
       </c>
-      <c r="U15" s="8">
-        <f>+U13-U14</f>
+      <c r="Y15" s="8">
+        <f>+Y13-Y14</f>
         <v>100112</v>
       </c>
-      <c r="V15" s="8">
-        <f>+V13-V14</f>
+      <c r="Z15" s="8">
+        <f>+Z13-Z14</f>
         <v>142521</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>26</v>
@@ -1611,20 +1670,23 @@
         <v>758</v>
       </c>
       <c r="N16" s="8">
-        <f>+V16-SUM(K16:M16)</f>
+        <f>+Z16-SUM(K16:M16)</f>
         <v>1271</v>
       </c>
-      <c r="T16" s="8">
+      <c r="O16" s="8">
+        <v>1023</v>
+      </c>
+      <c r="X16" s="8">
         <v>5301</v>
       </c>
-      <c r="U16" s="8">
+      <c r="Y16" s="8">
         <v>5745</v>
       </c>
-      <c r="V16" s="8">
+      <c r="Z16" s="8">
         <v>4580</v>
       </c>
     </row>
-    <row r="17" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -1669,20 +1731,23 @@
         <v>1359</v>
       </c>
       <c r="N17" s="8">
-        <f>+V17-SUM(K17:M17)</f>
+        <f>+Z17-SUM(K17:M17)</f>
         <v>1389</v>
       </c>
-      <c r="T17" s="8">
+      <c r="O17" s="8">
+        <v>3011</v>
+      </c>
+      <c r="X17" s="8">
         <v>8845</v>
       </c>
-      <c r="U17" s="8">
+      <c r="Y17" s="8">
         <v>13255</v>
       </c>
-      <c r="V17" s="8">
+      <c r="Z17" s="8">
         <v>7804</v>
       </c>
     </row>
-    <row r="18" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>30</v>
@@ -1716,7 +1781,7 @@
         <v>30457</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" ref="J18:N18" si="9">+J15-J17+J16</f>
+        <f t="shared" ref="J18:O18" si="9">+J15-J17+J16</f>
         <v>4322</v>
       </c>
       <c r="K18" s="8">
@@ -1735,20 +1800,24 @@
         <f t="shared" si="9"/>
         <v>14796</v>
       </c>
-      <c r="T18" s="8">
-        <f>+T15+T16-T17</f>
+      <c r="O18" s="8">
+        <f t="shared" si="9"/>
+        <v>58776</v>
+      </c>
+      <c r="X18" s="8">
+        <f>+X15+X16-X17</f>
         <v>50673</v>
       </c>
-      <c r="U18" s="8">
-        <f>+U15+U16-U17</f>
+      <c r="Y18" s="8">
+        <f>+Y15+Y16-Y17</f>
         <v>92602</v>
       </c>
-      <c r="V18" s="8">
-        <f>+V15+V16-V17</f>
+      <c r="Z18" s="8">
+        <f>+Z15+Z16-Z17</f>
         <v>139297</v>
       </c>
     </row>
-    <row r="19" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -1793,20 +1862,23 @@
         <v>1</v>
       </c>
       <c r="N19" s="8">
-        <f>+V19-SUM(K19:M19)</f>
+        <f>+Z19-SUM(K19:M19)</f>
         <v>7</v>
       </c>
-      <c r="T19" s="8">
+      <c r="O19" s="8">
+        <v>3108</v>
+      </c>
+      <c r="X19" s="8">
         <v>8418</v>
       </c>
-      <c r="U19" s="8">
+      <c r="Y19" s="8">
         <v>7174</v>
       </c>
-      <c r="V19" s="8">
+      <c r="Z19" s="8">
         <v>2313</v>
       </c>
     </row>
-    <row r="20" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>29</v>
@@ -1851,20 +1923,23 @@
         <v>68</v>
       </c>
       <c r="N20" s="8">
-        <f>+V20-SUM(K20:M20)</f>
+        <f>+Z20-SUM(K20:M20)</f>
         <v>2591</v>
       </c>
-      <c r="T20" s="8">
+      <c r="O20" s="8">
+        <v>14</v>
+      </c>
+      <c r="X20" s="8">
         <v>8516</v>
       </c>
-      <c r="U20" s="8">
+      <c r="Y20" s="8">
         <v>6531</v>
       </c>
-      <c r="V20" s="8">
+      <c r="Z20" s="8">
         <v>2859</v>
       </c>
     </row>
-    <row r="21" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>31</v>
@@ -1898,7 +1973,7 @@
         <v>34016</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" ref="J21:N21" si="11">+J18+J19-J20</f>
+        <f t="shared" ref="J21:O21" si="11">+J18+J19-J20</f>
         <v>1170</v>
       </c>
       <c r="K21" s="8">
@@ -1917,20 +1992,24 @@
         <f t="shared" si="11"/>
         <v>12212</v>
       </c>
-      <c r="T21" s="8">
-        <f>+T18+T19-T20</f>
+      <c r="O21" s="8">
+        <f t="shared" si="11"/>
+        <v>61870</v>
+      </c>
+      <c r="X21" s="8">
+        <f>+X18+X19-X20</f>
         <v>50575</v>
       </c>
-      <c r="U21" s="8">
-        <f>+U18+U19-U20</f>
+      <c r="Y21" s="8">
+        <f>+Y18+Y19-Y20</f>
         <v>93245</v>
       </c>
-      <c r="V21" s="8">
-        <f>+V18+V19-V20</f>
+      <c r="Z21" s="8">
+        <f>+Z18+Z19-Z20</f>
         <v>138751</v>
       </c>
     </row>
-    <row r="22" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>32</v>
@@ -1975,20 +2054,23 @@
         <v>13118</v>
       </c>
       <c r="N22" s="8">
-        <f>+V22-SUM(K22:M22)</f>
+        <f>+Z22-SUM(K22:M22)</f>
         <v>-246</v>
       </c>
-      <c r="T22" s="8">
+      <c r="O22" s="8">
+        <v>15198</v>
+      </c>
+      <c r="X22" s="8">
         <v>15119</v>
       </c>
-      <c r="U22" s="8">
+      <c r="Y22" s="8">
         <v>29299</v>
       </c>
-      <c r="V22" s="8">
+      <c r="Z22" s="8">
         <v>39920</v>
       </c>
     </row>
-    <row r="23" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>33</v>
@@ -2022,7 +2104,7 @@
         <v>22665</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" ref="J23:N23" si="13">+J21-J22</f>
+        <f t="shared" ref="J23:O23" si="13">+J21-J22</f>
         <v>-1017</v>
       </c>
       <c r="K23" s="8">
@@ -2041,20 +2123,24 @@
         <f t="shared" si="13"/>
         <v>12458</v>
       </c>
-      <c r="T23" s="8">
-        <f>+T21-T22</f>
+      <c r="O23" s="8">
+        <f t="shared" si="13"/>
+        <v>46672</v>
+      </c>
+      <c r="X23" s="8">
+        <f>+X21-X22</f>
         <v>35456</v>
       </c>
-      <c r="U23" s="8">
-        <f>+U21-U22</f>
+      <c r="Y23" s="8">
+        <f>+Y21-Y22</f>
         <v>63946</v>
       </c>
-      <c r="V23" s="8">
-        <f>+V21-V22</f>
+      <c r="Z23" s="8">
+        <f>+Z21-Z22</f>
         <v>98831</v>
       </c>
     </row>
-    <row r="24" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>34</v>
@@ -2099,20 +2185,23 @@
         <v>-20</v>
       </c>
       <c r="N24" s="8">
-        <f>+V24-SUM(K24:M24)</f>
+        <f>+Z24-SUM(K24:M24)</f>
         <v>52</v>
       </c>
-      <c r="T24" s="8">
+      <c r="O24" s="8">
+        <v>101</v>
+      </c>
+      <c r="X24" s="8">
         <v>180</v>
       </c>
-      <c r="U24" s="8">
+      <c r="Y24" s="8">
         <v>138</v>
       </c>
-      <c r="V24" s="8">
+      <c r="Z24" s="8">
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
         <v>35</v>
@@ -2146,7 +2235,7 @@
         <v>22722</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" ref="J25:N25" si="15">+J23-J24</f>
+        <f t="shared" ref="J25:O25" si="15">+J23-J24</f>
         <v>-1135</v>
       </c>
       <c r="K25" s="8">
@@ -2165,24 +2254,28 @@
         <f t="shared" si="15"/>
         <v>12406</v>
       </c>
-      <c r="T25" s="8">
-        <f>+T23-T24</f>
+      <c r="O25" s="8">
+        <f t="shared" si="15"/>
+        <v>46571</v>
+      </c>
+      <c r="X25" s="8">
+        <f>+X23-X24</f>
         <v>35276</v>
       </c>
-      <c r="U25" s="8">
-        <f>+U23-U24</f>
+      <c r="Y25" s="8">
+        <f>+Y23-Y24</f>
         <v>63808</v>
       </c>
-      <c r="V25" s="8">
-        <f>+V23-V24</f>
+      <c r="Z25" s="8">
+        <f>+Z23-Z24</f>
         <v>98723</v>
       </c>
     </row>
-    <row r="26" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:66" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>36</v>
@@ -2216,7 +2309,7 @@
         <v>31.354480047458221</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" ref="J27:N27" si="17">+J25/J28</f>
+        <f t="shared" ref="J27:O27" si="17">+J25/J28</f>
         <v>-1.5611804944298882</v>
       </c>
       <c r="K27" s="12">
@@ -2235,16 +2328,23 @@
         <f t="shared" si="17"/>
         <v>17.35840682767957</v>
       </c>
-      <c r="U27" s="8">
-        <f>+U25/U28</f>
+      <c r="O27" s="12">
+        <f t="shared" si="17"/>
+        <v>65.712791315061338</v>
+      </c>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="Y27" s="8">
+        <f>+Y25/Y28</f>
         <v>88.301123892658509</v>
       </c>
-      <c r="V27" s="8">
-        <f>+V25/V28</f>
+      <c r="Z27" s="8">
+        <f>+Z25/Z28</f>
         <v>138.13267751483235</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -2285,22 +2385,24 @@
       <c r="N28" s="3">
         <v>714.69692599999996</v>
       </c>
-      <c r="O28" s="3"/>
+      <c r="O28" s="3">
+        <v>708.70524699999999</v>
+      </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3">
-        <v>722.61820899999998</v>
-      </c>
-      <c r="V28" s="3">
-        <v>714.69692599999996</v>
-      </c>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
+      <c r="Y28" s="3">
+        <v>722.61820899999998</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>714.69692599999996</v>
+      </c>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -2325,15 +2427,15 @@
       <c r="AV28" s="3"/>
       <c r="AW28" s="3"/>
       <c r="AX28" s="3"/>
-      <c r="AY28" s="6"/>
-      <c r="AZ28" s="6"/>
-      <c r="BA28" s="6"/>
-      <c r="BB28" s="6"/>
+      <c r="AY28" s="3"/>
+      <c r="AZ28" s="3"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="3"/>
       <c r="BC28" s="6"/>
-      <c r="BD28" s="3"/>
-      <c r="BE28" s="3"/>
-      <c r="BF28" s="3"/>
-      <c r="BG28" s="3"/>
+      <c r="BD28" s="6"/>
+      <c r="BE28" s="6"/>
+      <c r="BF28" s="6"/>
+      <c r="BG28" s="6"/>
       <c r="BH28" s="3"/>
       <c r="BI28" s="3"/>
       <c r="BJ28" s="3"/>
@@ -2341,8 +2443,12 @@
       <c r="BL28" s="3"/>
       <c r="BM28" s="3"/>
       <c r="BN28" s="3"/>
-    </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BO28" s="3"/>
+      <c r="BP28" s="3"/>
+      <c r="BQ28" s="3"/>
+      <c r="BR28" s="3"/>
+    </row>
+    <row r="29" spans="1:70" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2391,15 +2497,15 @@
       <c r="AV29" s="3"/>
       <c r="AW29" s="3"/>
       <c r="AX29" s="3"/>
-      <c r="AY29" s="6"/>
-      <c r="AZ29" s="6"/>
-      <c r="BA29" s="6"/>
-      <c r="BB29" s="6"/>
+      <c r="AY29" s="3"/>
+      <c r="AZ29" s="3"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="3"/>
       <c r="BC29" s="6"/>
-      <c r="BD29" s="3"/>
-      <c r="BE29" s="3"/>
-      <c r="BF29" s="3"/>
-      <c r="BG29" s="3"/>
+      <c r="BD29" s="6"/>
+      <c r="BE29" s="6"/>
+      <c r="BF29" s="6"/>
+      <c r="BG29" s="6"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3"/>
       <c r="BJ29" s="3"/>
@@ -2407,8 +2513,12 @@
       <c r="BL29" s="3"/>
       <c r="BM29" s="3"/>
       <c r="BN29" s="3"/>
-    </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BO29" s="3"/>
+      <c r="BP29" s="3"/>
+      <c r="BQ29" s="3"/>
+      <c r="BR29" s="3"/>
+    </row>
+    <row r="30" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
@@ -2437,7 +2547,7 @@
         <v>0.11501353903565659</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:N35" si="22">+L6/H6-1</f>
+        <f t="shared" ref="L30:O35" si="22">+L6/H6-1</f>
         <v>4.7609295377609717E-2</v>
       </c>
       <c r="M30" s="9">
@@ -2448,10 +2558,13 @@
         <f t="shared" si="22"/>
         <v>0.15406574520456173</v>
       </c>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
+      <c r="O30" s="9">
+        <f t="shared" si="22"/>
+        <v>0.19121863616419899</v>
+      </c>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -2484,15 +2597,15 @@
       <c r="AV30" s="3"/>
       <c r="AW30" s="3"/>
       <c r="AX30" s="3"/>
-      <c r="AY30" s="6"/>
-      <c r="AZ30" s="6"/>
-      <c r="BA30" s="6"/>
-      <c r="BB30" s="6"/>
+      <c r="AY30" s="3"/>
+      <c r="AZ30" s="3"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="3"/>
       <c r="BC30" s="6"/>
-      <c r="BD30" s="3"/>
-      <c r="BE30" s="3"/>
-      <c r="BF30" s="3"/>
-      <c r="BG30" s="3"/>
+      <c r="BD30" s="6"/>
+      <c r="BE30" s="6"/>
+      <c r="BF30" s="6"/>
+      <c r="BG30" s="6"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3"/>
       <c r="BJ30" s="3"/>
@@ -2500,8 +2613,12 @@
       <c r="BL30" s="3"/>
       <c r="BM30" s="3"/>
       <c r="BN30" s="3"/>
-    </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BO30" s="3"/>
+      <c r="BP30" s="3"/>
+      <c r="BQ30" s="3"/>
+      <c r="BR30" s="3"/>
+    </row>
+    <row r="31" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
@@ -2541,10 +2658,13 @@
         <f t="shared" si="22"/>
         <v>0.19605416423995337</v>
       </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
+      <c r="O31" s="9">
+        <f t="shared" si="22"/>
+        <v>0.19821939836059155</v>
+      </c>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
@@ -2577,15 +2697,15 @@
       <c r="AV31" s="3"/>
       <c r="AW31" s="3"/>
       <c r="AX31" s="3"/>
-      <c r="AY31" s="6"/>
-      <c r="AZ31" s="6"/>
-      <c r="BA31" s="6"/>
-      <c r="BB31" s="6"/>
+      <c r="AY31" s="3"/>
+      <c r="AZ31" s="3"/>
+      <c r="BA31" s="3"/>
+      <c r="BB31" s="3"/>
       <c r="BC31" s="6"/>
-      <c r="BD31" s="3"/>
-      <c r="BE31" s="3"/>
-      <c r="BF31" s="3"/>
-      <c r="BG31" s="3"/>
+      <c r="BD31" s="6"/>
+      <c r="BE31" s="6"/>
+      <c r="BF31" s="6"/>
+      <c r="BG31" s="6"/>
       <c r="BH31" s="3"/>
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
@@ -2593,8 +2713,12 @@
       <c r="BL31" s="3"/>
       <c r="BM31" s="3"/>
       <c r="BN31" s="3"/>
-    </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BO31" s="3"/>
+      <c r="BP31" s="3"/>
+      <c r="BQ31" s="3"/>
+      <c r="BR31" s="3"/>
+    </row>
+    <row r="32" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
@@ -2634,10 +2758,13 @@
         <f t="shared" si="22"/>
         <v>9.9944040290990577E-2</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
+      <c r="O32" s="9">
+        <f t="shared" si="22"/>
+        <v>0.39529935196827548</v>
+      </c>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
@@ -2670,15 +2797,15 @@
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
       <c r="AX32" s="3"/>
-      <c r="AY32" s="6"/>
-      <c r="AZ32" s="6"/>
-      <c r="BA32" s="6"/>
-      <c r="BB32" s="6"/>
+      <c r="AY32" s="3"/>
+      <c r="AZ32" s="3"/>
+      <c r="BA32" s="3"/>
+      <c r="BB32" s="3"/>
       <c r="BC32" s="6"/>
-      <c r="BD32" s="3"/>
-      <c r="BE32" s="3"/>
-      <c r="BF32" s="3"/>
-      <c r="BG32" s="3"/>
+      <c r="BD32" s="6"/>
+      <c r="BE32" s="6"/>
+      <c r="BF32" s="6"/>
+      <c r="BG32" s="6"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
@@ -2686,8 +2813,12 @@
       <c r="BL32" s="3"/>
       <c r="BM32" s="3"/>
       <c r="BN32" s="3"/>
-    </row>
-    <row r="33" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO32" s="3"/>
+      <c r="BP32" s="3"/>
+      <c r="BQ32" s="3"/>
+      <c r="BR32" s="3"/>
+    </row>
+    <row r="33" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>40</v>
       </c>
@@ -2727,10 +2858,13 @@
         <f t="shared" si="22"/>
         <v>0.38303341902313615</v>
       </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
+      <c r="O33" s="9">
+        <f t="shared" si="22"/>
+        <v>0.69647735033007052</v>
+      </c>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -2763,15 +2897,15 @@
       <c r="AV33" s="3"/>
       <c r="AW33" s="3"/>
       <c r="AX33" s="3"/>
-      <c r="AY33" s="6"/>
-      <c r="AZ33" s="6"/>
-      <c r="BA33" s="6"/>
-      <c r="BB33" s="6"/>
+      <c r="AY33" s="3"/>
+      <c r="AZ33" s="3"/>
+      <c r="BA33" s="3"/>
+      <c r="BB33" s="3"/>
       <c r="BC33" s="6"/>
-      <c r="BD33" s="3"/>
-      <c r="BE33" s="3"/>
-      <c r="BF33" s="3"/>
-      <c r="BG33" s="3"/>
+      <c r="BD33" s="6"/>
+      <c r="BE33" s="6"/>
+      <c r="BF33" s="6"/>
+      <c r="BG33" s="6"/>
       <c r="BH33" s="3"/>
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
@@ -2779,8 +2913,12 @@
       <c r="BL33" s="3"/>
       <c r="BM33" s="3"/>
       <c r="BN33" s="3"/>
-    </row>
-    <row r="34" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO33" s="3"/>
+      <c r="BP33" s="3"/>
+      <c r="BQ33" s="3"/>
+      <c r="BR33" s="3"/>
+    </row>
+    <row r="34" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>41</v>
       </c>
@@ -2820,10 +2958,13 @@
         <f t="shared" si="22"/>
         <v>0.36199078203984536</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
+      <c r="O34" s="9">
+        <f t="shared" si="22"/>
+        <v>0.33772285966460713</v>
+      </c>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -2856,15 +2997,15 @@
       <c r="AV34" s="3"/>
       <c r="AW34" s="3"/>
       <c r="AX34" s="3"/>
-      <c r="AY34" s="6"/>
-      <c r="AZ34" s="6"/>
-      <c r="BA34" s="6"/>
-      <c r="BB34" s="6"/>
+      <c r="AY34" s="3"/>
+      <c r="AZ34" s="3"/>
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="3"/>
       <c r="BC34" s="6"/>
-      <c r="BD34" s="3"/>
-      <c r="BE34" s="3"/>
-      <c r="BF34" s="3"/>
-      <c r="BG34" s="3"/>
+      <c r="BD34" s="6"/>
+      <c r="BE34" s="6"/>
+      <c r="BF34" s="6"/>
+      <c r="BG34" s="6"/>
       <c r="BH34" s="3"/>
       <c r="BI34" s="3"/>
       <c r="BJ34" s="3"/>
@@ -2872,8 +3013,12 @@
       <c r="BL34" s="3"/>
       <c r="BM34" s="3"/>
       <c r="BN34" s="3"/>
-    </row>
-    <row r="35" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO34" s="3"/>
+      <c r="BP34" s="3"/>
+      <c r="BQ34" s="3"/>
+      <c r="BR34" s="3"/>
+    </row>
+    <row r="35" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
@@ -2913,33 +3058,36 @@
         <f t="shared" si="22"/>
         <v>0.21420638653705448</v>
       </c>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="10" t="e">
-        <f t="shared" ref="R35:T35" si="23">+R11/Q11-1</f>
+      <c r="O35" s="10">
+        <f t="shared" si="22"/>
+        <v>0.29739862610590784</v>
+      </c>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="10" t="e">
+        <f t="shared" ref="V35:X35" si="23">+V11/U11-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S35" s="10">
+      <c r="W35" s="10">
         <f t="shared" si="23"/>
         <v>0.19926104290455182</v>
       </c>
-      <c r="T35" s="10">
+      <c r="X35" s="10">
         <f t="shared" si="23"/>
         <v>0.17718081473211988</v>
       </c>
-      <c r="U35" s="10">
-        <f>+U11/T11-1</f>
+      <c r="Y35" s="10">
+        <f>+Y11/X11-1</f>
         <v>0.18943033991687463</v>
       </c>
-      <c r="V35" s="10">
-        <f t="shared" ref="V35" si="24">+V11/U11-1</f>
+      <c r="Z35" s="10">
+        <f t="shared" ref="Z35" si="24">+Z11/Y11-1</f>
         <v>0.19511411500812059</v>
       </c>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -2964,15 +3112,15 @@
       <c r="AV35" s="3"/>
       <c r="AW35" s="3"/>
       <c r="AX35" s="3"/>
-      <c r="AY35" s="6"/>
-      <c r="AZ35" s="6"/>
-      <c r="BA35" s="6"/>
-      <c r="BB35" s="6"/>
+      <c r="AY35" s="3"/>
+      <c r="AZ35" s="3"/>
+      <c r="BA35" s="3"/>
+      <c r="BB35" s="3"/>
       <c r="BC35" s="6"/>
-      <c r="BD35" s="3"/>
-      <c r="BE35" s="3"/>
-      <c r="BF35" s="3"/>
-      <c r="BG35" s="3"/>
+      <c r="BD35" s="6"/>
+      <c r="BE35" s="6"/>
+      <c r="BF35" s="6"/>
+      <c r="BG35" s="6"/>
       <c r="BH35" s="3"/>
       <c r="BI35" s="3"/>
       <c r="BJ35" s="3"/>
@@ -2980,8 +3128,12 @@
       <c r="BL35" s="3"/>
       <c r="BM35" s="3"/>
       <c r="BN35" s="3"/>
-    </row>
-    <row r="36" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO35" s="3"/>
+      <c r="BP35" s="3"/>
+      <c r="BQ35" s="3"/>
+      <c r="BR35" s="3"/>
+    </row>
+    <row r="36" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>58</v>
       </c>
@@ -3033,39 +3185,42 @@
         <f t="shared" si="27"/>
         <v>0.57817401176147765</v>
       </c>
-      <c r="O36" s="3"/>
-      <c r="P36" s="9" t="e">
-        <f t="shared" ref="P36:T36" si="28">+P13/P11</f>
+      <c r="O36" s="9">
+        <f t="shared" ref="O36" si="28">+O13/O11</f>
+        <v>0.54583094370340224</v>
+      </c>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="9" t="e">
+        <f t="shared" ref="T36:X36" si="29">+T13/T11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="9" t="e">
-        <f t="shared" si="28"/>
+      <c r="U36" s="9" t="e">
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R36" s="9">
-        <f t="shared" si="28"/>
+      <c r="V36" s="9">
+        <f t="shared" si="29"/>
         <v>0.49464590195578634</v>
       </c>
-      <c r="S36" s="9">
-        <f t="shared" si="28"/>
+      <c r="W36" s="9">
+        <f t="shared" si="29"/>
         <v>0.49671172779255512</v>
       </c>
-      <c r="T36" s="9">
-        <f t="shared" si="28"/>
+      <c r="X36" s="9">
+        <f t="shared" si="29"/>
         <v>0.52044917900021559</v>
       </c>
-      <c r="U36" s="9">
-        <f>+U13/U11</f>
+      <c r="Y36" s="9">
+        <f>+Y13/Y11</f>
         <v>0.55838390864904219</v>
       </c>
-      <c r="V36" s="9">
-        <f t="shared" ref="V36" si="29">+V13/V11</f>
+      <c r="Z36" s="9">
+        <f t="shared" ref="Z36" si="30">+Z13/Z11</f>
         <v>0.56804033956661359</v>
       </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
@@ -3090,15 +3245,15 @@
       <c r="AV36" s="3"/>
       <c r="AW36" s="3"/>
       <c r="AX36" s="3"/>
-      <c r="AY36" s="6"/>
-      <c r="AZ36" s="6"/>
-      <c r="BA36" s="6"/>
-      <c r="BB36" s="6"/>
+      <c r="AY36" s="3"/>
+      <c r="AZ36" s="3"/>
+      <c r="BA36" s="3"/>
+      <c r="BB36" s="3"/>
       <c r="BC36" s="6"/>
-      <c r="BD36" s="3"/>
-      <c r="BE36" s="3"/>
-      <c r="BF36" s="3"/>
-      <c r="BG36" s="3"/>
+      <c r="BD36" s="6"/>
+      <c r="BE36" s="6"/>
+      <c r="BF36" s="6"/>
+      <c r="BG36" s="6"/>
       <c r="BH36" s="3"/>
       <c r="BI36" s="3"/>
       <c r="BJ36" s="3"/>
@@ -3106,33 +3261,37 @@
       <c r="BL36" s="3"/>
       <c r="BM36" s="3"/>
       <c r="BN36" s="3"/>
-    </row>
-    <row r="37" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO36" s="3"/>
+      <c r="BP36" s="3"/>
+      <c r="BQ36" s="3"/>
+      <c r="BR36" s="3"/>
+    </row>
+    <row r="37" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:H37" si="30">+C15/C11</f>
+        <f t="shared" ref="C37:H37" si="31">+C15/C11</f>
         <v>0.1452490856681353</v>
       </c>
       <c r="D37" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-0.86140424728919596</v>
       </c>
       <c r="E37" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.4824965512004353</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3.1469540201703197</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.19421948053439939</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.1498123107491508</v>
       </c>
       <c r="I37" s="9">
@@ -3144,54 +3303,57 @@
         <v>5.6104316922755304E-2</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" ref="K37:L37" si="31">+K15/K11</f>
+        <f t="shared" ref="K37:L37" si="32">+K15/K11</f>
         <v>0.21368325548573541</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.18828701442270612</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" ref="M37:N37" si="32">+M15/M11</f>
+        <f t="shared" ref="M37:N37" si="33">+M15/M11</f>
         <v>0.20910477510269643</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.0242762064123188E-2</v>
       </c>
-      <c r="O37" s="3"/>
-      <c r="P37" s="9" t="e">
-        <f t="shared" ref="P37:V37" si="33">+P15/P11</f>
+      <c r="O37" s="9">
+        <f t="shared" ref="O37" si="34">+O15/O11</f>
+        <v>0.22483118420809206</v>
+      </c>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="9" t="e">
+        <f t="shared" ref="T37:Z37" si="35">+T15/T11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q37" s="9" t="e">
-        <f t="shared" si="33"/>
+      <c r="U37" s="9" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R37" s="9">
-        <f t="shared" si="33"/>
+      <c r="V37" s="9">
+        <f t="shared" si="35"/>
         <v>5.4310624302432914E-2</v>
       </c>
-      <c r="S37" s="9">
-        <f t="shared" si="33"/>
+      <c r="W37" s="9">
+        <f t="shared" si="35"/>
         <v>7.0167003369782557E-2</v>
       </c>
-      <c r="T37" s="9">
-        <f t="shared" si="33"/>
+      <c r="X37" s="9">
+        <f t="shared" si="35"/>
         <v>9.5040344421987055E-2</v>
       </c>
-      <c r="U37" s="9">
-        <f t="shared" si="33"/>
+      <c r="Y37" s="9">
+        <f t="shared" si="35"/>
         <v>0.14754335132330965</v>
       </c>
-      <c r="V37" s="9">
-        <f t="shared" si="33"/>
+      <c r="Z37" s="9">
+        <f t="shared" si="35"/>
         <v>0.17575309896462765</v>
       </c>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3216,15 +3378,15 @@
       <c r="AV37" s="3"/>
       <c r="AW37" s="3"/>
       <c r="AX37" s="3"/>
-      <c r="AY37" s="6"/>
-      <c r="AZ37" s="6"/>
-      <c r="BA37" s="6"/>
-      <c r="BB37" s="6"/>
+      <c r="AY37" s="3"/>
+      <c r="AZ37" s="3"/>
+      <c r="BA37" s="3"/>
+      <c r="BB37" s="3"/>
       <c r="BC37" s="6"/>
-      <c r="BD37" s="3"/>
-      <c r="BE37" s="3"/>
-      <c r="BF37" s="3"/>
-      <c r="BG37" s="3"/>
+      <c r="BD37" s="6"/>
+      <c r="BE37" s="6"/>
+      <c r="BF37" s="6"/>
+      <c r="BG37" s="6"/>
       <c r="BH37" s="3"/>
       <c r="BI37" s="3"/>
       <c r="BJ37" s="3"/>
@@ -3232,33 +3394,37 @@
       <c r="BL37" s="3"/>
       <c r="BM37" s="3"/>
       <c r="BN37" s="3"/>
-    </row>
-    <row r="38" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO37" s="3"/>
+      <c r="BP37" s="3"/>
+      <c r="BQ37" s="3"/>
+      <c r="BR37" s="3"/>
+    </row>
+    <row r="38" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="9">
-        <f t="shared" ref="C38:H38" si="34">+C22/C21</f>
+        <f t="shared" ref="C38:H38" si="36">+C22/C21</f>
         <v>0.24017588521175653</v>
       </c>
       <c r="D38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-7.1262763040589414E-2</v>
       </c>
       <c r="E38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-6.3295720672769853E-2</v>
       </c>
       <c r="F38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-3.5033627893122352E-2</v>
       </c>
       <c r="G38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.1886946527945802</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.38095619123824764</v>
       </c>
       <c r="I38" s="9">
@@ -3270,54 +3436,57 @@
         <v>1.8692307692307693</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" ref="K38:L38" si="35">+K22/K21</f>
+        <f t="shared" ref="K38:L38" si="37">+K22/K21</f>
         <v>0.26862437765074682</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.41217735889471996</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:N38" si="36">+M22/M21</f>
+        <f t="shared" ref="M38:N38" si="38">+M22/M21</f>
         <v>0.28637544480101296</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-2.0144120537176548E-2</v>
       </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="9" t="e">
-        <f t="shared" ref="P38:V38" si="37">+P22/P21</f>
+      <c r="O38" s="9">
+        <f t="shared" ref="O38" si="39">+O22/O21</f>
+        <v>0.24564409245191532</v>
+      </c>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="9" t="e">
+        <f t="shared" ref="T38:Z38" si="40">+T22/T21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q38" s="9" t="e">
-        <f t="shared" si="37"/>
+      <c r="U38" s="9" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="9" t="e">
-        <f t="shared" si="37"/>
+      <c r="V38" s="9" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S38" s="9" t="e">
-        <f t="shared" si="37"/>
+      <c r="W38" s="9" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T38" s="9">
-        <f t="shared" si="37"/>
+      <c r="X38" s="9">
+        <f t="shared" si="40"/>
         <v>0.29894216510133464</v>
       </c>
-      <c r="U38" s="9">
-        <f t="shared" si="37"/>
+      <c r="Y38" s="9">
+        <f t="shared" si="40"/>
         <v>0.31421523942302537</v>
       </c>
-      <c r="V38" s="9">
-        <f t="shared" si="37"/>
+      <c r="Z38" s="9">
+        <f t="shared" si="40"/>
         <v>0.28770963812873418</v>
       </c>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3342,15 +3511,15 @@
       <c r="AV38" s="3"/>
       <c r="AW38" s="3"/>
       <c r="AX38" s="3"/>
-      <c r="AY38" s="6"/>
-      <c r="AZ38" s="6"/>
-      <c r="BA38" s="6"/>
-      <c r="BB38" s="6"/>
+      <c r="AY38" s="3"/>
+      <c r="AZ38" s="3"/>
+      <c r="BA38" s="3"/>
+      <c r="BB38" s="3"/>
       <c r="BC38" s="6"/>
-      <c r="BD38" s="3"/>
-      <c r="BE38" s="3"/>
-      <c r="BF38" s="3"/>
-      <c r="BG38" s="3"/>
+      <c r="BD38" s="6"/>
+      <c r="BE38" s="6"/>
+      <c r="BF38" s="6"/>
+      <c r="BG38" s="6"/>
       <c r="BH38" s="3"/>
       <c r="BI38" s="3"/>
       <c r="BJ38" s="3"/>
@@ -3358,8 +3527,12 @@
       <c r="BL38" s="3"/>
       <c r="BM38" s="3"/>
       <c r="BN38" s="3"/>
-    </row>
-    <row r="39" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO38" s="3"/>
+      <c r="BP38" s="3"/>
+      <c r="BQ38" s="3"/>
+      <c r="BR38" s="3"/>
+    </row>
+    <row r="39" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3408,15 +3581,15 @@
       <c r="AV39" s="3"/>
       <c r="AW39" s="3"/>
       <c r="AX39" s="3"/>
-      <c r="AY39" s="6"/>
-      <c r="AZ39" s="6"/>
-      <c r="BA39" s="6"/>
-      <c r="BB39" s="6"/>
+      <c r="AY39" s="3"/>
+      <c r="AZ39" s="3"/>
+      <c r="BA39" s="3"/>
+      <c r="BB39" s="3"/>
       <c r="BC39" s="6"/>
-      <c r="BD39" s="3"/>
-      <c r="BE39" s="3"/>
-      <c r="BF39" s="3"/>
-      <c r="BG39" s="3"/>
+      <c r="BD39" s="6"/>
+      <c r="BE39" s="6"/>
+      <c r="BF39" s="6"/>
+      <c r="BG39" s="6"/>
       <c r="BH39" s="3"/>
       <c r="BI39" s="3"/>
       <c r="BJ39" s="3"/>
@@ -3424,8 +3597,12 @@
       <c r="BL39" s="3"/>
       <c r="BM39" s="3"/>
       <c r="BN39" s="3"/>
-    </row>
-    <row r="40" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO39" s="3"/>
+      <c r="BP39" s="3"/>
+      <c r="BQ39" s="3"/>
+      <c r="BR39" s="3"/>
+    </row>
+    <row r="40" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3474,15 +3651,15 @@
       <c r="AV40" s="3"/>
       <c r="AW40" s="3"/>
       <c r="AX40" s="3"/>
-      <c r="AY40" s="6"/>
-      <c r="AZ40" s="6"/>
-      <c r="BA40" s="6"/>
-      <c r="BB40" s="6"/>
+      <c r="AY40" s="3"/>
+      <c r="AZ40" s="3"/>
+      <c r="BA40" s="3"/>
+      <c r="BB40" s="3"/>
       <c r="BC40" s="6"/>
-      <c r="BD40" s="3"/>
-      <c r="BE40" s="3"/>
-      <c r="BF40" s="3"/>
-      <c r="BG40" s="3"/>
+      <c r="BD40" s="6"/>
+      <c r="BE40" s="6"/>
+      <c r="BF40" s="6"/>
+      <c r="BG40" s="6"/>
       <c r="BH40" s="3"/>
       <c r="BI40" s="3"/>
       <c r="BJ40" s="3"/>
@@ -3490,8 +3667,12 @@
       <c r="BL40" s="3"/>
       <c r="BM40" s="3"/>
       <c r="BN40" s="3"/>
-    </row>
-    <row r="41" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO40" s="3"/>
+      <c r="BP40" s="3"/>
+      <c r="BQ40" s="3"/>
+      <c r="BR40" s="3"/>
+    </row>
+    <row r="41" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3540,15 +3721,15 @@
       <c r="AV41" s="3"/>
       <c r="AW41" s="3"/>
       <c r="AX41" s="3"/>
-      <c r="AY41" s="6"/>
-      <c r="AZ41" s="6"/>
-      <c r="BA41" s="6"/>
-      <c r="BB41" s="6"/>
+      <c r="AY41" s="3"/>
+      <c r="AZ41" s="3"/>
+      <c r="BA41" s="3"/>
+      <c r="BB41" s="3"/>
       <c r="BC41" s="6"/>
-      <c r="BD41" s="3"/>
-      <c r="BE41" s="3"/>
-      <c r="BF41" s="3"/>
-      <c r="BG41" s="3"/>
+      <c r="BD41" s="6"/>
+      <c r="BE41" s="6"/>
+      <c r="BF41" s="6"/>
+      <c r="BG41" s="6"/>
       <c r="BH41" s="3"/>
       <c r="BI41" s="3"/>
       <c r="BJ41" s="3"/>
@@ -3556,8 +3737,12 @@
       <c r="BL41" s="3"/>
       <c r="BM41" s="3"/>
       <c r="BN41" s="3"/>
-    </row>
-    <row r="42" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO41" s="3"/>
+      <c r="BP41" s="3"/>
+      <c r="BQ41" s="3"/>
+      <c r="BR41" s="3"/>
+    </row>
+    <row r="42" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3606,15 +3791,15 @@
       <c r="AV42" s="3"/>
       <c r="AW42" s="3"/>
       <c r="AX42" s="3"/>
-      <c r="AY42" s="6"/>
-      <c r="AZ42" s="6"/>
-      <c r="BA42" s="6"/>
-      <c r="BB42" s="6"/>
+      <c r="AY42" s="3"/>
+      <c r="AZ42" s="3"/>
+      <c r="BA42" s="3"/>
+      <c r="BB42" s="3"/>
       <c r="BC42" s="6"/>
-      <c r="BD42" s="3"/>
-      <c r="BE42" s="3"/>
-      <c r="BF42" s="3"/>
-      <c r="BG42" s="3"/>
+      <c r="BD42" s="6"/>
+      <c r="BE42" s="6"/>
+      <c r="BF42" s="6"/>
+      <c r="BG42" s="6"/>
       <c r="BH42" s="3"/>
       <c r="BI42" s="3"/>
       <c r="BJ42" s="3"/>
@@ -3622,8 +3807,12 @@
       <c r="BL42" s="3"/>
       <c r="BM42" s="3"/>
       <c r="BN42" s="3"/>
-    </row>
-    <row r="43" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO42" s="3"/>
+      <c r="BP42" s="3"/>
+      <c r="BQ42" s="3"/>
+      <c r="BR42" s="3"/>
+    </row>
+    <row r="43" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3672,15 +3861,15 @@
       <c r="AV43" s="3"/>
       <c r="AW43" s="3"/>
       <c r="AX43" s="3"/>
-      <c r="AY43" s="6"/>
-      <c r="AZ43" s="6"/>
-      <c r="BA43" s="6"/>
-      <c r="BB43" s="6"/>
+      <c r="AY43" s="3"/>
+      <c r="AZ43" s="3"/>
+      <c r="BA43" s="3"/>
+      <c r="BB43" s="3"/>
       <c r="BC43" s="6"/>
-      <c r="BD43" s="3"/>
-      <c r="BE43" s="3"/>
-      <c r="BF43" s="3"/>
-      <c r="BG43" s="3"/>
+      <c r="BD43" s="6"/>
+      <c r="BE43" s="6"/>
+      <c r="BF43" s="6"/>
+      <c r="BG43" s="6"/>
       <c r="BH43" s="3"/>
       <c r="BI43" s="3"/>
       <c r="BJ43" s="3"/>
@@ -3688,8 +3877,12 @@
       <c r="BL43" s="3"/>
       <c r="BM43" s="3"/>
       <c r="BN43" s="3"/>
-    </row>
-    <row r="44" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO43" s="3"/>
+      <c r="BP43" s="3"/>
+      <c r="BQ43" s="3"/>
+      <c r="BR43" s="3"/>
+    </row>
+    <row r="44" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -3738,15 +3931,15 @@
       <c r="AV44" s="3"/>
       <c r="AW44" s="3"/>
       <c r="AX44" s="3"/>
-      <c r="AY44" s="6"/>
-      <c r="AZ44" s="6"/>
-      <c r="BA44" s="6"/>
-      <c r="BB44" s="6"/>
+      <c r="AY44" s="3"/>
+      <c r="AZ44" s="3"/>
+      <c r="BA44" s="3"/>
+      <c r="BB44" s="3"/>
       <c r="BC44" s="6"/>
-      <c r="BD44" s="3"/>
-      <c r="BE44" s="3"/>
-      <c r="BF44" s="3"/>
-      <c r="BG44" s="3"/>
+      <c r="BD44" s="6"/>
+      <c r="BE44" s="6"/>
+      <c r="BF44" s="6"/>
+      <c r="BG44" s="6"/>
       <c r="BH44" s="3"/>
       <c r="BI44" s="3"/>
       <c r="BJ44" s="3"/>
@@ -3754,8 +3947,12 @@
       <c r="BL44" s="3"/>
       <c r="BM44" s="3"/>
       <c r="BN44" s="3"/>
-    </row>
-    <row r="45" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO44" s="3"/>
+      <c r="BP44" s="3"/>
+      <c r="BQ44" s="3"/>
+      <c r="BR44" s="3"/>
+    </row>
+    <row r="45" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -3804,15 +4001,15 @@
       <c r="AV45" s="3"/>
       <c r="AW45" s="3"/>
       <c r="AX45" s="3"/>
-      <c r="AY45" s="6"/>
-      <c r="AZ45" s="6"/>
-      <c r="BA45" s="6"/>
-      <c r="BB45" s="6"/>
+      <c r="AY45" s="3"/>
+      <c r="AZ45" s="3"/>
+      <c r="BA45" s="3"/>
+      <c r="BB45" s="3"/>
       <c r="BC45" s="6"/>
-      <c r="BD45" s="3"/>
-      <c r="BE45" s="3"/>
-      <c r="BF45" s="3"/>
-      <c r="BG45" s="3"/>
+      <c r="BD45" s="6"/>
+      <c r="BE45" s="6"/>
+      <c r="BF45" s="6"/>
+      <c r="BG45" s="6"/>
       <c r="BH45" s="3"/>
       <c r="BI45" s="3"/>
       <c r="BJ45" s="3"/>
@@ -3820,8 +4017,12 @@
       <c r="BL45" s="3"/>
       <c r="BM45" s="3"/>
       <c r="BN45" s="3"/>
-    </row>
-    <row r="46" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO45" s="3"/>
+      <c r="BP45" s="3"/>
+      <c r="BQ45" s="3"/>
+      <c r="BR45" s="3"/>
+    </row>
+    <row r="46" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3870,15 +4071,15 @@
       <c r="AV46" s="3"/>
       <c r="AW46" s="3"/>
       <c r="AX46" s="3"/>
-      <c r="AY46" s="6"/>
-      <c r="AZ46" s="6"/>
-      <c r="BA46" s="6"/>
-      <c r="BB46" s="6"/>
+      <c r="AY46" s="3"/>
+      <c r="AZ46" s="3"/>
+      <c r="BA46" s="3"/>
+      <c r="BB46" s="3"/>
       <c r="BC46" s="6"/>
-      <c r="BD46" s="3"/>
-      <c r="BE46" s="3"/>
-      <c r="BF46" s="3"/>
-      <c r="BG46" s="3"/>
+      <c r="BD46" s="6"/>
+      <c r="BE46" s="6"/>
+      <c r="BF46" s="6"/>
+      <c r="BG46" s="6"/>
       <c r="BH46" s="3"/>
       <c r="BI46" s="3"/>
       <c r="BJ46" s="3"/>
@@ -3886,8 +4087,12 @@
       <c r="BL46" s="3"/>
       <c r="BM46" s="3"/>
       <c r="BN46" s="3"/>
-    </row>
-    <row r="47" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO46" s="3"/>
+      <c r="BP46" s="3"/>
+      <c r="BQ46" s="3"/>
+      <c r="BR46" s="3"/>
+    </row>
+    <row r="47" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -3936,15 +4141,15 @@
       <c r="AV47" s="3"/>
       <c r="AW47" s="3"/>
       <c r="AX47" s="3"/>
-      <c r="AY47" s="6"/>
-      <c r="AZ47" s="6"/>
-      <c r="BA47" s="6"/>
-      <c r="BB47" s="6"/>
+      <c r="AY47" s="3"/>
+      <c r="AZ47" s="3"/>
+      <c r="BA47" s="3"/>
+      <c r="BB47" s="3"/>
       <c r="BC47" s="6"/>
-      <c r="BD47" s="3"/>
-      <c r="BE47" s="3"/>
-      <c r="BF47" s="3"/>
-      <c r="BG47" s="3"/>
+      <c r="BD47" s="6"/>
+      <c r="BE47" s="6"/>
+      <c r="BF47" s="6"/>
+      <c r="BG47" s="6"/>
       <c r="BH47" s="3"/>
       <c r="BI47" s="3"/>
       <c r="BJ47" s="3"/>
@@ -3952,8 +4157,12 @@
       <c r="BL47" s="3"/>
       <c r="BM47" s="3"/>
       <c r="BN47" s="3"/>
-    </row>
-    <row r="48" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="BO47" s="3"/>
+      <c r="BP47" s="3"/>
+      <c r="BQ47" s="3"/>
+      <c r="BR47" s="3"/>
+    </row>
+    <row r="48" spans="2:70" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4002,15 +4211,15 @@
       <c r="AV48" s="3"/>
       <c r="AW48" s="3"/>
       <c r="AX48" s="3"/>
-      <c r="AY48" s="6"/>
-      <c r="AZ48" s="6"/>
-      <c r="BA48" s="6"/>
-      <c r="BB48" s="6"/>
+      <c r="AY48" s="3"/>
+      <c r="AZ48" s="3"/>
+      <c r="BA48" s="3"/>
+      <c r="BB48" s="3"/>
       <c r="BC48" s="6"/>
-      <c r="BD48" s="3"/>
-      <c r="BE48" s="3"/>
-      <c r="BF48" s="3"/>
-      <c r="BG48" s="3"/>
+      <c r="BD48" s="6"/>
+      <c r="BE48" s="6"/>
+      <c r="BF48" s="6"/>
+      <c r="BG48" s="6"/>
       <c r="BH48" s="3"/>
       <c r="BI48" s="3"/>
       <c r="BJ48" s="3"/>
@@ -4018,8 +4227,12 @@
       <c r="BL48" s="3"/>
       <c r="BM48" s="3"/>
       <c r="BN48" s="3"/>
-    </row>
-    <row r="49" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO48" s="3"/>
+      <c r="BP48" s="3"/>
+      <c r="BQ48" s="3"/>
+      <c r="BR48" s="3"/>
+    </row>
+    <row r="49" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4068,15 +4281,15 @@
       <c r="AV49" s="3"/>
       <c r="AW49" s="3"/>
       <c r="AX49" s="3"/>
-      <c r="AY49" s="6"/>
-      <c r="AZ49" s="6"/>
-      <c r="BA49" s="6"/>
-      <c r="BB49" s="6"/>
+      <c r="AY49" s="3"/>
+      <c r="AZ49" s="3"/>
+      <c r="BA49" s="3"/>
+      <c r="BB49" s="3"/>
       <c r="BC49" s="6"/>
-      <c r="BD49" s="3"/>
-      <c r="BE49" s="3"/>
-      <c r="BF49" s="3"/>
-      <c r="BG49" s="3"/>
+      <c r="BD49" s="6"/>
+      <c r="BE49" s="6"/>
+      <c r="BF49" s="6"/>
+      <c r="BG49" s="6"/>
       <c r="BH49" s="3"/>
       <c r="BI49" s="3"/>
       <c r="BJ49" s="3"/>
@@ -4084,8 +4297,12 @@
       <c r="BL49" s="3"/>
       <c r="BM49" s="3"/>
       <c r="BN49" s="3"/>
-    </row>
-    <row r="50" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO49" s="3"/>
+      <c r="BP49" s="3"/>
+      <c r="BQ49" s="3"/>
+      <c r="BR49" s="3"/>
+    </row>
+    <row r="50" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4134,15 +4351,15 @@
       <c r="AV50" s="3"/>
       <c r="AW50" s="3"/>
       <c r="AX50" s="3"/>
-      <c r="AY50" s="6"/>
-      <c r="AZ50" s="6"/>
-      <c r="BA50" s="6"/>
-      <c r="BB50" s="6"/>
+      <c r="AY50" s="3"/>
+      <c r="AZ50" s="3"/>
+      <c r="BA50" s="3"/>
+      <c r="BB50" s="3"/>
       <c r="BC50" s="6"/>
-      <c r="BD50" s="3"/>
-      <c r="BE50" s="3"/>
-      <c r="BF50" s="3"/>
-      <c r="BG50" s="3"/>
+      <c r="BD50" s="6"/>
+      <c r="BE50" s="6"/>
+      <c r="BF50" s="6"/>
+      <c r="BG50" s="6"/>
       <c r="BH50" s="3"/>
       <c r="BI50" s="3"/>
       <c r="BJ50" s="3"/>
@@ -4150,8 +4367,12 @@
       <c r="BL50" s="3"/>
       <c r="BM50" s="3"/>
       <c r="BN50" s="3"/>
-    </row>
-    <row r="51" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO50" s="3"/>
+      <c r="BP50" s="3"/>
+      <c r="BQ50" s="3"/>
+      <c r="BR50" s="3"/>
+    </row>
+    <row r="51" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -4200,15 +4421,15 @@
       <c r="AV51" s="3"/>
       <c r="AW51" s="3"/>
       <c r="AX51" s="3"/>
-      <c r="AY51" s="6"/>
-      <c r="AZ51" s="6"/>
-      <c r="BA51" s="6"/>
-      <c r="BB51" s="6"/>
+      <c r="AY51" s="3"/>
+      <c r="AZ51" s="3"/>
+      <c r="BA51" s="3"/>
+      <c r="BB51" s="3"/>
       <c r="BC51" s="6"/>
-      <c r="BD51" s="3"/>
-      <c r="BE51" s="3"/>
-      <c r="BF51" s="3"/>
-      <c r="BG51" s="3"/>
+      <c r="BD51" s="6"/>
+      <c r="BE51" s="6"/>
+      <c r="BF51" s="6"/>
+      <c r="BG51" s="6"/>
       <c r="BH51" s="3"/>
       <c r="BI51" s="3"/>
       <c r="BJ51" s="3"/>
@@ -4216,8 +4437,12 @@
       <c r="BL51" s="3"/>
       <c r="BM51" s="3"/>
       <c r="BN51" s="3"/>
-    </row>
-    <row r="52" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO51" s="3"/>
+      <c r="BP51" s="3"/>
+      <c r="BQ51" s="3"/>
+      <c r="BR51" s="3"/>
+    </row>
+    <row r="52" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4266,15 +4491,15 @@
       <c r="AV52" s="3"/>
       <c r="AW52" s="3"/>
       <c r="AX52" s="3"/>
-      <c r="AY52" s="6"/>
-      <c r="AZ52" s="6"/>
-      <c r="BA52" s="6"/>
-      <c r="BB52" s="6"/>
+      <c r="AY52" s="3"/>
+      <c r="AZ52" s="3"/>
+      <c r="BA52" s="3"/>
+      <c r="BB52" s="3"/>
       <c r="BC52" s="6"/>
-      <c r="BD52" s="3"/>
-      <c r="BE52" s="3"/>
-      <c r="BF52" s="3"/>
-      <c r="BG52" s="3"/>
+      <c r="BD52" s="6"/>
+      <c r="BE52" s="6"/>
+      <c r="BF52" s="6"/>
+      <c r="BG52" s="6"/>
       <c r="BH52" s="3"/>
       <c r="BI52" s="3"/>
       <c r="BJ52" s="3"/>
@@ -4282,8 +4507,12 @@
       <c r="BL52" s="3"/>
       <c r="BM52" s="3"/>
       <c r="BN52" s="3"/>
-    </row>
-    <row r="53" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO52" s="3"/>
+      <c r="BP52" s="3"/>
+      <c r="BQ52" s="3"/>
+      <c r="BR52" s="3"/>
+    </row>
+    <row r="53" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4332,15 +4561,15 @@
       <c r="AV53" s="3"/>
       <c r="AW53" s="3"/>
       <c r="AX53" s="3"/>
-      <c r="AY53" s="6"/>
-      <c r="AZ53" s="6"/>
-      <c r="BA53" s="6"/>
-      <c r="BB53" s="6"/>
+      <c r="AY53" s="3"/>
+      <c r="AZ53" s="3"/>
+      <c r="BA53" s="3"/>
+      <c r="BB53" s="3"/>
       <c r="BC53" s="6"/>
-      <c r="BD53" s="3"/>
-      <c r="BE53" s="3"/>
-      <c r="BF53" s="3"/>
-      <c r="BG53" s="3"/>
+      <c r="BD53" s="6"/>
+      <c r="BE53" s="6"/>
+      <c r="BF53" s="6"/>
+      <c r="BG53" s="6"/>
       <c r="BH53" s="3"/>
       <c r="BI53" s="3"/>
       <c r="BJ53" s="3"/>
@@ -4348,8 +4577,12 @@
       <c r="BL53" s="3"/>
       <c r="BM53" s="3"/>
       <c r="BN53" s="3"/>
-    </row>
-    <row r="54" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO53" s="3"/>
+      <c r="BP53" s="3"/>
+      <c r="BQ53" s="3"/>
+      <c r="BR53" s="3"/>
+    </row>
+    <row r="54" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -4398,15 +4631,15 @@
       <c r="AV54" s="3"/>
       <c r="AW54" s="3"/>
       <c r="AX54" s="3"/>
-      <c r="AY54" s="6"/>
-      <c r="AZ54" s="6"/>
-      <c r="BA54" s="6"/>
-      <c r="BB54" s="6"/>
+      <c r="AY54" s="3"/>
+      <c r="AZ54" s="3"/>
+      <c r="BA54" s="3"/>
+      <c r="BB54" s="3"/>
       <c r="BC54" s="6"/>
-      <c r="BD54" s="3"/>
-      <c r="BE54" s="3"/>
-      <c r="BF54" s="3"/>
-      <c r="BG54" s="3"/>
+      <c r="BD54" s="6"/>
+      <c r="BE54" s="6"/>
+      <c r="BF54" s="6"/>
+      <c r="BG54" s="6"/>
       <c r="BH54" s="3"/>
       <c r="BI54" s="3"/>
       <c r="BJ54" s="3"/>
@@ -4414,8 +4647,12 @@
       <c r="BL54" s="3"/>
       <c r="BM54" s="3"/>
       <c r="BN54" s="3"/>
-    </row>
-    <row r="55" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO54" s="3"/>
+      <c r="BP54" s="3"/>
+      <c r="BQ54" s="3"/>
+      <c r="BR54" s="3"/>
+    </row>
+    <row r="55" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -4464,15 +4701,15 @@
       <c r="AV55" s="3"/>
       <c r="AW55" s="3"/>
       <c r="AX55" s="3"/>
-      <c r="AY55" s="6"/>
-      <c r="AZ55" s="6"/>
-      <c r="BA55" s="6"/>
-      <c r="BB55" s="6"/>
+      <c r="AY55" s="3"/>
+      <c r="AZ55" s="3"/>
+      <c r="BA55" s="3"/>
+      <c r="BB55" s="3"/>
       <c r="BC55" s="6"/>
-      <c r="BD55" s="3"/>
-      <c r="BE55" s="3"/>
-      <c r="BF55" s="3"/>
-      <c r="BG55" s="3"/>
+      <c r="BD55" s="6"/>
+      <c r="BE55" s="6"/>
+      <c r="BF55" s="6"/>
+      <c r="BG55" s="6"/>
       <c r="BH55" s="3"/>
       <c r="BI55" s="3"/>
       <c r="BJ55" s="3"/>
@@ -4480,8 +4717,12 @@
       <c r="BL55" s="3"/>
       <c r="BM55" s="3"/>
       <c r="BN55" s="3"/>
-    </row>
-    <row r="56" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO55" s="3"/>
+      <c r="BP55" s="3"/>
+      <c r="BQ55" s="3"/>
+      <c r="BR55" s="3"/>
+    </row>
+    <row r="56" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -4530,15 +4771,15 @@
       <c r="AV56" s="3"/>
       <c r="AW56" s="3"/>
       <c r="AX56" s="3"/>
-      <c r="AY56" s="6"/>
-      <c r="AZ56" s="6"/>
-      <c r="BA56" s="6"/>
-      <c r="BB56" s="6"/>
+      <c r="AY56" s="3"/>
+      <c r="AZ56" s="3"/>
+      <c r="BA56" s="3"/>
+      <c r="BB56" s="3"/>
       <c r="BC56" s="6"/>
-      <c r="BD56" s="3"/>
-      <c r="BE56" s="3"/>
-      <c r="BF56" s="3"/>
-      <c r="BG56" s="3"/>
+      <c r="BD56" s="6"/>
+      <c r="BE56" s="6"/>
+      <c r="BF56" s="6"/>
+      <c r="BG56" s="6"/>
       <c r="BH56" s="3"/>
       <c r="BI56" s="3"/>
       <c r="BJ56" s="3"/>
@@ -4546,8 +4787,12 @@
       <c r="BL56" s="3"/>
       <c r="BM56" s="3"/>
       <c r="BN56" s="3"/>
-    </row>
-    <row r="57" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO56" s="3"/>
+      <c r="BP56" s="3"/>
+      <c r="BQ56" s="3"/>
+      <c r="BR56" s="3"/>
+    </row>
+    <row r="57" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -4596,15 +4841,15 @@
       <c r="AV57" s="3"/>
       <c r="AW57" s="3"/>
       <c r="AX57" s="3"/>
-      <c r="AY57" s="6"/>
-      <c r="AZ57" s="6"/>
-      <c r="BA57" s="6"/>
-      <c r="BB57" s="6"/>
+      <c r="AY57" s="3"/>
+      <c r="AZ57" s="3"/>
+      <c r="BA57" s="3"/>
+      <c r="BB57" s="3"/>
       <c r="BC57" s="6"/>
-      <c r="BD57" s="3"/>
-      <c r="BE57" s="3"/>
-      <c r="BF57" s="3"/>
-      <c r="BG57" s="3"/>
+      <c r="BD57" s="6"/>
+      <c r="BE57" s="6"/>
+      <c r="BF57" s="6"/>
+      <c r="BG57" s="6"/>
       <c r="BH57" s="3"/>
       <c r="BI57" s="3"/>
       <c r="BJ57" s="3"/>
@@ -4612,8 +4857,12 @@
       <c r="BL57" s="3"/>
       <c r="BM57" s="3"/>
       <c r="BN57" s="3"/>
-    </row>
-    <row r="58" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO57" s="3"/>
+      <c r="BP57" s="3"/>
+      <c r="BQ57" s="3"/>
+      <c r="BR57" s="3"/>
+    </row>
+    <row r="58" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -4662,15 +4911,15 @@
       <c r="AV58" s="3"/>
       <c r="AW58" s="3"/>
       <c r="AX58" s="3"/>
-      <c r="AY58" s="6"/>
-      <c r="AZ58" s="6"/>
-      <c r="BA58" s="6"/>
-      <c r="BB58" s="6"/>
+      <c r="AY58" s="3"/>
+      <c r="AZ58" s="3"/>
+      <c r="BA58" s="3"/>
+      <c r="BB58" s="3"/>
       <c r="BC58" s="6"/>
-      <c r="BD58" s="3"/>
-      <c r="BE58" s="3"/>
-      <c r="BF58" s="3"/>
-      <c r="BG58" s="3"/>
+      <c r="BD58" s="6"/>
+      <c r="BE58" s="6"/>
+      <c r="BF58" s="6"/>
+      <c r="BG58" s="6"/>
       <c r="BH58" s="3"/>
       <c r="BI58" s="3"/>
       <c r="BJ58" s="3"/>
@@ -4678,8 +4927,12 @@
       <c r="BL58" s="3"/>
       <c r="BM58" s="3"/>
       <c r="BN58" s="3"/>
-    </row>
-    <row r="59" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO58" s="3"/>
+      <c r="BP58" s="3"/>
+      <c r="BQ58" s="3"/>
+      <c r="BR58" s="3"/>
+    </row>
+    <row r="59" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -4728,15 +4981,15 @@
       <c r="AV59" s="3"/>
       <c r="AW59" s="3"/>
       <c r="AX59" s="3"/>
-      <c r="AY59" s="6"/>
-      <c r="AZ59" s="6"/>
-      <c r="BA59" s="6"/>
-      <c r="BB59" s="6"/>
+      <c r="AY59" s="3"/>
+      <c r="AZ59" s="3"/>
+      <c r="BA59" s="3"/>
+      <c r="BB59" s="3"/>
       <c r="BC59" s="6"/>
-      <c r="BD59" s="3"/>
-      <c r="BE59" s="3"/>
-      <c r="BF59" s="3"/>
-      <c r="BG59" s="3"/>
+      <c r="BD59" s="6"/>
+      <c r="BE59" s="6"/>
+      <c r="BF59" s="6"/>
+      <c r="BG59" s="6"/>
       <c r="BH59" s="3"/>
       <c r="BI59" s="3"/>
       <c r="BJ59" s="3"/>
@@ -4744,8 +4997,12 @@
       <c r="BL59" s="3"/>
       <c r="BM59" s="3"/>
       <c r="BN59" s="3"/>
-    </row>
-    <row r="60" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO59" s="3"/>
+      <c r="BP59" s="3"/>
+      <c r="BQ59" s="3"/>
+      <c r="BR59" s="3"/>
+    </row>
+    <row r="60" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -4794,15 +5051,15 @@
       <c r="AV60" s="3"/>
       <c r="AW60" s="3"/>
       <c r="AX60" s="3"/>
-      <c r="AY60" s="6"/>
-      <c r="AZ60" s="6"/>
-      <c r="BA60" s="6"/>
-      <c r="BB60" s="6"/>
+      <c r="AY60" s="3"/>
+      <c r="AZ60" s="3"/>
+      <c r="BA60" s="3"/>
+      <c r="BB60" s="3"/>
       <c r="BC60" s="6"/>
-      <c r="BD60" s="3"/>
-      <c r="BE60" s="3"/>
-      <c r="BF60" s="3"/>
-      <c r="BG60" s="3"/>
+      <c r="BD60" s="6"/>
+      <c r="BE60" s="6"/>
+      <c r="BF60" s="6"/>
+      <c r="BG60" s="6"/>
       <c r="BH60" s="3"/>
       <c r="BI60" s="3"/>
       <c r="BJ60" s="3"/>
@@ -4810,8 +5067,12 @@
       <c r="BL60" s="3"/>
       <c r="BM60" s="3"/>
       <c r="BN60" s="3"/>
-    </row>
-    <row r="61" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO60" s="3"/>
+      <c r="BP60" s="3"/>
+      <c r="BQ60" s="3"/>
+      <c r="BR60" s="3"/>
+    </row>
+    <row r="61" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -4860,15 +5121,15 @@
       <c r="AV61" s="3"/>
       <c r="AW61" s="3"/>
       <c r="AX61" s="3"/>
-      <c r="AY61" s="6"/>
-      <c r="AZ61" s="6"/>
-      <c r="BA61" s="6"/>
-      <c r="BB61" s="6"/>
+      <c r="AY61" s="3"/>
+      <c r="AZ61" s="3"/>
+      <c r="BA61" s="3"/>
+      <c r="BB61" s="3"/>
       <c r="BC61" s="6"/>
-      <c r="BD61" s="3"/>
-      <c r="BE61" s="3"/>
-      <c r="BF61" s="3"/>
-      <c r="BG61" s="3"/>
+      <c r="BD61" s="6"/>
+      <c r="BE61" s="6"/>
+      <c r="BF61" s="6"/>
+      <c r="BG61" s="6"/>
       <c r="BH61" s="3"/>
       <c r="BI61" s="3"/>
       <c r="BJ61" s="3"/>
@@ -4876,8 +5137,12 @@
       <c r="BL61" s="3"/>
       <c r="BM61" s="3"/>
       <c r="BN61" s="3"/>
-    </row>
-    <row r="62" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO61" s="3"/>
+      <c r="BP61" s="3"/>
+      <c r="BQ61" s="3"/>
+      <c r="BR61" s="3"/>
+    </row>
+    <row r="62" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4926,15 +5191,15 @@
       <c r="AV62" s="3"/>
       <c r="AW62" s="3"/>
       <c r="AX62" s="3"/>
-      <c r="AY62" s="6"/>
-      <c r="AZ62" s="6"/>
-      <c r="BA62" s="6"/>
-      <c r="BB62" s="6"/>
+      <c r="AY62" s="3"/>
+      <c r="AZ62" s="3"/>
+      <c r="BA62" s="3"/>
+      <c r="BB62" s="3"/>
       <c r="BC62" s="6"/>
-      <c r="BD62" s="3"/>
-      <c r="BE62" s="3"/>
-      <c r="BF62" s="3"/>
-      <c r="BG62" s="3"/>
+      <c r="BD62" s="6"/>
+      <c r="BE62" s="6"/>
+      <c r="BF62" s="6"/>
+      <c r="BG62" s="6"/>
       <c r="BH62" s="3"/>
       <c r="BI62" s="3"/>
       <c r="BJ62" s="3"/>
@@ -4942,8 +5207,12 @@
       <c r="BL62" s="3"/>
       <c r="BM62" s="3"/>
       <c r="BN62" s="3"/>
-    </row>
-    <row r="63" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO62" s="3"/>
+      <c r="BP62" s="3"/>
+      <c r="BQ62" s="3"/>
+      <c r="BR62" s="3"/>
+    </row>
+    <row r="63" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -4992,15 +5261,15 @@
       <c r="AV63" s="3"/>
       <c r="AW63" s="3"/>
       <c r="AX63" s="3"/>
-      <c r="AY63" s="6"/>
-      <c r="AZ63" s="6"/>
-      <c r="BA63" s="6"/>
-      <c r="BB63" s="6"/>
+      <c r="AY63" s="3"/>
+      <c r="AZ63" s="3"/>
+      <c r="BA63" s="3"/>
+      <c r="BB63" s="3"/>
       <c r="BC63" s="6"/>
-      <c r="BD63" s="3"/>
-      <c r="BE63" s="3"/>
-      <c r="BF63" s="3"/>
-      <c r="BG63" s="3"/>
+      <c r="BD63" s="6"/>
+      <c r="BE63" s="6"/>
+      <c r="BF63" s="6"/>
+      <c r="BG63" s="6"/>
       <c r="BH63" s="3"/>
       <c r="BI63" s="3"/>
       <c r="BJ63" s="3"/>
@@ -5008,8 +5277,12 @@
       <c r="BL63" s="3"/>
       <c r="BM63" s="3"/>
       <c r="BN63" s="3"/>
-    </row>
-    <row r="64" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO63" s="3"/>
+      <c r="BP63" s="3"/>
+      <c r="BQ63" s="3"/>
+      <c r="BR63" s="3"/>
+    </row>
+    <row r="64" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5058,15 +5331,15 @@
       <c r="AV64" s="3"/>
       <c r="AW64" s="3"/>
       <c r="AX64" s="3"/>
-      <c r="AY64" s="6"/>
-      <c r="AZ64" s="6"/>
-      <c r="BA64" s="6"/>
-      <c r="BB64" s="6"/>
+      <c r="AY64" s="3"/>
+      <c r="AZ64" s="3"/>
+      <c r="BA64" s="3"/>
+      <c r="BB64" s="3"/>
       <c r="BC64" s="6"/>
-      <c r="BD64" s="3"/>
-      <c r="BE64" s="3"/>
-      <c r="BF64" s="3"/>
-      <c r="BG64" s="3"/>
+      <c r="BD64" s="6"/>
+      <c r="BE64" s="6"/>
+      <c r="BF64" s="6"/>
+      <c r="BG64" s="6"/>
       <c r="BH64" s="3"/>
       <c r="BI64" s="3"/>
       <c r="BJ64" s="3"/>
@@ -5074,8 +5347,12 @@
       <c r="BL64" s="3"/>
       <c r="BM64" s="3"/>
       <c r="BN64" s="3"/>
-    </row>
-    <row r="65" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO64" s="3"/>
+      <c r="BP64" s="3"/>
+      <c r="BQ64" s="3"/>
+      <c r="BR64" s="3"/>
+    </row>
+    <row r="65" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -5124,15 +5401,15 @@
       <c r="AV65" s="3"/>
       <c r="AW65" s="3"/>
       <c r="AX65" s="3"/>
-      <c r="AY65" s="6"/>
-      <c r="AZ65" s="6"/>
-      <c r="BA65" s="6"/>
-      <c r="BB65" s="6"/>
+      <c r="AY65" s="3"/>
+      <c r="AZ65" s="3"/>
+      <c r="BA65" s="3"/>
+      <c r="BB65" s="3"/>
       <c r="BC65" s="6"/>
-      <c r="BD65" s="3"/>
-      <c r="BE65" s="3"/>
-      <c r="BF65" s="3"/>
-      <c r="BG65" s="3"/>
+      <c r="BD65" s="6"/>
+      <c r="BE65" s="6"/>
+      <c r="BF65" s="6"/>
+      <c r="BG65" s="6"/>
       <c r="BH65" s="3"/>
       <c r="BI65" s="3"/>
       <c r="BJ65" s="3"/>
@@ -5140,8 +5417,12 @@
       <c r="BL65" s="3"/>
       <c r="BM65" s="3"/>
       <c r="BN65" s="3"/>
-    </row>
-    <row r="66" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO65" s="3"/>
+      <c r="BP65" s="3"/>
+      <c r="BQ65" s="3"/>
+      <c r="BR65" s="3"/>
+    </row>
+    <row r="66" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -5190,15 +5471,15 @@
       <c r="AV66" s="3"/>
       <c r="AW66" s="3"/>
       <c r="AX66" s="3"/>
-      <c r="AY66" s="6"/>
-      <c r="AZ66" s="6"/>
-      <c r="BA66" s="6"/>
-      <c r="BB66" s="6"/>
+      <c r="AY66" s="3"/>
+      <c r="AZ66" s="3"/>
+      <c r="BA66" s="3"/>
+      <c r="BB66" s="3"/>
       <c r="BC66" s="6"/>
-      <c r="BD66" s="3"/>
-      <c r="BE66" s="3"/>
-      <c r="BF66" s="3"/>
-      <c r="BG66" s="3"/>
+      <c r="BD66" s="6"/>
+      <c r="BE66" s="6"/>
+      <c r="BF66" s="6"/>
+      <c r="BG66" s="6"/>
       <c r="BH66" s="3"/>
       <c r="BI66" s="3"/>
       <c r="BJ66" s="3"/>
@@ -5206,8 +5487,12 @@
       <c r="BL66" s="3"/>
       <c r="BM66" s="3"/>
       <c r="BN66" s="3"/>
-    </row>
-    <row r="67" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO66" s="3"/>
+      <c r="BP66" s="3"/>
+      <c r="BQ66" s="3"/>
+      <c r="BR66" s="3"/>
+    </row>
+    <row r="67" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -5256,15 +5541,15 @@
       <c r="AV67" s="3"/>
       <c r="AW67" s="3"/>
       <c r="AX67" s="3"/>
-      <c r="AY67" s="6"/>
-      <c r="AZ67" s="6"/>
-      <c r="BA67" s="6"/>
-      <c r="BB67" s="6"/>
+      <c r="AY67" s="3"/>
+      <c r="AZ67" s="3"/>
+      <c r="BA67" s="3"/>
+      <c r="BB67" s="3"/>
       <c r="BC67" s="6"/>
-      <c r="BD67" s="3"/>
-      <c r="BE67" s="3"/>
-      <c r="BF67" s="3"/>
-      <c r="BG67" s="3"/>
+      <c r="BD67" s="6"/>
+      <c r="BE67" s="6"/>
+      <c r="BF67" s="6"/>
+      <c r="BG67" s="6"/>
       <c r="BH67" s="3"/>
       <c r="BI67" s="3"/>
       <c r="BJ67" s="3"/>
@@ -5272,8 +5557,12 @@
       <c r="BL67" s="3"/>
       <c r="BM67" s="3"/>
       <c r="BN67" s="3"/>
-    </row>
-    <row r="68" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO67" s="3"/>
+      <c r="BP67" s="3"/>
+      <c r="BQ67" s="3"/>
+      <c r="BR67" s="3"/>
+    </row>
+    <row r="68" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -5322,15 +5611,15 @@
       <c r="AV68" s="3"/>
       <c r="AW68" s="3"/>
       <c r="AX68" s="3"/>
-      <c r="AY68" s="6"/>
-      <c r="AZ68" s="6"/>
-      <c r="BA68" s="6"/>
-      <c r="BB68" s="6"/>
+      <c r="AY68" s="3"/>
+      <c r="AZ68" s="3"/>
+      <c r="BA68" s="3"/>
+      <c r="BB68" s="3"/>
       <c r="BC68" s="6"/>
-      <c r="BD68" s="3"/>
-      <c r="BE68" s="3"/>
-      <c r="BF68" s="3"/>
-      <c r="BG68" s="3"/>
+      <c r="BD68" s="6"/>
+      <c r="BE68" s="6"/>
+      <c r="BF68" s="6"/>
+      <c r="BG68" s="6"/>
       <c r="BH68" s="3"/>
       <c r="BI68" s="3"/>
       <c r="BJ68" s="3"/>
@@ -5338,8 +5627,12 @@
       <c r="BL68" s="3"/>
       <c r="BM68" s="3"/>
       <c r="BN68" s="3"/>
-    </row>
-    <row r="69" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO68" s="3"/>
+      <c r="BP68" s="3"/>
+      <c r="BQ68" s="3"/>
+      <c r="BR68" s="3"/>
+    </row>
+    <row r="69" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -5388,15 +5681,15 @@
       <c r="AV69" s="3"/>
       <c r="AW69" s="3"/>
       <c r="AX69" s="3"/>
-      <c r="AY69" s="6"/>
-      <c r="AZ69" s="6"/>
-      <c r="BA69" s="6"/>
-      <c r="BB69" s="6"/>
+      <c r="AY69" s="3"/>
+      <c r="AZ69" s="3"/>
+      <c r="BA69" s="3"/>
+      <c r="BB69" s="3"/>
       <c r="BC69" s="6"/>
-      <c r="BD69" s="3"/>
-      <c r="BE69" s="3"/>
-      <c r="BF69" s="3"/>
-      <c r="BG69" s="3"/>
+      <c r="BD69" s="6"/>
+      <c r="BE69" s="6"/>
+      <c r="BF69" s="6"/>
+      <c r="BG69" s="6"/>
       <c r="BH69" s="3"/>
       <c r="BI69" s="3"/>
       <c r="BJ69" s="3"/>
@@ -5404,8 +5697,12 @@
       <c r="BL69" s="3"/>
       <c r="BM69" s="3"/>
       <c r="BN69" s="3"/>
-    </row>
-    <row r="70" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO69" s="3"/>
+      <c r="BP69" s="3"/>
+      <c r="BQ69" s="3"/>
+      <c r="BR69" s="3"/>
+    </row>
+    <row r="70" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -5454,15 +5751,15 @@
       <c r="AV70" s="3"/>
       <c r="AW70" s="3"/>
       <c r="AX70" s="3"/>
-      <c r="AY70" s="6"/>
-      <c r="AZ70" s="6"/>
-      <c r="BA70" s="6"/>
-      <c r="BB70" s="6"/>
+      <c r="AY70" s="3"/>
+      <c r="AZ70" s="3"/>
+      <c r="BA70" s="3"/>
+      <c r="BB70" s="3"/>
       <c r="BC70" s="6"/>
-      <c r="BD70" s="3"/>
-      <c r="BE70" s="3"/>
-      <c r="BF70" s="3"/>
-      <c r="BG70" s="3"/>
+      <c r="BD70" s="6"/>
+      <c r="BE70" s="6"/>
+      <c r="BF70" s="6"/>
+      <c r="BG70" s="6"/>
       <c r="BH70" s="3"/>
       <c r="BI70" s="3"/>
       <c r="BJ70" s="3"/>
@@ -5470,8 +5767,12 @@
       <c r="BL70" s="3"/>
       <c r="BM70" s="3"/>
       <c r="BN70" s="3"/>
-    </row>
-    <row r="71" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO70" s="3"/>
+      <c r="BP70" s="3"/>
+      <c r="BQ70" s="3"/>
+      <c r="BR70" s="3"/>
+    </row>
+    <row r="71" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -5520,15 +5821,15 @@
       <c r="AV71" s="3"/>
       <c r="AW71" s="3"/>
       <c r="AX71" s="3"/>
-      <c r="AY71" s="6"/>
-      <c r="AZ71" s="6"/>
-      <c r="BA71" s="6"/>
-      <c r="BB71" s="6"/>
+      <c r="AY71" s="3"/>
+      <c r="AZ71" s="3"/>
+      <c r="BA71" s="3"/>
+      <c r="BB71" s="3"/>
       <c r="BC71" s="6"/>
-      <c r="BD71" s="3"/>
-      <c r="BE71" s="3"/>
-      <c r="BF71" s="3"/>
-      <c r="BG71" s="3"/>
+      <c r="BD71" s="6"/>
+      <c r="BE71" s="6"/>
+      <c r="BF71" s="6"/>
+      <c r="BG71" s="6"/>
       <c r="BH71" s="3"/>
       <c r="BI71" s="3"/>
       <c r="BJ71" s="3"/>
@@ -5536,8 +5837,12 @@
       <c r="BL71" s="3"/>
       <c r="BM71" s="3"/>
       <c r="BN71" s="3"/>
-    </row>
-    <row r="72" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO71" s="3"/>
+      <c r="BP71" s="3"/>
+      <c r="BQ71" s="3"/>
+      <c r="BR71" s="3"/>
+    </row>
+    <row r="72" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -5586,15 +5891,15 @@
       <c r="AV72" s="3"/>
       <c r="AW72" s="3"/>
       <c r="AX72" s="3"/>
-      <c r="AY72" s="6"/>
-      <c r="AZ72" s="6"/>
-      <c r="BA72" s="6"/>
-      <c r="BB72" s="6"/>
+      <c r="AY72" s="3"/>
+      <c r="AZ72" s="3"/>
+      <c r="BA72" s="3"/>
+      <c r="BB72" s="3"/>
       <c r="BC72" s="6"/>
-      <c r="BD72" s="3"/>
-      <c r="BE72" s="3"/>
-      <c r="BF72" s="3"/>
-      <c r="BG72" s="3"/>
+      <c r="BD72" s="6"/>
+      <c r="BE72" s="6"/>
+      <c r="BF72" s="6"/>
+      <c r="BG72" s="6"/>
       <c r="BH72" s="3"/>
       <c r="BI72" s="3"/>
       <c r="BJ72" s="3"/>
@@ -5602,8 +5907,12 @@
       <c r="BL72" s="3"/>
       <c r="BM72" s="3"/>
       <c r="BN72" s="3"/>
-    </row>
-    <row r="73" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO72" s="3"/>
+      <c r="BP72" s="3"/>
+      <c r="BQ72" s="3"/>
+      <c r="BR72" s="3"/>
+    </row>
+    <row r="73" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -5652,15 +5961,15 @@
       <c r="AV73" s="3"/>
       <c r="AW73" s="3"/>
       <c r="AX73" s="3"/>
-      <c r="AY73" s="6"/>
-      <c r="AZ73" s="6"/>
-      <c r="BA73" s="6"/>
-      <c r="BB73" s="6"/>
+      <c r="AY73" s="3"/>
+      <c r="AZ73" s="3"/>
+      <c r="BA73" s="3"/>
+      <c r="BB73" s="3"/>
       <c r="BC73" s="6"/>
-      <c r="BD73" s="3"/>
-      <c r="BE73" s="3"/>
-      <c r="BF73" s="3"/>
-      <c r="BG73" s="3"/>
+      <c r="BD73" s="6"/>
+      <c r="BE73" s="6"/>
+      <c r="BF73" s="6"/>
+      <c r="BG73" s="6"/>
       <c r="BH73" s="3"/>
       <c r="BI73" s="3"/>
       <c r="BJ73" s="3"/>
@@ -5668,8 +5977,12 @@
       <c r="BL73" s="3"/>
       <c r="BM73" s="3"/>
       <c r="BN73" s="3"/>
-    </row>
-    <row r="74" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO73" s="3"/>
+      <c r="BP73" s="3"/>
+      <c r="BQ73" s="3"/>
+      <c r="BR73" s="3"/>
+    </row>
+    <row r="74" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -5718,15 +6031,15 @@
       <c r="AV74" s="3"/>
       <c r="AW74" s="3"/>
       <c r="AX74" s="3"/>
-      <c r="AY74" s="6"/>
-      <c r="AZ74" s="6"/>
-      <c r="BA74" s="6"/>
-      <c r="BB74" s="6"/>
+      <c r="AY74" s="3"/>
+      <c r="AZ74" s="3"/>
+      <c r="BA74" s="3"/>
+      <c r="BB74" s="3"/>
       <c r="BC74" s="6"/>
-      <c r="BD74" s="3"/>
-      <c r="BE74" s="3"/>
-      <c r="BF74" s="3"/>
-      <c r="BG74" s="3"/>
+      <c r="BD74" s="6"/>
+      <c r="BE74" s="6"/>
+      <c r="BF74" s="6"/>
+      <c r="BG74" s="6"/>
       <c r="BH74" s="3"/>
       <c r="BI74" s="3"/>
       <c r="BJ74" s="3"/>
@@ -5734,8 +6047,12 @@
       <c r="BL74" s="3"/>
       <c r="BM74" s="3"/>
       <c r="BN74" s="3"/>
-    </row>
-    <row r="75" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO74" s="3"/>
+      <c r="BP74" s="3"/>
+      <c r="BQ74" s="3"/>
+      <c r="BR74" s="3"/>
+    </row>
+    <row r="75" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -5784,15 +6101,15 @@
       <c r="AV75" s="3"/>
       <c r="AW75" s="3"/>
       <c r="AX75" s="3"/>
-      <c r="AY75" s="6"/>
-      <c r="AZ75" s="6"/>
-      <c r="BA75" s="6"/>
-      <c r="BB75" s="6"/>
+      <c r="AY75" s="3"/>
+      <c r="AZ75" s="3"/>
+      <c r="BA75" s="3"/>
+      <c r="BB75" s="3"/>
       <c r="BC75" s="6"/>
-      <c r="BD75" s="3"/>
-      <c r="BE75" s="3"/>
-      <c r="BF75" s="3"/>
-      <c r="BG75" s="3"/>
+      <c r="BD75" s="6"/>
+      <c r="BE75" s="6"/>
+      <c r="BF75" s="6"/>
+      <c r="BG75" s="6"/>
       <c r="BH75" s="3"/>
       <c r="BI75" s="3"/>
       <c r="BJ75" s="3"/>
@@ -5800,8 +6117,12 @@
       <c r="BL75" s="3"/>
       <c r="BM75" s="3"/>
       <c r="BN75" s="3"/>
-    </row>
-    <row r="76" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO75" s="3"/>
+      <c r="BP75" s="3"/>
+      <c r="BQ75" s="3"/>
+      <c r="BR75" s="3"/>
+    </row>
+    <row r="76" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -5850,15 +6171,15 @@
       <c r="AV76" s="3"/>
       <c r="AW76" s="3"/>
       <c r="AX76" s="3"/>
-      <c r="AY76" s="6"/>
-      <c r="AZ76" s="6"/>
-      <c r="BA76" s="6"/>
-      <c r="BB76" s="6"/>
+      <c r="AY76" s="3"/>
+      <c r="AZ76" s="3"/>
+      <c r="BA76" s="3"/>
+      <c r="BB76" s="3"/>
       <c r="BC76" s="6"/>
-      <c r="BD76" s="3"/>
-      <c r="BE76" s="3"/>
-      <c r="BF76" s="3"/>
-      <c r="BG76" s="3"/>
+      <c r="BD76" s="6"/>
+      <c r="BE76" s="6"/>
+      <c r="BF76" s="6"/>
+      <c r="BG76" s="6"/>
       <c r="BH76" s="3"/>
       <c r="BI76" s="3"/>
       <c r="BJ76" s="3"/>
@@ -5866,8 +6187,12 @@
       <c r="BL76" s="3"/>
       <c r="BM76" s="3"/>
       <c r="BN76" s="3"/>
-    </row>
-    <row r="77" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO76" s="3"/>
+      <c r="BP76" s="3"/>
+      <c r="BQ76" s="3"/>
+      <c r="BR76" s="3"/>
+    </row>
+    <row r="77" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -5916,15 +6241,15 @@
       <c r="AV77" s="3"/>
       <c r="AW77" s="3"/>
       <c r="AX77" s="3"/>
-      <c r="AY77" s="6"/>
-      <c r="AZ77" s="6"/>
-      <c r="BA77" s="6"/>
-      <c r="BB77" s="6"/>
+      <c r="AY77" s="3"/>
+      <c r="AZ77" s="3"/>
+      <c r="BA77" s="3"/>
+      <c r="BB77" s="3"/>
       <c r="BC77" s="6"/>
-      <c r="BD77" s="3"/>
-      <c r="BE77" s="3"/>
-      <c r="BF77" s="3"/>
-      <c r="BG77" s="3"/>
+      <c r="BD77" s="6"/>
+      <c r="BE77" s="6"/>
+      <c r="BF77" s="6"/>
+      <c r="BG77" s="6"/>
       <c r="BH77" s="3"/>
       <c r="BI77" s="3"/>
       <c r="BJ77" s="3"/>
@@ -5932,8 +6257,12 @@
       <c r="BL77" s="3"/>
       <c r="BM77" s="3"/>
       <c r="BN77" s="3"/>
-    </row>
-    <row r="78" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO77" s="3"/>
+      <c r="BP77" s="3"/>
+      <c r="BQ77" s="3"/>
+      <c r="BR77" s="3"/>
+    </row>
+    <row r="78" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -5982,15 +6311,15 @@
       <c r="AV78" s="3"/>
       <c r="AW78" s="3"/>
       <c r="AX78" s="3"/>
-      <c r="AY78" s="6"/>
-      <c r="AZ78" s="6"/>
-      <c r="BA78" s="6"/>
-      <c r="BB78" s="6"/>
+      <c r="AY78" s="3"/>
+      <c r="AZ78" s="3"/>
+      <c r="BA78" s="3"/>
+      <c r="BB78" s="3"/>
       <c r="BC78" s="6"/>
-      <c r="BD78" s="3"/>
-      <c r="BE78" s="3"/>
-      <c r="BF78" s="3"/>
-      <c r="BG78" s="3"/>
+      <c r="BD78" s="6"/>
+      <c r="BE78" s="6"/>
+      <c r="BF78" s="6"/>
+      <c r="BG78" s="6"/>
       <c r="BH78" s="3"/>
       <c r="BI78" s="3"/>
       <c r="BJ78" s="3"/>
@@ -5998,8 +6327,12 @@
       <c r="BL78" s="3"/>
       <c r="BM78" s="3"/>
       <c r="BN78" s="3"/>
-    </row>
-    <row r="79" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO78" s="3"/>
+      <c r="BP78" s="3"/>
+      <c r="BQ78" s="3"/>
+      <c r="BR78" s="3"/>
+    </row>
+    <row r="79" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -6048,15 +6381,15 @@
       <c r="AV79" s="3"/>
       <c r="AW79" s="3"/>
       <c r="AX79" s="3"/>
-      <c r="AY79" s="6"/>
-      <c r="AZ79" s="6"/>
-      <c r="BA79" s="6"/>
-      <c r="BB79" s="6"/>
+      <c r="AY79" s="3"/>
+      <c r="AZ79" s="3"/>
+      <c r="BA79" s="3"/>
+      <c r="BB79" s="3"/>
       <c r="BC79" s="6"/>
-      <c r="BD79" s="3"/>
-      <c r="BE79" s="3"/>
-      <c r="BF79" s="3"/>
-      <c r="BG79" s="3"/>
+      <c r="BD79" s="6"/>
+      <c r="BE79" s="6"/>
+      <c r="BF79" s="6"/>
+      <c r="BG79" s="6"/>
       <c r="BH79" s="3"/>
       <c r="BI79" s="3"/>
       <c r="BJ79" s="3"/>
@@ -6064,8 +6397,12 @@
       <c r="BL79" s="3"/>
       <c r="BM79" s="3"/>
       <c r="BN79" s="3"/>
-    </row>
-    <row r="80" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO79" s="3"/>
+      <c r="BP79" s="3"/>
+      <c r="BQ79" s="3"/>
+      <c r="BR79" s="3"/>
+    </row>
+    <row r="80" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -6114,15 +6451,15 @@
       <c r="AV80" s="3"/>
       <c r="AW80" s="3"/>
       <c r="AX80" s="3"/>
-      <c r="AY80" s="6"/>
-      <c r="AZ80" s="6"/>
-      <c r="BA80" s="6"/>
-      <c r="BB80" s="6"/>
+      <c r="AY80" s="3"/>
+      <c r="AZ80" s="3"/>
+      <c r="BA80" s="3"/>
+      <c r="BB80" s="3"/>
       <c r="BC80" s="6"/>
-      <c r="BD80" s="3"/>
-      <c r="BE80" s="3"/>
-      <c r="BF80" s="3"/>
-      <c r="BG80" s="3"/>
+      <c r="BD80" s="6"/>
+      <c r="BE80" s="6"/>
+      <c r="BF80" s="6"/>
+      <c r="BG80" s="6"/>
       <c r="BH80" s="3"/>
       <c r="BI80" s="3"/>
       <c r="BJ80" s="3"/>
@@ -6130,8 +6467,12 @@
       <c r="BL80" s="3"/>
       <c r="BM80" s="3"/>
       <c r="BN80" s="3"/>
-    </row>
-    <row r="81" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO80" s="3"/>
+      <c r="BP80" s="3"/>
+      <c r="BQ80" s="3"/>
+      <c r="BR80" s="3"/>
+    </row>
+    <row r="81" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -6180,15 +6521,15 @@
       <c r="AV81" s="3"/>
       <c r="AW81" s="3"/>
       <c r="AX81" s="3"/>
-      <c r="AY81" s="6"/>
-      <c r="AZ81" s="6"/>
-      <c r="BA81" s="6"/>
-      <c r="BB81" s="6"/>
+      <c r="AY81" s="3"/>
+      <c r="AZ81" s="3"/>
+      <c r="BA81" s="3"/>
+      <c r="BB81" s="3"/>
       <c r="BC81" s="6"/>
-      <c r="BD81" s="3"/>
-      <c r="BE81" s="3"/>
-      <c r="BF81" s="3"/>
-      <c r="BG81" s="3"/>
+      <c r="BD81" s="6"/>
+      <c r="BE81" s="6"/>
+      <c r="BF81" s="6"/>
+      <c r="BG81" s="6"/>
       <c r="BH81" s="3"/>
       <c r="BI81" s="3"/>
       <c r="BJ81" s="3"/>
@@ -6196,8 +6537,12 @@
       <c r="BL81" s="3"/>
       <c r="BM81" s="3"/>
       <c r="BN81" s="3"/>
-    </row>
-    <row r="82" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO81" s="3"/>
+      <c r="BP81" s="3"/>
+      <c r="BQ81" s="3"/>
+      <c r="BR81" s="3"/>
+    </row>
+    <row r="82" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -6246,15 +6591,15 @@
       <c r="AV82" s="3"/>
       <c r="AW82" s="3"/>
       <c r="AX82" s="3"/>
-      <c r="AY82" s="6"/>
-      <c r="AZ82" s="6"/>
-      <c r="BA82" s="6"/>
-      <c r="BB82" s="6"/>
+      <c r="AY82" s="3"/>
+      <c r="AZ82" s="3"/>
+      <c r="BA82" s="3"/>
+      <c r="BB82" s="3"/>
       <c r="BC82" s="6"/>
-      <c r="BD82" s="3"/>
-      <c r="BE82" s="3"/>
-      <c r="BF82" s="3"/>
-      <c r="BG82" s="3"/>
+      <c r="BD82" s="6"/>
+      <c r="BE82" s="6"/>
+      <c r="BF82" s="6"/>
+      <c r="BG82" s="6"/>
       <c r="BH82" s="3"/>
       <c r="BI82" s="3"/>
       <c r="BJ82" s="3"/>
@@ -6262,8 +6607,12 @@
       <c r="BL82" s="3"/>
       <c r="BM82" s="3"/>
       <c r="BN82" s="3"/>
-    </row>
-    <row r="83" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO82" s="3"/>
+      <c r="BP82" s="3"/>
+      <c r="BQ82" s="3"/>
+      <c r="BR82" s="3"/>
+    </row>
+    <row r="83" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -6312,15 +6661,15 @@
       <c r="AV83" s="3"/>
       <c r="AW83" s="3"/>
       <c r="AX83" s="3"/>
-      <c r="AY83" s="6"/>
-      <c r="AZ83" s="6"/>
-      <c r="BA83" s="6"/>
-      <c r="BB83" s="6"/>
+      <c r="AY83" s="3"/>
+      <c r="AZ83" s="3"/>
+      <c r="BA83" s="3"/>
+      <c r="BB83" s="3"/>
       <c r="BC83" s="6"/>
-      <c r="BD83" s="3"/>
-      <c r="BE83" s="3"/>
-      <c r="BF83" s="3"/>
-      <c r="BG83" s="3"/>
+      <c r="BD83" s="6"/>
+      <c r="BE83" s="6"/>
+      <c r="BF83" s="6"/>
+      <c r="BG83" s="6"/>
       <c r="BH83" s="3"/>
       <c r="BI83" s="3"/>
       <c r="BJ83" s="3"/>
@@ -6328,8 +6677,12 @@
       <c r="BL83" s="3"/>
       <c r="BM83" s="3"/>
       <c r="BN83" s="3"/>
-    </row>
-    <row r="84" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO83" s="3"/>
+      <c r="BP83" s="3"/>
+      <c r="BQ83" s="3"/>
+      <c r="BR83" s="3"/>
+    </row>
+    <row r="84" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -6378,15 +6731,15 @@
       <c r="AV84" s="3"/>
       <c r="AW84" s="3"/>
       <c r="AX84" s="3"/>
-      <c r="AY84" s="6"/>
-      <c r="AZ84" s="6"/>
-      <c r="BA84" s="6"/>
-      <c r="BB84" s="6"/>
+      <c r="AY84" s="3"/>
+      <c r="AZ84" s="3"/>
+      <c r="BA84" s="3"/>
+      <c r="BB84" s="3"/>
       <c r="BC84" s="6"/>
-      <c r="BD84" s="3"/>
-      <c r="BE84" s="3"/>
-      <c r="BF84" s="3"/>
-      <c r="BG84" s="3"/>
+      <c r="BD84" s="6"/>
+      <c r="BE84" s="6"/>
+      <c r="BF84" s="6"/>
+      <c r="BG84" s="6"/>
       <c r="BH84" s="3"/>
       <c r="BI84" s="3"/>
       <c r="BJ84" s="3"/>
@@ -6394,8 +6747,12 @@
       <c r="BL84" s="3"/>
       <c r="BM84" s="3"/>
       <c r="BN84" s="3"/>
-    </row>
-    <row r="85" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO84" s="3"/>
+      <c r="BP84" s="3"/>
+      <c r="BQ84" s="3"/>
+      <c r="BR84" s="3"/>
+    </row>
+    <row r="85" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -6444,15 +6801,15 @@
       <c r="AV85" s="3"/>
       <c r="AW85" s="3"/>
       <c r="AX85" s="3"/>
-      <c r="AY85" s="6"/>
-      <c r="AZ85" s="6"/>
-      <c r="BA85" s="6"/>
-      <c r="BB85" s="6"/>
+      <c r="AY85" s="3"/>
+      <c r="AZ85" s="3"/>
+      <c r="BA85" s="3"/>
+      <c r="BB85" s="3"/>
       <c r="BC85" s="6"/>
-      <c r="BD85" s="3"/>
-      <c r="BE85" s="3"/>
-      <c r="BF85" s="3"/>
-      <c r="BG85" s="3"/>
+      <c r="BD85" s="6"/>
+      <c r="BE85" s="6"/>
+      <c r="BF85" s="6"/>
+      <c r="BG85" s="6"/>
       <c r="BH85" s="3"/>
       <c r="BI85" s="3"/>
       <c r="BJ85" s="3"/>
@@ -6460,8 +6817,12 @@
       <c r="BL85" s="3"/>
       <c r="BM85" s="3"/>
       <c r="BN85" s="3"/>
-    </row>
-    <row r="86" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO85" s="3"/>
+      <c r="BP85" s="3"/>
+      <c r="BQ85" s="3"/>
+      <c r="BR85" s="3"/>
+    </row>
+    <row r="86" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -6510,15 +6871,15 @@
       <c r="AV86" s="3"/>
       <c r="AW86" s="3"/>
       <c r="AX86" s="3"/>
-      <c r="AY86" s="6"/>
-      <c r="AZ86" s="6"/>
-      <c r="BA86" s="6"/>
-      <c r="BB86" s="6"/>
+      <c r="AY86" s="3"/>
+      <c r="AZ86" s="3"/>
+      <c r="BA86" s="3"/>
+      <c r="BB86" s="3"/>
       <c r="BC86" s="6"/>
-      <c r="BD86" s="3"/>
-      <c r="BE86" s="3"/>
-      <c r="BF86" s="3"/>
-      <c r="BG86" s="3"/>
+      <c r="BD86" s="6"/>
+      <c r="BE86" s="6"/>
+      <c r="BF86" s="6"/>
+      <c r="BG86" s="6"/>
       <c r="BH86" s="3"/>
       <c r="BI86" s="3"/>
       <c r="BJ86" s="3"/>
@@ -6526,8 +6887,12 @@
       <c r="BL86" s="3"/>
       <c r="BM86" s="3"/>
       <c r="BN86" s="3"/>
-    </row>
-    <row r="87" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO86" s="3"/>
+      <c r="BP86" s="3"/>
+      <c r="BQ86" s="3"/>
+      <c r="BR86" s="3"/>
+    </row>
+    <row r="87" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -6576,15 +6941,15 @@
       <c r="AV87" s="3"/>
       <c r="AW87" s="3"/>
       <c r="AX87" s="3"/>
-      <c r="AY87" s="6"/>
-      <c r="AZ87" s="6"/>
-      <c r="BA87" s="6"/>
-      <c r="BB87" s="6"/>
+      <c r="AY87" s="3"/>
+      <c r="AZ87" s="3"/>
+      <c r="BA87" s="3"/>
+      <c r="BB87" s="3"/>
       <c r="BC87" s="6"/>
-      <c r="BD87" s="3"/>
-      <c r="BE87" s="3"/>
-      <c r="BF87" s="3"/>
-      <c r="BG87" s="3"/>
+      <c r="BD87" s="6"/>
+      <c r="BE87" s="6"/>
+      <c r="BF87" s="6"/>
+      <c r="BG87" s="6"/>
       <c r="BH87" s="3"/>
       <c r="BI87" s="3"/>
       <c r="BJ87" s="3"/>
@@ -6592,8 +6957,12 @@
       <c r="BL87" s="3"/>
       <c r="BM87" s="3"/>
       <c r="BN87" s="3"/>
-    </row>
-    <row r="88" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO87" s="3"/>
+      <c r="BP87" s="3"/>
+      <c r="BQ87" s="3"/>
+      <c r="BR87" s="3"/>
+    </row>
+    <row r="88" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -6642,15 +7011,15 @@
       <c r="AV88" s="3"/>
       <c r="AW88" s="3"/>
       <c r="AX88" s="3"/>
-      <c r="AY88" s="6"/>
-      <c r="AZ88" s="6"/>
-      <c r="BA88" s="6"/>
-      <c r="BB88" s="6"/>
+      <c r="AY88" s="3"/>
+      <c r="AZ88" s="3"/>
+      <c r="BA88" s="3"/>
+      <c r="BB88" s="3"/>
       <c r="BC88" s="6"/>
-      <c r="BD88" s="3"/>
-      <c r="BE88" s="3"/>
-      <c r="BF88" s="3"/>
-      <c r="BG88" s="3"/>
+      <c r="BD88" s="6"/>
+      <c r="BE88" s="6"/>
+      <c r="BF88" s="6"/>
+      <c r="BG88" s="6"/>
       <c r="BH88" s="3"/>
       <c r="BI88" s="3"/>
       <c r="BJ88" s="3"/>
@@ -6658,8 +7027,12 @@
       <c r="BL88" s="3"/>
       <c r="BM88" s="3"/>
       <c r="BN88" s="3"/>
-    </row>
-    <row r="89" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO88" s="3"/>
+      <c r="BP88" s="3"/>
+      <c r="BQ88" s="3"/>
+      <c r="BR88" s="3"/>
+    </row>
+    <row r="89" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -6708,15 +7081,15 @@
       <c r="AV89" s="3"/>
       <c r="AW89" s="3"/>
       <c r="AX89" s="3"/>
-      <c r="AY89" s="6"/>
-      <c r="AZ89" s="6"/>
-      <c r="BA89" s="6"/>
-      <c r="BB89" s="6"/>
+      <c r="AY89" s="3"/>
+      <c r="AZ89" s="3"/>
+      <c r="BA89" s="3"/>
+      <c r="BB89" s="3"/>
       <c r="BC89" s="6"/>
-      <c r="BD89" s="3"/>
-      <c r="BE89" s="3"/>
-      <c r="BF89" s="3"/>
-      <c r="BG89" s="3"/>
+      <c r="BD89" s="6"/>
+      <c r="BE89" s="6"/>
+      <c r="BF89" s="6"/>
+      <c r="BG89" s="6"/>
       <c r="BH89" s="3"/>
       <c r="BI89" s="3"/>
       <c r="BJ89" s="3"/>
@@ -6724,8 +7097,12 @@
       <c r="BL89" s="3"/>
       <c r="BM89" s="3"/>
       <c r="BN89" s="3"/>
-    </row>
-    <row r="90" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO89" s="3"/>
+      <c r="BP89" s="3"/>
+      <c r="BQ89" s="3"/>
+      <c r="BR89" s="3"/>
+    </row>
+    <row r="90" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -6774,15 +7151,15 @@
       <c r="AV90" s="3"/>
       <c r="AW90" s="3"/>
       <c r="AX90" s="3"/>
-      <c r="AY90" s="6"/>
-      <c r="AZ90" s="6"/>
-      <c r="BA90" s="6"/>
-      <c r="BB90" s="6"/>
+      <c r="AY90" s="3"/>
+      <c r="AZ90" s="3"/>
+      <c r="BA90" s="3"/>
+      <c r="BB90" s="3"/>
       <c r="BC90" s="6"/>
-      <c r="BD90" s="3"/>
-      <c r="BE90" s="3"/>
-      <c r="BF90" s="3"/>
-      <c r="BG90" s="3"/>
+      <c r="BD90" s="6"/>
+      <c r="BE90" s="6"/>
+      <c r="BF90" s="6"/>
+      <c r="BG90" s="6"/>
       <c r="BH90" s="3"/>
       <c r="BI90" s="3"/>
       <c r="BJ90" s="3"/>
@@ -6790,8 +7167,12 @@
       <c r="BL90" s="3"/>
       <c r="BM90" s="3"/>
       <c r="BN90" s="3"/>
-    </row>
-    <row r="91" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO90" s="3"/>
+      <c r="BP90" s="3"/>
+      <c r="BQ90" s="3"/>
+      <c r="BR90" s="3"/>
+    </row>
+    <row r="91" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -6840,15 +7221,15 @@
       <c r="AV91" s="3"/>
       <c r="AW91" s="3"/>
       <c r="AX91" s="3"/>
-      <c r="AY91" s="6"/>
-      <c r="AZ91" s="6"/>
-      <c r="BA91" s="6"/>
-      <c r="BB91" s="6"/>
+      <c r="AY91" s="3"/>
+      <c r="AZ91" s="3"/>
+      <c r="BA91" s="3"/>
+      <c r="BB91" s="3"/>
       <c r="BC91" s="6"/>
-      <c r="BD91" s="3"/>
-      <c r="BE91" s="3"/>
-      <c r="BF91" s="3"/>
-      <c r="BG91" s="3"/>
+      <c r="BD91" s="6"/>
+      <c r="BE91" s="6"/>
+      <c r="BF91" s="6"/>
+      <c r="BG91" s="6"/>
       <c r="BH91" s="3"/>
       <c r="BI91" s="3"/>
       <c r="BJ91" s="3"/>
@@ -6856,8 +7237,12 @@
       <c r="BL91" s="3"/>
       <c r="BM91" s="3"/>
       <c r="BN91" s="3"/>
-    </row>
-    <row r="92" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO91" s="3"/>
+      <c r="BP91" s="3"/>
+      <c r="BQ91" s="3"/>
+      <c r="BR91" s="3"/>
+    </row>
+    <row r="92" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -6906,15 +7291,15 @@
       <c r="AV92" s="3"/>
       <c r="AW92" s="3"/>
       <c r="AX92" s="3"/>
-      <c r="AY92" s="6"/>
-      <c r="AZ92" s="6"/>
-      <c r="BA92" s="6"/>
-      <c r="BB92" s="6"/>
+      <c r="AY92" s="3"/>
+      <c r="AZ92" s="3"/>
+      <c r="BA92" s="3"/>
+      <c r="BB92" s="3"/>
       <c r="BC92" s="6"/>
-      <c r="BD92" s="3"/>
-      <c r="BE92" s="3"/>
-      <c r="BF92" s="3"/>
-      <c r="BG92" s="3"/>
+      <c r="BD92" s="6"/>
+      <c r="BE92" s="6"/>
+      <c r="BF92" s="6"/>
+      <c r="BG92" s="6"/>
       <c r="BH92" s="3"/>
       <c r="BI92" s="3"/>
       <c r="BJ92" s="3"/>
@@ -6922,8 +7307,12 @@
       <c r="BL92" s="3"/>
       <c r="BM92" s="3"/>
       <c r="BN92" s="3"/>
-    </row>
-    <row r="93" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO92" s="3"/>
+      <c r="BP92" s="3"/>
+      <c r="BQ92" s="3"/>
+      <c r="BR92" s="3"/>
+    </row>
+    <row r="93" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -6972,15 +7361,15 @@
       <c r="AV93" s="3"/>
       <c r="AW93" s="3"/>
       <c r="AX93" s="3"/>
-      <c r="AY93" s="6"/>
-      <c r="AZ93" s="6"/>
-      <c r="BA93" s="6"/>
-      <c r="BB93" s="6"/>
+      <c r="AY93" s="3"/>
+      <c r="AZ93" s="3"/>
+      <c r="BA93" s="3"/>
+      <c r="BB93" s="3"/>
       <c r="BC93" s="6"/>
-      <c r="BD93" s="3"/>
-      <c r="BE93" s="3"/>
-      <c r="BF93" s="3"/>
-      <c r="BG93" s="3"/>
+      <c r="BD93" s="6"/>
+      <c r="BE93" s="6"/>
+      <c r="BF93" s="6"/>
+      <c r="BG93" s="6"/>
       <c r="BH93" s="3"/>
       <c r="BI93" s="3"/>
       <c r="BJ93" s="3"/>
@@ -6988,8 +7377,12 @@
       <c r="BL93" s="3"/>
       <c r="BM93" s="3"/>
       <c r="BN93" s="3"/>
-    </row>
-    <row r="94" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO93" s="3"/>
+      <c r="BP93" s="3"/>
+      <c r="BQ93" s="3"/>
+      <c r="BR93" s="3"/>
+    </row>
+    <row r="94" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -7038,15 +7431,15 @@
       <c r="AV94" s="3"/>
       <c r="AW94" s="3"/>
       <c r="AX94" s="3"/>
-      <c r="AY94" s="6"/>
-      <c r="AZ94" s="6"/>
-      <c r="BA94" s="6"/>
-      <c r="BB94" s="6"/>
+      <c r="AY94" s="3"/>
+      <c r="AZ94" s="3"/>
+      <c r="BA94" s="3"/>
+      <c r="BB94" s="3"/>
       <c r="BC94" s="6"/>
-      <c r="BD94" s="3"/>
-      <c r="BE94" s="3"/>
-      <c r="BF94" s="3"/>
-      <c r="BG94" s="3"/>
+      <c r="BD94" s="6"/>
+      <c r="BE94" s="6"/>
+      <c r="BF94" s="6"/>
+      <c r="BG94" s="6"/>
       <c r="BH94" s="3"/>
       <c r="BI94" s="3"/>
       <c r="BJ94" s="3"/>
@@ -7054,8 +7447,12 @@
       <c r="BL94" s="3"/>
       <c r="BM94" s="3"/>
       <c r="BN94" s="3"/>
-    </row>
-    <row r="95" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO94" s="3"/>
+      <c r="BP94" s="3"/>
+      <c r="BQ94" s="3"/>
+      <c r="BR94" s="3"/>
+    </row>
+    <row r="95" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -7104,15 +7501,15 @@
       <c r="AV95" s="3"/>
       <c r="AW95" s="3"/>
       <c r="AX95" s="3"/>
-      <c r="AY95" s="6"/>
-      <c r="AZ95" s="6"/>
-      <c r="BA95" s="6"/>
-      <c r="BB95" s="6"/>
+      <c r="AY95" s="3"/>
+      <c r="AZ95" s="3"/>
+      <c r="BA95" s="3"/>
+      <c r="BB95" s="3"/>
       <c r="BC95" s="6"/>
-      <c r="BD95" s="3"/>
-      <c r="BE95" s="3"/>
-      <c r="BF95" s="3"/>
-      <c r="BG95" s="3"/>
+      <c r="BD95" s="6"/>
+      <c r="BE95" s="6"/>
+      <c r="BF95" s="6"/>
+      <c r="BG95" s="6"/>
       <c r="BH95" s="3"/>
       <c r="BI95" s="3"/>
       <c r="BJ95" s="3"/>
@@ -7120,8 +7517,12 @@
       <c r="BL95" s="3"/>
       <c r="BM95" s="3"/>
       <c r="BN95" s="3"/>
-    </row>
-    <row r="96" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO95" s="3"/>
+      <c r="BP95" s="3"/>
+      <c r="BQ95" s="3"/>
+      <c r="BR95" s="3"/>
+    </row>
+    <row r="96" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -7170,15 +7571,15 @@
       <c r="AV96" s="3"/>
       <c r="AW96" s="3"/>
       <c r="AX96" s="3"/>
-      <c r="AY96" s="6"/>
-      <c r="AZ96" s="6"/>
-      <c r="BA96" s="6"/>
-      <c r="BB96" s="6"/>
+      <c r="AY96" s="3"/>
+      <c r="AZ96" s="3"/>
+      <c r="BA96" s="3"/>
+      <c r="BB96" s="3"/>
       <c r="BC96" s="6"/>
-      <c r="BD96" s="3"/>
-      <c r="BE96" s="3"/>
-      <c r="BF96" s="3"/>
-      <c r="BG96" s="3"/>
+      <c r="BD96" s="6"/>
+      <c r="BE96" s="6"/>
+      <c r="BF96" s="6"/>
+      <c r="BG96" s="6"/>
       <c r="BH96" s="3"/>
       <c r="BI96" s="3"/>
       <c r="BJ96" s="3"/>
@@ -7186,8 +7587,12 @@
       <c r="BL96" s="3"/>
       <c r="BM96" s="3"/>
       <c r="BN96" s="3"/>
-    </row>
-    <row r="97" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO96" s="3"/>
+      <c r="BP96" s="3"/>
+      <c r="BQ96" s="3"/>
+      <c r="BR96" s="3"/>
+    </row>
+    <row r="97" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -7236,15 +7641,15 @@
       <c r="AV97" s="3"/>
       <c r="AW97" s="3"/>
       <c r="AX97" s="3"/>
-      <c r="AY97" s="6"/>
-      <c r="AZ97" s="6"/>
-      <c r="BA97" s="6"/>
-      <c r="BB97" s="6"/>
+      <c r="AY97" s="3"/>
+      <c r="AZ97" s="3"/>
+      <c r="BA97" s="3"/>
+      <c r="BB97" s="3"/>
       <c r="BC97" s="6"/>
-      <c r="BD97" s="3"/>
-      <c r="BE97" s="3"/>
-      <c r="BF97" s="3"/>
-      <c r="BG97" s="3"/>
+      <c r="BD97" s="6"/>
+      <c r="BE97" s="6"/>
+      <c r="BF97" s="6"/>
+      <c r="BG97" s="6"/>
       <c r="BH97" s="3"/>
       <c r="BI97" s="3"/>
       <c r="BJ97" s="3"/>
@@ -7252,8 +7657,12 @@
       <c r="BL97" s="3"/>
       <c r="BM97" s="3"/>
       <c r="BN97" s="3"/>
-    </row>
-    <row r="98" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO97" s="3"/>
+      <c r="BP97" s="3"/>
+      <c r="BQ97" s="3"/>
+      <c r="BR97" s="3"/>
+    </row>
+    <row r="98" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -7302,15 +7711,15 @@
       <c r="AV98" s="3"/>
       <c r="AW98" s="3"/>
       <c r="AX98" s="3"/>
-      <c r="AY98" s="6"/>
-      <c r="AZ98" s="6"/>
-      <c r="BA98" s="6"/>
-      <c r="BB98" s="6"/>
+      <c r="AY98" s="3"/>
+      <c r="AZ98" s="3"/>
+      <c r="BA98" s="3"/>
+      <c r="BB98" s="3"/>
       <c r="BC98" s="6"/>
-      <c r="BD98" s="3"/>
-      <c r="BE98" s="3"/>
-      <c r="BF98" s="3"/>
-      <c r="BG98" s="3"/>
+      <c r="BD98" s="6"/>
+      <c r="BE98" s="6"/>
+      <c r="BF98" s="6"/>
+      <c r="BG98" s="6"/>
       <c r="BH98" s="3"/>
       <c r="BI98" s="3"/>
       <c r="BJ98" s="3"/>
@@ -7318,8 +7727,12 @@
       <c r="BL98" s="3"/>
       <c r="BM98" s="3"/>
       <c r="BN98" s="3"/>
-    </row>
-    <row r="99" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO98" s="3"/>
+      <c r="BP98" s="3"/>
+      <c r="BQ98" s="3"/>
+      <c r="BR98" s="3"/>
+    </row>
+    <row r="99" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -7368,15 +7781,15 @@
       <c r="AV99" s="3"/>
       <c r="AW99" s="3"/>
       <c r="AX99" s="3"/>
-      <c r="AY99" s="6"/>
-      <c r="AZ99" s="6"/>
-      <c r="BA99" s="6"/>
-      <c r="BB99" s="6"/>
+      <c r="AY99" s="3"/>
+      <c r="AZ99" s="3"/>
+      <c r="BA99" s="3"/>
+      <c r="BB99" s="3"/>
       <c r="BC99" s="6"/>
-      <c r="BD99" s="3"/>
-      <c r="BE99" s="3"/>
-      <c r="BF99" s="3"/>
-      <c r="BG99" s="3"/>
+      <c r="BD99" s="6"/>
+      <c r="BE99" s="6"/>
+      <c r="BF99" s="6"/>
+      <c r="BG99" s="6"/>
       <c r="BH99" s="3"/>
       <c r="BI99" s="3"/>
       <c r="BJ99" s="3"/>
@@ -7384,8 +7797,12 @@
       <c r="BL99" s="3"/>
       <c r="BM99" s="3"/>
       <c r="BN99" s="3"/>
-    </row>
-    <row r="100" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO99" s="3"/>
+      <c r="BP99" s="3"/>
+      <c r="BQ99" s="3"/>
+      <c r="BR99" s="3"/>
+    </row>
+    <row r="100" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -7434,15 +7851,15 @@
       <c r="AV100" s="3"/>
       <c r="AW100" s="3"/>
       <c r="AX100" s="3"/>
-      <c r="AY100" s="6"/>
-      <c r="AZ100" s="6"/>
-      <c r="BA100" s="6"/>
-      <c r="BB100" s="6"/>
+      <c r="AY100" s="3"/>
+      <c r="AZ100" s="3"/>
+      <c r="BA100" s="3"/>
+      <c r="BB100" s="3"/>
       <c r="BC100" s="6"/>
-      <c r="BD100" s="3"/>
-      <c r="BE100" s="3"/>
-      <c r="BF100" s="3"/>
-      <c r="BG100" s="3"/>
+      <c r="BD100" s="6"/>
+      <c r="BE100" s="6"/>
+      <c r="BF100" s="6"/>
+      <c r="BG100" s="6"/>
       <c r="BH100" s="3"/>
       <c r="BI100" s="3"/>
       <c r="BJ100" s="3"/>
@@ -7450,8 +7867,12 @@
       <c r="BL100" s="3"/>
       <c r="BM100" s="3"/>
       <c r="BN100" s="3"/>
-    </row>
-    <row r="101" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO100" s="3"/>
+      <c r="BP100" s="3"/>
+      <c r="BQ100" s="3"/>
+      <c r="BR100" s="3"/>
+    </row>
+    <row r="101" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -7500,15 +7921,15 @@
       <c r="AV101" s="3"/>
       <c r="AW101" s="3"/>
       <c r="AX101" s="3"/>
-      <c r="AY101" s="6"/>
-      <c r="AZ101" s="6"/>
-      <c r="BA101" s="6"/>
-      <c r="BB101" s="6"/>
+      <c r="AY101" s="3"/>
+      <c r="AZ101" s="3"/>
+      <c r="BA101" s="3"/>
+      <c r="BB101" s="3"/>
       <c r="BC101" s="6"/>
-      <c r="BD101" s="3"/>
-      <c r="BE101" s="3"/>
-      <c r="BF101" s="3"/>
-      <c r="BG101" s="3"/>
+      <c r="BD101" s="6"/>
+      <c r="BE101" s="6"/>
+      <c r="BF101" s="6"/>
+      <c r="BG101" s="6"/>
       <c r="BH101" s="3"/>
       <c r="BI101" s="3"/>
       <c r="BJ101" s="3"/>
@@ -7516,8 +7937,12 @@
       <c r="BL101" s="3"/>
       <c r="BM101" s="3"/>
       <c r="BN101" s="3"/>
-    </row>
-    <row r="102" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO101" s="3"/>
+      <c r="BP101" s="3"/>
+      <c r="BQ101" s="3"/>
+      <c r="BR101" s="3"/>
+    </row>
+    <row r="102" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -7566,15 +7991,15 @@
       <c r="AV102" s="3"/>
       <c r="AW102" s="3"/>
       <c r="AX102" s="3"/>
-      <c r="AY102" s="6"/>
-      <c r="AZ102" s="6"/>
-      <c r="BA102" s="6"/>
-      <c r="BB102" s="6"/>
+      <c r="AY102" s="3"/>
+      <c r="AZ102" s="3"/>
+      <c r="BA102" s="3"/>
+      <c r="BB102" s="3"/>
       <c r="BC102" s="6"/>
-      <c r="BD102" s="3"/>
-      <c r="BE102" s="3"/>
-      <c r="BF102" s="3"/>
-      <c r="BG102" s="3"/>
+      <c r="BD102" s="6"/>
+      <c r="BE102" s="6"/>
+      <c r="BF102" s="6"/>
+      <c r="BG102" s="6"/>
       <c r="BH102" s="3"/>
       <c r="BI102" s="3"/>
       <c r="BJ102" s="3"/>
@@ -7582,8 +8007,12 @@
       <c r="BL102" s="3"/>
       <c r="BM102" s="3"/>
       <c r="BN102" s="3"/>
-    </row>
-    <row r="103" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO102" s="3"/>
+      <c r="BP102" s="3"/>
+      <c r="BQ102" s="3"/>
+      <c r="BR102" s="3"/>
+    </row>
+    <row r="103" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -7632,15 +8061,15 @@
       <c r="AV103" s="3"/>
       <c r="AW103" s="3"/>
       <c r="AX103" s="3"/>
-      <c r="AY103" s="6"/>
-      <c r="AZ103" s="6"/>
-      <c r="BA103" s="6"/>
-      <c r="BB103" s="6"/>
+      <c r="AY103" s="3"/>
+      <c r="AZ103" s="3"/>
+      <c r="BA103" s="3"/>
+      <c r="BB103" s="3"/>
       <c r="BC103" s="6"/>
-      <c r="BD103" s="3"/>
-      <c r="BE103" s="3"/>
-      <c r="BF103" s="3"/>
-      <c r="BG103" s="3"/>
+      <c r="BD103" s="6"/>
+      <c r="BE103" s="6"/>
+      <c r="BF103" s="6"/>
+      <c r="BG103" s="6"/>
       <c r="BH103" s="3"/>
       <c r="BI103" s="3"/>
       <c r="BJ103" s="3"/>
@@ -7648,8 +8077,12 @@
       <c r="BL103" s="3"/>
       <c r="BM103" s="3"/>
       <c r="BN103" s="3"/>
-    </row>
-    <row r="104" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO103" s="3"/>
+      <c r="BP103" s="3"/>
+      <c r="BQ103" s="3"/>
+      <c r="BR103" s="3"/>
+    </row>
+    <row r="104" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -7698,15 +8131,15 @@
       <c r="AV104" s="3"/>
       <c r="AW104" s="3"/>
       <c r="AX104" s="3"/>
-      <c r="AY104" s="6"/>
-      <c r="AZ104" s="6"/>
-      <c r="BA104" s="6"/>
-      <c r="BB104" s="6"/>
+      <c r="AY104" s="3"/>
+      <c r="AZ104" s="3"/>
+      <c r="BA104" s="3"/>
+      <c r="BB104" s="3"/>
       <c r="BC104" s="6"/>
-      <c r="BD104" s="3"/>
-      <c r="BE104" s="3"/>
-      <c r="BF104" s="3"/>
-      <c r="BG104" s="3"/>
+      <c r="BD104" s="6"/>
+      <c r="BE104" s="6"/>
+      <c r="BF104" s="6"/>
+      <c r="BG104" s="6"/>
       <c r="BH104" s="3"/>
       <c r="BI104" s="3"/>
       <c r="BJ104" s="3"/>
@@ -7714,8 +8147,12 @@
       <c r="BL104" s="3"/>
       <c r="BM104" s="3"/>
       <c r="BN104" s="3"/>
-    </row>
-    <row r="105" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO104" s="3"/>
+      <c r="BP104" s="3"/>
+      <c r="BQ104" s="3"/>
+      <c r="BR104" s="3"/>
+    </row>
+    <row r="105" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -7764,15 +8201,15 @@
       <c r="AV105" s="3"/>
       <c r="AW105" s="3"/>
       <c r="AX105" s="3"/>
-      <c r="AY105" s="6"/>
-      <c r="AZ105" s="6"/>
-      <c r="BA105" s="6"/>
-      <c r="BB105" s="6"/>
+      <c r="AY105" s="3"/>
+      <c r="AZ105" s="3"/>
+      <c r="BA105" s="3"/>
+      <c r="BB105" s="3"/>
       <c r="BC105" s="6"/>
-      <c r="BD105" s="3"/>
-      <c r="BE105" s="3"/>
-      <c r="BF105" s="3"/>
-      <c r="BG105" s="3"/>
+      <c r="BD105" s="6"/>
+      <c r="BE105" s="6"/>
+      <c r="BF105" s="6"/>
+      <c r="BG105" s="6"/>
       <c r="BH105" s="3"/>
       <c r="BI105" s="3"/>
       <c r="BJ105" s="3"/>
@@ -7780,8 +8217,12 @@
       <c r="BL105" s="3"/>
       <c r="BM105" s="3"/>
       <c r="BN105" s="3"/>
-    </row>
-    <row r="106" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO105" s="3"/>
+      <c r="BP105" s="3"/>
+      <c r="BQ105" s="3"/>
+      <c r="BR105" s="3"/>
+    </row>
+    <row r="106" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -7830,15 +8271,15 @@
       <c r="AV106" s="3"/>
       <c r="AW106" s="3"/>
       <c r="AX106" s="3"/>
-      <c r="AY106" s="6"/>
-      <c r="AZ106" s="6"/>
-      <c r="BA106" s="6"/>
-      <c r="BB106" s="6"/>
+      <c r="AY106" s="3"/>
+      <c r="AZ106" s="3"/>
+      <c r="BA106" s="3"/>
+      <c r="BB106" s="3"/>
       <c r="BC106" s="6"/>
-      <c r="BD106" s="3"/>
-      <c r="BE106" s="3"/>
-      <c r="BF106" s="3"/>
-      <c r="BG106" s="3"/>
+      <c r="BD106" s="6"/>
+      <c r="BE106" s="6"/>
+      <c r="BF106" s="6"/>
+      <c r="BG106" s="6"/>
       <c r="BH106" s="3"/>
       <c r="BI106" s="3"/>
       <c r="BJ106" s="3"/>
@@ -7846,8 +8287,12 @@
       <c r="BL106" s="3"/>
       <c r="BM106" s="3"/>
       <c r="BN106" s="3"/>
-    </row>
-    <row r="107" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO106" s="3"/>
+      <c r="BP106" s="3"/>
+      <c r="BQ106" s="3"/>
+      <c r="BR106" s="3"/>
+    </row>
+    <row r="107" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -7896,15 +8341,15 @@
       <c r="AV107" s="3"/>
       <c r="AW107" s="3"/>
       <c r="AX107" s="3"/>
-      <c r="AY107" s="6"/>
-      <c r="AZ107" s="6"/>
-      <c r="BA107" s="6"/>
-      <c r="BB107" s="6"/>
+      <c r="AY107" s="3"/>
+      <c r="AZ107" s="3"/>
+      <c r="BA107" s="3"/>
+      <c r="BB107" s="3"/>
       <c r="BC107" s="6"/>
-      <c r="BD107" s="3"/>
-      <c r="BE107" s="3"/>
-      <c r="BF107" s="3"/>
-      <c r="BG107" s="3"/>
+      <c r="BD107" s="6"/>
+      <c r="BE107" s="6"/>
+      <c r="BF107" s="6"/>
+      <c r="BG107" s="6"/>
       <c r="BH107" s="3"/>
       <c r="BI107" s="3"/>
       <c r="BJ107" s="3"/>
@@ -7912,8 +8357,12 @@
       <c r="BL107" s="3"/>
       <c r="BM107" s="3"/>
       <c r="BN107" s="3"/>
-    </row>
-    <row r="108" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO107" s="3"/>
+      <c r="BP107" s="3"/>
+      <c r="BQ107" s="3"/>
+      <c r="BR107" s="3"/>
+    </row>
+    <row r="108" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -7962,15 +8411,15 @@
       <c r="AV108" s="3"/>
       <c r="AW108" s="3"/>
       <c r="AX108" s="3"/>
-      <c r="AY108" s="6"/>
-      <c r="AZ108" s="6"/>
-      <c r="BA108" s="6"/>
-      <c r="BB108" s="6"/>
+      <c r="AY108" s="3"/>
+      <c r="AZ108" s="3"/>
+      <c r="BA108" s="3"/>
+      <c r="BB108" s="3"/>
       <c r="BC108" s="6"/>
-      <c r="BD108" s="3"/>
-      <c r="BE108" s="3"/>
-      <c r="BF108" s="3"/>
-      <c r="BG108" s="3"/>
+      <c r="BD108" s="6"/>
+      <c r="BE108" s="6"/>
+      <c r="BF108" s="6"/>
+      <c r="BG108" s="6"/>
       <c r="BH108" s="3"/>
       <c r="BI108" s="3"/>
       <c r="BJ108" s="3"/>
@@ -7978,8 +8427,12 @@
       <c r="BL108" s="3"/>
       <c r="BM108" s="3"/>
       <c r="BN108" s="3"/>
-    </row>
-    <row r="109" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO108" s="3"/>
+      <c r="BP108" s="3"/>
+      <c r="BQ108" s="3"/>
+      <c r="BR108" s="3"/>
+    </row>
+    <row r="109" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -8028,15 +8481,15 @@
       <c r="AV109" s="3"/>
       <c r="AW109" s="3"/>
       <c r="AX109" s="3"/>
-      <c r="AY109" s="6"/>
-      <c r="AZ109" s="6"/>
-      <c r="BA109" s="6"/>
-      <c r="BB109" s="6"/>
+      <c r="AY109" s="3"/>
+      <c r="AZ109" s="3"/>
+      <c r="BA109" s="3"/>
+      <c r="BB109" s="3"/>
       <c r="BC109" s="6"/>
-      <c r="BD109" s="3"/>
-      <c r="BE109" s="3"/>
-      <c r="BF109" s="3"/>
-      <c r="BG109" s="3"/>
+      <c r="BD109" s="6"/>
+      <c r="BE109" s="6"/>
+      <c r="BF109" s="6"/>
+      <c r="BG109" s="6"/>
       <c r="BH109" s="3"/>
       <c r="BI109" s="3"/>
       <c r="BJ109" s="3"/>
@@ -8044,8 +8497,12 @@
       <c r="BL109" s="3"/>
       <c r="BM109" s="3"/>
       <c r="BN109" s="3"/>
-    </row>
-    <row r="110" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO109" s="3"/>
+      <c r="BP109" s="3"/>
+      <c r="BQ109" s="3"/>
+      <c r="BR109" s="3"/>
+    </row>
+    <row r="110" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -8094,15 +8551,15 @@
       <c r="AV110" s="3"/>
       <c r="AW110" s="3"/>
       <c r="AX110" s="3"/>
-      <c r="AY110" s="6"/>
-      <c r="AZ110" s="6"/>
-      <c r="BA110" s="6"/>
-      <c r="BB110" s="6"/>
+      <c r="AY110" s="3"/>
+      <c r="AZ110" s="3"/>
+      <c r="BA110" s="3"/>
+      <c r="BB110" s="3"/>
       <c r="BC110" s="6"/>
-      <c r="BD110" s="3"/>
-      <c r="BE110" s="3"/>
-      <c r="BF110" s="3"/>
-      <c r="BG110" s="3"/>
+      <c r="BD110" s="6"/>
+      <c r="BE110" s="6"/>
+      <c r="BF110" s="6"/>
+      <c r="BG110" s="6"/>
       <c r="BH110" s="3"/>
       <c r="BI110" s="3"/>
       <c r="BJ110" s="3"/>
@@ -8110,8 +8567,12 @@
       <c r="BL110" s="3"/>
       <c r="BM110" s="3"/>
       <c r="BN110" s="3"/>
-    </row>
-    <row r="111" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO110" s="3"/>
+      <c r="BP110" s="3"/>
+      <c r="BQ110" s="3"/>
+      <c r="BR110" s="3"/>
+    </row>
+    <row r="111" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -8160,15 +8621,15 @@
       <c r="AV111" s="3"/>
       <c r="AW111" s="3"/>
       <c r="AX111" s="3"/>
-      <c r="AY111" s="6"/>
-      <c r="AZ111" s="6"/>
-      <c r="BA111" s="6"/>
-      <c r="BB111" s="6"/>
+      <c r="AY111" s="3"/>
+      <c r="AZ111" s="3"/>
+      <c r="BA111" s="3"/>
+      <c r="BB111" s="3"/>
       <c r="BC111" s="6"/>
-      <c r="BD111" s="3"/>
-      <c r="BE111" s="3"/>
-      <c r="BF111" s="3"/>
-      <c r="BG111" s="3"/>
+      <c r="BD111" s="6"/>
+      <c r="BE111" s="6"/>
+      <c r="BF111" s="6"/>
+      <c r="BG111" s="6"/>
       <c r="BH111" s="3"/>
       <c r="BI111" s="3"/>
       <c r="BJ111" s="3"/>
@@ -8176,8 +8637,12 @@
       <c r="BL111" s="3"/>
       <c r="BM111" s="3"/>
       <c r="BN111" s="3"/>
-    </row>
-    <row r="112" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO111" s="3"/>
+      <c r="BP111" s="3"/>
+      <c r="BQ111" s="3"/>
+      <c r="BR111" s="3"/>
+    </row>
+    <row r="112" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -8226,15 +8691,15 @@
       <c r="AV112" s="3"/>
       <c r="AW112" s="3"/>
       <c r="AX112" s="3"/>
-      <c r="AY112" s="6"/>
-      <c r="AZ112" s="6"/>
-      <c r="BA112" s="6"/>
-      <c r="BB112" s="6"/>
+      <c r="AY112" s="3"/>
+      <c r="AZ112" s="3"/>
+      <c r="BA112" s="3"/>
+      <c r="BB112" s="3"/>
       <c r="BC112" s="6"/>
-      <c r="BD112" s="3"/>
-      <c r="BE112" s="3"/>
-      <c r="BF112" s="3"/>
-      <c r="BG112" s="3"/>
+      <c r="BD112" s="6"/>
+      <c r="BE112" s="6"/>
+      <c r="BF112" s="6"/>
+      <c r="BG112" s="6"/>
       <c r="BH112" s="3"/>
       <c r="BI112" s="3"/>
       <c r="BJ112" s="3"/>
@@ -8242,8 +8707,12 @@
       <c r="BL112" s="3"/>
       <c r="BM112" s="3"/>
       <c r="BN112" s="3"/>
-    </row>
-    <row r="113" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO112" s="3"/>
+      <c r="BP112" s="3"/>
+      <c r="BQ112" s="3"/>
+      <c r="BR112" s="3"/>
+    </row>
+    <row r="113" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -8292,15 +8761,15 @@
       <c r="AV113" s="3"/>
       <c r="AW113" s="3"/>
       <c r="AX113" s="3"/>
-      <c r="AY113" s="6"/>
-      <c r="AZ113" s="6"/>
-      <c r="BA113" s="6"/>
-      <c r="BB113" s="6"/>
+      <c r="AY113" s="3"/>
+      <c r="AZ113" s="3"/>
+      <c r="BA113" s="3"/>
+      <c r="BB113" s="3"/>
       <c r="BC113" s="6"/>
-      <c r="BD113" s="3"/>
-      <c r="BE113" s="3"/>
-      <c r="BF113" s="3"/>
-      <c r="BG113" s="3"/>
+      <c r="BD113" s="6"/>
+      <c r="BE113" s="6"/>
+      <c r="BF113" s="6"/>
+      <c r="BG113" s="6"/>
       <c r="BH113" s="3"/>
       <c r="BI113" s="3"/>
       <c r="BJ113" s="3"/>
@@ -8308,8 +8777,12 @@
       <c r="BL113" s="3"/>
       <c r="BM113" s="3"/>
       <c r="BN113" s="3"/>
-    </row>
-    <row r="114" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO113" s="3"/>
+      <c r="BP113" s="3"/>
+      <c r="BQ113" s="3"/>
+      <c r="BR113" s="3"/>
+    </row>
+    <row r="114" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -8358,15 +8831,15 @@
       <c r="AV114" s="3"/>
       <c r="AW114" s="3"/>
       <c r="AX114" s="3"/>
-      <c r="AY114" s="6"/>
-      <c r="AZ114" s="6"/>
-      <c r="BA114" s="6"/>
-      <c r="BB114" s="6"/>
+      <c r="AY114" s="3"/>
+      <c r="AZ114" s="3"/>
+      <c r="BA114" s="3"/>
+      <c r="BB114" s="3"/>
       <c r="BC114" s="6"/>
-      <c r="BD114" s="3"/>
-      <c r="BE114" s="3"/>
-      <c r="BF114" s="3"/>
-      <c r="BG114" s="3"/>
+      <c r="BD114" s="6"/>
+      <c r="BE114" s="6"/>
+      <c r="BF114" s="6"/>
+      <c r="BG114" s="6"/>
       <c r="BH114" s="3"/>
       <c r="BI114" s="3"/>
       <c r="BJ114" s="3"/>
@@ -8374,8 +8847,12 @@
       <c r="BL114" s="3"/>
       <c r="BM114" s="3"/>
       <c r="BN114" s="3"/>
-    </row>
-    <row r="115" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO114" s="3"/>
+      <c r="BP114" s="3"/>
+      <c r="BQ114" s="3"/>
+      <c r="BR114" s="3"/>
+    </row>
+    <row r="115" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -8424,15 +8901,15 @@
       <c r="AV115" s="3"/>
       <c r="AW115" s="3"/>
       <c r="AX115" s="3"/>
-      <c r="AY115" s="6"/>
-      <c r="AZ115" s="6"/>
-      <c r="BA115" s="6"/>
-      <c r="BB115" s="6"/>
+      <c r="AY115" s="3"/>
+      <c r="AZ115" s="3"/>
+      <c r="BA115" s="3"/>
+      <c r="BB115" s="3"/>
       <c r="BC115" s="6"/>
-      <c r="BD115" s="3"/>
-      <c r="BE115" s="3"/>
-      <c r="BF115" s="3"/>
-      <c r="BG115" s="3"/>
+      <c r="BD115" s="6"/>
+      <c r="BE115" s="6"/>
+      <c r="BF115" s="6"/>
+      <c r="BG115" s="6"/>
       <c r="BH115" s="3"/>
       <c r="BI115" s="3"/>
       <c r="BJ115" s="3"/>
@@ -8440,8 +8917,12 @@
       <c r="BL115" s="3"/>
       <c r="BM115" s="3"/>
       <c r="BN115" s="3"/>
-    </row>
-    <row r="116" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO115" s="3"/>
+      <c r="BP115" s="3"/>
+      <c r="BQ115" s="3"/>
+      <c r="BR115" s="3"/>
+    </row>
+    <row r="116" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -8490,15 +8971,15 @@
       <c r="AV116" s="3"/>
       <c r="AW116" s="3"/>
       <c r="AX116" s="3"/>
-      <c r="AY116" s="6"/>
-      <c r="AZ116" s="6"/>
-      <c r="BA116" s="6"/>
-      <c r="BB116" s="6"/>
+      <c r="AY116" s="3"/>
+      <c r="AZ116" s="3"/>
+      <c r="BA116" s="3"/>
+      <c r="BB116" s="3"/>
       <c r="BC116" s="6"/>
-      <c r="BD116" s="3"/>
-      <c r="BE116" s="3"/>
-      <c r="BF116" s="3"/>
-      <c r="BG116" s="3"/>
+      <c r="BD116" s="6"/>
+      <c r="BE116" s="6"/>
+      <c r="BF116" s="6"/>
+      <c r="BG116" s="6"/>
       <c r="BH116" s="3"/>
       <c r="BI116" s="3"/>
       <c r="BJ116" s="3"/>
@@ -8506,8 +8987,12 @@
       <c r="BL116" s="3"/>
       <c r="BM116" s="3"/>
       <c r="BN116" s="3"/>
-    </row>
-    <row r="117" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO116" s="3"/>
+      <c r="BP116" s="3"/>
+      <c r="BQ116" s="3"/>
+      <c r="BR116" s="3"/>
+    </row>
+    <row r="117" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -8556,15 +9041,15 @@
       <c r="AV117" s="3"/>
       <c r="AW117" s="3"/>
       <c r="AX117" s="3"/>
-      <c r="AY117" s="6"/>
-      <c r="AZ117" s="6"/>
-      <c r="BA117" s="6"/>
-      <c r="BB117" s="6"/>
+      <c r="AY117" s="3"/>
+      <c r="AZ117" s="3"/>
+      <c r="BA117" s="3"/>
+      <c r="BB117" s="3"/>
       <c r="BC117" s="6"/>
-      <c r="BD117" s="3"/>
-      <c r="BE117" s="3"/>
-      <c r="BF117" s="3"/>
-      <c r="BG117" s="3"/>
+      <c r="BD117" s="6"/>
+      <c r="BE117" s="6"/>
+      <c r="BF117" s="6"/>
+      <c r="BG117" s="6"/>
       <c r="BH117" s="3"/>
       <c r="BI117" s="3"/>
       <c r="BJ117" s="3"/>
@@ -8572,8 +9057,12 @@
       <c r="BL117" s="3"/>
       <c r="BM117" s="3"/>
       <c r="BN117" s="3"/>
-    </row>
-    <row r="118" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO117" s="3"/>
+      <c r="BP117" s="3"/>
+      <c r="BQ117" s="3"/>
+      <c r="BR117" s="3"/>
+    </row>
+    <row r="118" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -8622,15 +9111,15 @@
       <c r="AV118" s="3"/>
       <c r="AW118" s="3"/>
       <c r="AX118" s="3"/>
-      <c r="AY118" s="6"/>
-      <c r="AZ118" s="6"/>
-      <c r="BA118" s="6"/>
-      <c r="BB118" s="6"/>
+      <c r="AY118" s="3"/>
+      <c r="AZ118" s="3"/>
+      <c r="BA118" s="3"/>
+      <c r="BB118" s="3"/>
       <c r="BC118" s="6"/>
-      <c r="BD118" s="3"/>
-      <c r="BE118" s="3"/>
-      <c r="BF118" s="3"/>
-      <c r="BG118" s="3"/>
+      <c r="BD118" s="6"/>
+      <c r="BE118" s="6"/>
+      <c r="BF118" s="6"/>
+      <c r="BG118" s="6"/>
       <c r="BH118" s="3"/>
       <c r="BI118" s="3"/>
       <c r="BJ118" s="3"/>
@@ -8638,8 +9127,12 @@
       <c r="BL118" s="3"/>
       <c r="BM118" s="3"/>
       <c r="BN118" s="3"/>
-    </row>
-    <row r="119" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO118" s="3"/>
+      <c r="BP118" s="3"/>
+      <c r="BQ118" s="3"/>
+      <c r="BR118" s="3"/>
+    </row>
+    <row r="119" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -8688,15 +9181,15 @@
       <c r="AV119" s="3"/>
       <c r="AW119" s="3"/>
       <c r="AX119" s="3"/>
-      <c r="AY119" s="6"/>
-      <c r="AZ119" s="6"/>
-      <c r="BA119" s="6"/>
-      <c r="BB119" s="6"/>
+      <c r="AY119" s="3"/>
+      <c r="AZ119" s="3"/>
+      <c r="BA119" s="3"/>
+      <c r="BB119" s="3"/>
       <c r="BC119" s="6"/>
-      <c r="BD119" s="3"/>
-      <c r="BE119" s="3"/>
-      <c r="BF119" s="3"/>
-      <c r="BG119" s="3"/>
+      <c r="BD119" s="6"/>
+      <c r="BE119" s="6"/>
+      <c r="BF119" s="6"/>
+      <c r="BG119" s="6"/>
       <c r="BH119" s="3"/>
       <c r="BI119" s="3"/>
       <c r="BJ119" s="3"/>
@@ -8704,8 +9197,12 @@
       <c r="BL119" s="3"/>
       <c r="BM119" s="3"/>
       <c r="BN119" s="3"/>
-    </row>
-    <row r="120" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO119" s="3"/>
+      <c r="BP119" s="3"/>
+      <c r="BQ119" s="3"/>
+      <c r="BR119" s="3"/>
+    </row>
+    <row r="120" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -8754,15 +9251,15 @@
       <c r="AV120" s="3"/>
       <c r="AW120" s="3"/>
       <c r="AX120" s="3"/>
-      <c r="AY120" s="6"/>
-      <c r="AZ120" s="6"/>
-      <c r="BA120" s="6"/>
-      <c r="BB120" s="6"/>
+      <c r="AY120" s="3"/>
+      <c r="AZ120" s="3"/>
+      <c r="BA120" s="3"/>
+      <c r="BB120" s="3"/>
       <c r="BC120" s="6"/>
-      <c r="BD120" s="3"/>
-      <c r="BE120" s="3"/>
-      <c r="BF120" s="3"/>
-      <c r="BG120" s="3"/>
+      <c r="BD120" s="6"/>
+      <c r="BE120" s="6"/>
+      <c r="BF120" s="6"/>
+      <c r="BG120" s="6"/>
       <c r="BH120" s="3"/>
       <c r="BI120" s="3"/>
       <c r="BJ120" s="3"/>
@@ -8770,8 +9267,12 @@
       <c r="BL120" s="3"/>
       <c r="BM120" s="3"/>
       <c r="BN120" s="3"/>
-    </row>
-    <row r="121" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO120" s="3"/>
+      <c r="BP120" s="3"/>
+      <c r="BQ120" s="3"/>
+      <c r="BR120" s="3"/>
+    </row>
+    <row r="121" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -8820,15 +9321,15 @@
       <c r="AV121" s="3"/>
       <c r="AW121" s="3"/>
       <c r="AX121" s="3"/>
-      <c r="AY121" s="6"/>
-      <c r="AZ121" s="6"/>
-      <c r="BA121" s="6"/>
-      <c r="BB121" s="6"/>
+      <c r="AY121" s="3"/>
+      <c r="AZ121" s="3"/>
+      <c r="BA121" s="3"/>
+      <c r="BB121" s="3"/>
       <c r="BC121" s="6"/>
-      <c r="BD121" s="3"/>
-      <c r="BE121" s="3"/>
-      <c r="BF121" s="3"/>
-      <c r="BG121" s="3"/>
+      <c r="BD121" s="6"/>
+      <c r="BE121" s="6"/>
+      <c r="BF121" s="6"/>
+      <c r="BG121" s="6"/>
       <c r="BH121" s="3"/>
       <c r="BI121" s="3"/>
       <c r="BJ121" s="3"/>
@@ -8836,8 +9337,12 @@
       <c r="BL121" s="3"/>
       <c r="BM121" s="3"/>
       <c r="BN121" s="3"/>
-    </row>
-    <row r="122" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO121" s="3"/>
+      <c r="BP121" s="3"/>
+      <c r="BQ121" s="3"/>
+      <c r="BR121" s="3"/>
+    </row>
+    <row r="122" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -8886,15 +9391,15 @@
       <c r="AV122" s="3"/>
       <c r="AW122" s="3"/>
       <c r="AX122" s="3"/>
-      <c r="AY122" s="6"/>
-      <c r="AZ122" s="6"/>
-      <c r="BA122" s="6"/>
-      <c r="BB122" s="6"/>
+      <c r="AY122" s="3"/>
+      <c r="AZ122" s="3"/>
+      <c r="BA122" s="3"/>
+      <c r="BB122" s="3"/>
       <c r="BC122" s="6"/>
-      <c r="BD122" s="3"/>
-      <c r="BE122" s="3"/>
-      <c r="BF122" s="3"/>
-      <c r="BG122" s="3"/>
+      <c r="BD122" s="6"/>
+      <c r="BE122" s="6"/>
+      <c r="BF122" s="6"/>
+      <c r="BG122" s="6"/>
       <c r="BH122" s="3"/>
       <c r="BI122" s="3"/>
       <c r="BJ122" s="3"/>
@@ -8902,8 +9407,12 @@
       <c r="BL122" s="3"/>
       <c r="BM122" s="3"/>
       <c r="BN122" s="3"/>
-    </row>
-    <row r="123" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO122" s="3"/>
+      <c r="BP122" s="3"/>
+      <c r="BQ122" s="3"/>
+      <c r="BR122" s="3"/>
+    </row>
+    <row r="123" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -8952,15 +9461,15 @@
       <c r="AV123" s="3"/>
       <c r="AW123" s="3"/>
       <c r="AX123" s="3"/>
-      <c r="AY123" s="6"/>
-      <c r="AZ123" s="6"/>
-      <c r="BA123" s="6"/>
-      <c r="BB123" s="6"/>
+      <c r="AY123" s="3"/>
+      <c r="AZ123" s="3"/>
+      <c r="BA123" s="3"/>
+      <c r="BB123" s="3"/>
       <c r="BC123" s="6"/>
-      <c r="BD123" s="3"/>
-      <c r="BE123" s="3"/>
-      <c r="BF123" s="3"/>
-      <c r="BG123" s="3"/>
+      <c r="BD123" s="6"/>
+      <c r="BE123" s="6"/>
+      <c r="BF123" s="6"/>
+      <c r="BG123" s="6"/>
       <c r="BH123" s="3"/>
       <c r="BI123" s="3"/>
       <c r="BJ123" s="3"/>
@@ -8968,8 +9477,12 @@
       <c r="BL123" s="3"/>
       <c r="BM123" s="3"/>
       <c r="BN123" s="3"/>
-    </row>
-    <row r="124" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO123" s="3"/>
+      <c r="BP123" s="3"/>
+      <c r="BQ123" s="3"/>
+      <c r="BR123" s="3"/>
+    </row>
+    <row r="124" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -9018,15 +9531,15 @@
       <c r="AV124" s="3"/>
       <c r="AW124" s="3"/>
       <c r="AX124" s="3"/>
-      <c r="AY124" s="6"/>
-      <c r="AZ124" s="6"/>
-      <c r="BA124" s="6"/>
-      <c r="BB124" s="6"/>
+      <c r="AY124" s="3"/>
+      <c r="AZ124" s="3"/>
+      <c r="BA124" s="3"/>
+      <c r="BB124" s="3"/>
       <c r="BC124" s="6"/>
-      <c r="BD124" s="3"/>
-      <c r="BE124" s="3"/>
-      <c r="BF124" s="3"/>
-      <c r="BG124" s="3"/>
+      <c r="BD124" s="6"/>
+      <c r="BE124" s="6"/>
+      <c r="BF124" s="6"/>
+      <c r="BG124" s="6"/>
       <c r="BH124" s="3"/>
       <c r="BI124" s="3"/>
       <c r="BJ124" s="3"/>
@@ -9034,8 +9547,12 @@
       <c r="BL124" s="3"/>
       <c r="BM124" s="3"/>
       <c r="BN124" s="3"/>
-    </row>
-    <row r="125" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO124" s="3"/>
+      <c r="BP124" s="3"/>
+      <c r="BQ124" s="3"/>
+      <c r="BR124" s="3"/>
+    </row>
+    <row r="125" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -9084,15 +9601,15 @@
       <c r="AV125" s="3"/>
       <c r="AW125" s="3"/>
       <c r="AX125" s="3"/>
-      <c r="AY125" s="6"/>
-      <c r="AZ125" s="6"/>
-      <c r="BA125" s="6"/>
-      <c r="BB125" s="6"/>
+      <c r="AY125" s="3"/>
+      <c r="AZ125" s="3"/>
+      <c r="BA125" s="3"/>
+      <c r="BB125" s="3"/>
       <c r="BC125" s="6"/>
-      <c r="BD125" s="3"/>
-      <c r="BE125" s="3"/>
-      <c r="BF125" s="3"/>
-      <c r="BG125" s="3"/>
+      <c r="BD125" s="6"/>
+      <c r="BE125" s="6"/>
+      <c r="BF125" s="6"/>
+      <c r="BG125" s="6"/>
       <c r="BH125" s="3"/>
       <c r="BI125" s="3"/>
       <c r="BJ125" s="3"/>
@@ -9100,8 +9617,12 @@
       <c r="BL125" s="3"/>
       <c r="BM125" s="3"/>
       <c r="BN125" s="3"/>
-    </row>
-    <row r="126" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO125" s="3"/>
+      <c r="BP125" s="3"/>
+      <c r="BQ125" s="3"/>
+      <c r="BR125" s="3"/>
+    </row>
+    <row r="126" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -9150,15 +9671,15 @@
       <c r="AV126" s="3"/>
       <c r="AW126" s="3"/>
       <c r="AX126" s="3"/>
-      <c r="AY126" s="6"/>
-      <c r="AZ126" s="6"/>
-      <c r="BA126" s="6"/>
-      <c r="BB126" s="6"/>
+      <c r="AY126" s="3"/>
+      <c r="AZ126" s="3"/>
+      <c r="BA126" s="3"/>
+      <c r="BB126" s="3"/>
       <c r="BC126" s="6"/>
-      <c r="BD126" s="3"/>
-      <c r="BE126" s="3"/>
-      <c r="BF126" s="3"/>
-      <c r="BG126" s="3"/>
+      <c r="BD126" s="6"/>
+      <c r="BE126" s="6"/>
+      <c r="BF126" s="6"/>
+      <c r="BG126" s="6"/>
       <c r="BH126" s="3"/>
       <c r="BI126" s="3"/>
       <c r="BJ126" s="3"/>
@@ -9166,8 +9687,12 @@
       <c r="BL126" s="3"/>
       <c r="BM126" s="3"/>
       <c r="BN126" s="3"/>
-    </row>
-    <row r="127" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO126" s="3"/>
+      <c r="BP126" s="3"/>
+      <c r="BQ126" s="3"/>
+      <c r="BR126" s="3"/>
+    </row>
+    <row r="127" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -9216,15 +9741,15 @@
       <c r="AV127" s="3"/>
       <c r="AW127" s="3"/>
       <c r="AX127" s="3"/>
-      <c r="AY127" s="6"/>
-      <c r="AZ127" s="6"/>
-      <c r="BA127" s="6"/>
-      <c r="BB127" s="6"/>
+      <c r="AY127" s="3"/>
+      <c r="AZ127" s="3"/>
+      <c r="BA127" s="3"/>
+      <c r="BB127" s="3"/>
       <c r="BC127" s="6"/>
-      <c r="BD127" s="3"/>
-      <c r="BE127" s="3"/>
-      <c r="BF127" s="3"/>
-      <c r="BG127" s="3"/>
+      <c r="BD127" s="6"/>
+      <c r="BE127" s="6"/>
+      <c r="BF127" s="6"/>
+      <c r="BG127" s="6"/>
       <c r="BH127" s="3"/>
       <c r="BI127" s="3"/>
       <c r="BJ127" s="3"/>
@@ -9232,8 +9757,12 @@
       <c r="BL127" s="3"/>
       <c r="BM127" s="3"/>
       <c r="BN127" s="3"/>
-    </row>
-    <row r="128" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO127" s="3"/>
+      <c r="BP127" s="3"/>
+      <c r="BQ127" s="3"/>
+      <c r="BR127" s="3"/>
+    </row>
+    <row r="128" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -9282,15 +9811,15 @@
       <c r="AV128" s="3"/>
       <c r="AW128" s="3"/>
       <c r="AX128" s="3"/>
-      <c r="AY128" s="6"/>
-      <c r="AZ128" s="6"/>
-      <c r="BA128" s="6"/>
-      <c r="BB128" s="6"/>
+      <c r="AY128" s="3"/>
+      <c r="AZ128" s="3"/>
+      <c r="BA128" s="3"/>
+      <c r="BB128" s="3"/>
       <c r="BC128" s="6"/>
-      <c r="BD128" s="3"/>
-      <c r="BE128" s="3"/>
-      <c r="BF128" s="3"/>
-      <c r="BG128" s="3"/>
+      <c r="BD128" s="6"/>
+      <c r="BE128" s="6"/>
+      <c r="BF128" s="6"/>
+      <c r="BG128" s="6"/>
       <c r="BH128" s="3"/>
       <c r="BI128" s="3"/>
       <c r="BJ128" s="3"/>
@@ -9298,8 +9827,12 @@
       <c r="BL128" s="3"/>
       <c r="BM128" s="3"/>
       <c r="BN128" s="3"/>
-    </row>
-    <row r="129" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO128" s="3"/>
+      <c r="BP128" s="3"/>
+      <c r="BQ128" s="3"/>
+      <c r="BR128" s="3"/>
+    </row>
+    <row r="129" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -9348,15 +9881,15 @@
       <c r="AV129" s="3"/>
       <c r="AW129" s="3"/>
       <c r="AX129" s="3"/>
-      <c r="AY129" s="6"/>
-      <c r="AZ129" s="6"/>
-      <c r="BA129" s="6"/>
-      <c r="BB129" s="6"/>
+      <c r="AY129" s="3"/>
+      <c r="AZ129" s="3"/>
+      <c r="BA129" s="3"/>
+      <c r="BB129" s="3"/>
       <c r="BC129" s="6"/>
-      <c r="BD129" s="3"/>
-      <c r="BE129" s="3"/>
-      <c r="BF129" s="3"/>
-      <c r="BG129" s="3"/>
+      <c r="BD129" s="6"/>
+      <c r="BE129" s="6"/>
+      <c r="BF129" s="6"/>
+      <c r="BG129" s="6"/>
       <c r="BH129" s="3"/>
       <c r="BI129" s="3"/>
       <c r="BJ129" s="3"/>
@@ -9364,8 +9897,12 @@
       <c r="BL129" s="3"/>
       <c r="BM129" s="3"/>
       <c r="BN129" s="3"/>
-    </row>
-    <row r="130" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO129" s="3"/>
+      <c r="BP129" s="3"/>
+      <c r="BQ129" s="3"/>
+      <c r="BR129" s="3"/>
+    </row>
+    <row r="130" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -9414,15 +9951,15 @@
       <c r="AV130" s="3"/>
       <c r="AW130" s="3"/>
       <c r="AX130" s="3"/>
-      <c r="AY130" s="6"/>
-      <c r="AZ130" s="6"/>
-      <c r="BA130" s="6"/>
-      <c r="BB130" s="6"/>
+      <c r="AY130" s="3"/>
+      <c r="AZ130" s="3"/>
+      <c r="BA130" s="3"/>
+      <c r="BB130" s="3"/>
       <c r="BC130" s="6"/>
-      <c r="BD130" s="3"/>
-      <c r="BE130" s="3"/>
-      <c r="BF130" s="3"/>
-      <c r="BG130" s="3"/>
+      <c r="BD130" s="6"/>
+      <c r="BE130" s="6"/>
+      <c r="BF130" s="6"/>
+      <c r="BG130" s="6"/>
       <c r="BH130" s="3"/>
       <c r="BI130" s="3"/>
       <c r="BJ130" s="3"/>
@@ -9430,8 +9967,12 @@
       <c r="BL130" s="3"/>
       <c r="BM130" s="3"/>
       <c r="BN130" s="3"/>
-    </row>
-    <row r="131" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO130" s="3"/>
+      <c r="BP130" s="3"/>
+      <c r="BQ130" s="3"/>
+      <c r="BR130" s="3"/>
+    </row>
+    <row r="131" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -9480,15 +10021,15 @@
       <c r="AV131" s="3"/>
       <c r="AW131" s="3"/>
       <c r="AX131" s="3"/>
-      <c r="AY131" s="6"/>
-      <c r="AZ131" s="6"/>
-      <c r="BA131" s="6"/>
-      <c r="BB131" s="6"/>
+      <c r="AY131" s="3"/>
+      <c r="AZ131" s="3"/>
+      <c r="BA131" s="3"/>
+      <c r="BB131" s="3"/>
       <c r="BC131" s="6"/>
-      <c r="BD131" s="3"/>
-      <c r="BE131" s="3"/>
-      <c r="BF131" s="3"/>
-      <c r="BG131" s="3"/>
+      <c r="BD131" s="6"/>
+      <c r="BE131" s="6"/>
+      <c r="BF131" s="6"/>
+      <c r="BG131" s="6"/>
       <c r="BH131" s="3"/>
       <c r="BI131" s="3"/>
       <c r="BJ131" s="3"/>
@@ -9496,8 +10037,12 @@
       <c r="BL131" s="3"/>
       <c r="BM131" s="3"/>
       <c r="BN131" s="3"/>
-    </row>
-    <row r="132" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO131" s="3"/>
+      <c r="BP131" s="3"/>
+      <c r="BQ131" s="3"/>
+      <c r="BR131" s="3"/>
+    </row>
+    <row r="132" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -9546,15 +10091,15 @@
       <c r="AV132" s="3"/>
       <c r="AW132" s="3"/>
       <c r="AX132" s="3"/>
-      <c r="AY132" s="6"/>
-      <c r="AZ132" s="6"/>
-      <c r="BA132" s="6"/>
-      <c r="BB132" s="6"/>
+      <c r="AY132" s="3"/>
+      <c r="AZ132" s="3"/>
+      <c r="BA132" s="3"/>
+      <c r="BB132" s="3"/>
       <c r="BC132" s="6"/>
-      <c r="BD132" s="3"/>
-      <c r="BE132" s="3"/>
-      <c r="BF132" s="3"/>
-      <c r="BG132" s="3"/>
+      <c r="BD132" s="6"/>
+      <c r="BE132" s="6"/>
+      <c r="BF132" s="6"/>
+      <c r="BG132" s="6"/>
       <c r="BH132" s="3"/>
       <c r="BI132" s="3"/>
       <c r="BJ132" s="3"/>
@@ -9562,8 +10107,12 @@
       <c r="BL132" s="3"/>
       <c r="BM132" s="3"/>
       <c r="BN132" s="3"/>
-    </row>
-    <row r="133" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO132" s="3"/>
+      <c r="BP132" s="3"/>
+      <c r="BQ132" s="3"/>
+      <c r="BR132" s="3"/>
+    </row>
+    <row r="133" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -9612,15 +10161,15 @@
       <c r="AV133" s="3"/>
       <c r="AW133" s="3"/>
       <c r="AX133" s="3"/>
-      <c r="AY133" s="6"/>
-      <c r="AZ133" s="6"/>
-      <c r="BA133" s="6"/>
-      <c r="BB133" s="6"/>
+      <c r="AY133" s="3"/>
+      <c r="AZ133" s="3"/>
+      <c r="BA133" s="3"/>
+      <c r="BB133" s="3"/>
       <c r="BC133" s="6"/>
-      <c r="BD133" s="3"/>
-      <c r="BE133" s="3"/>
-      <c r="BF133" s="3"/>
-      <c r="BG133" s="3"/>
+      <c r="BD133" s="6"/>
+      <c r="BE133" s="6"/>
+      <c r="BF133" s="6"/>
+      <c r="BG133" s="6"/>
       <c r="BH133" s="3"/>
       <c r="BI133" s="3"/>
       <c r="BJ133" s="3"/>
@@ -9628,8 +10177,12 @@
       <c r="BL133" s="3"/>
       <c r="BM133" s="3"/>
       <c r="BN133" s="3"/>
-    </row>
-    <row r="134" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO133" s="3"/>
+      <c r="BP133" s="3"/>
+      <c r="BQ133" s="3"/>
+      <c r="BR133" s="3"/>
+    </row>
+    <row r="134" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -9678,15 +10231,15 @@
       <c r="AV134" s="3"/>
       <c r="AW134" s="3"/>
       <c r="AX134" s="3"/>
-      <c r="AY134" s="6"/>
-      <c r="AZ134" s="6"/>
-      <c r="BA134" s="6"/>
-      <c r="BB134" s="6"/>
+      <c r="AY134" s="3"/>
+      <c r="AZ134" s="3"/>
+      <c r="BA134" s="3"/>
+      <c r="BB134" s="3"/>
       <c r="BC134" s="6"/>
-      <c r="BD134" s="3"/>
-      <c r="BE134" s="3"/>
-      <c r="BF134" s="3"/>
-      <c r="BG134" s="3"/>
+      <c r="BD134" s="6"/>
+      <c r="BE134" s="6"/>
+      <c r="BF134" s="6"/>
+      <c r="BG134" s="6"/>
       <c r="BH134" s="3"/>
       <c r="BI134" s="3"/>
       <c r="BJ134" s="3"/>
@@ -9694,8 +10247,12 @@
       <c r="BL134" s="3"/>
       <c r="BM134" s="3"/>
       <c r="BN134" s="3"/>
-    </row>
-    <row r="135" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO134" s="3"/>
+      <c r="BP134" s="3"/>
+      <c r="BQ134" s="3"/>
+      <c r="BR134" s="3"/>
+    </row>
+    <row r="135" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -9744,15 +10301,15 @@
       <c r="AV135" s="3"/>
       <c r="AW135" s="3"/>
       <c r="AX135" s="3"/>
-      <c r="AY135" s="6"/>
-      <c r="AZ135" s="6"/>
-      <c r="BA135" s="6"/>
-      <c r="BB135" s="6"/>
+      <c r="AY135" s="3"/>
+      <c r="AZ135" s="3"/>
+      <c r="BA135" s="3"/>
+      <c r="BB135" s="3"/>
       <c r="BC135" s="6"/>
-      <c r="BD135" s="3"/>
-      <c r="BE135" s="3"/>
-      <c r="BF135" s="3"/>
-      <c r="BG135" s="3"/>
+      <c r="BD135" s="6"/>
+      <c r="BE135" s="6"/>
+      <c r="BF135" s="6"/>
+      <c r="BG135" s="6"/>
       <c r="BH135" s="3"/>
       <c r="BI135" s="3"/>
       <c r="BJ135" s="3"/>
@@ -9760,8 +10317,12 @@
       <c r="BL135" s="3"/>
       <c r="BM135" s="3"/>
       <c r="BN135" s="3"/>
-    </row>
-    <row r="136" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO135" s="3"/>
+      <c r="BP135" s="3"/>
+      <c r="BQ135" s="3"/>
+      <c r="BR135" s="3"/>
+    </row>
+    <row r="136" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -9810,15 +10371,15 @@
       <c r="AV136" s="3"/>
       <c r="AW136" s="3"/>
       <c r="AX136" s="3"/>
-      <c r="AY136" s="6"/>
-      <c r="AZ136" s="6"/>
-      <c r="BA136" s="6"/>
-      <c r="BB136" s="6"/>
+      <c r="AY136" s="3"/>
+      <c r="AZ136" s="3"/>
+      <c r="BA136" s="3"/>
+      <c r="BB136" s="3"/>
       <c r="BC136" s="6"/>
-      <c r="BD136" s="3"/>
-      <c r="BE136" s="3"/>
-      <c r="BF136" s="3"/>
-      <c r="BG136" s="3"/>
+      <c r="BD136" s="6"/>
+      <c r="BE136" s="6"/>
+      <c r="BF136" s="6"/>
+      <c r="BG136" s="6"/>
       <c r="BH136" s="3"/>
       <c r="BI136" s="3"/>
       <c r="BJ136" s="3"/>
@@ -9826,8 +10387,12 @@
       <c r="BL136" s="3"/>
       <c r="BM136" s="3"/>
       <c r="BN136" s="3"/>
-    </row>
-    <row r="137" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO136" s="3"/>
+      <c r="BP136" s="3"/>
+      <c r="BQ136" s="3"/>
+      <c r="BR136" s="3"/>
+    </row>
+    <row r="137" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -9876,15 +10441,15 @@
       <c r="AV137" s="3"/>
       <c r="AW137" s="3"/>
       <c r="AX137" s="3"/>
-      <c r="AY137" s="6"/>
-      <c r="AZ137" s="6"/>
-      <c r="BA137" s="6"/>
-      <c r="BB137" s="6"/>
+      <c r="AY137" s="3"/>
+      <c r="AZ137" s="3"/>
+      <c r="BA137" s="3"/>
+      <c r="BB137" s="3"/>
       <c r="BC137" s="6"/>
-      <c r="BD137" s="3"/>
-      <c r="BE137" s="3"/>
-      <c r="BF137" s="3"/>
-      <c r="BG137" s="3"/>
+      <c r="BD137" s="6"/>
+      <c r="BE137" s="6"/>
+      <c r="BF137" s="6"/>
+      <c r="BG137" s="6"/>
       <c r="BH137" s="3"/>
       <c r="BI137" s="3"/>
       <c r="BJ137" s="3"/>
@@ -9892,8 +10457,12 @@
       <c r="BL137" s="3"/>
       <c r="BM137" s="3"/>
       <c r="BN137" s="3"/>
-    </row>
-    <row r="138" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO137" s="3"/>
+      <c r="BP137" s="3"/>
+      <c r="BQ137" s="3"/>
+      <c r="BR137" s="3"/>
+    </row>
+    <row r="138" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -9942,15 +10511,15 @@
       <c r="AV138" s="3"/>
       <c r="AW138" s="3"/>
       <c r="AX138" s="3"/>
-      <c r="AY138" s="6"/>
-      <c r="AZ138" s="6"/>
-      <c r="BA138" s="6"/>
-      <c r="BB138" s="6"/>
+      <c r="AY138" s="3"/>
+      <c r="AZ138" s="3"/>
+      <c r="BA138" s="3"/>
+      <c r="BB138" s="3"/>
       <c r="BC138" s="6"/>
-      <c r="BD138" s="3"/>
-      <c r="BE138" s="3"/>
-      <c r="BF138" s="3"/>
-      <c r="BG138" s="3"/>
+      <c r="BD138" s="6"/>
+      <c r="BE138" s="6"/>
+      <c r="BF138" s="6"/>
+      <c r="BG138" s="6"/>
       <c r="BH138" s="3"/>
       <c r="BI138" s="3"/>
       <c r="BJ138" s="3"/>
@@ -9958,8 +10527,12 @@
       <c r="BL138" s="3"/>
       <c r="BM138" s="3"/>
       <c r="BN138" s="3"/>
-    </row>
-    <row r="139" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO138" s="3"/>
+      <c r="BP138" s="3"/>
+      <c r="BQ138" s="3"/>
+      <c r="BR138" s="3"/>
+    </row>
+    <row r="139" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -10008,15 +10581,15 @@
       <c r="AV139" s="3"/>
       <c r="AW139" s="3"/>
       <c r="AX139" s="3"/>
-      <c r="AY139" s="6"/>
-      <c r="AZ139" s="6"/>
-      <c r="BA139" s="6"/>
-      <c r="BB139" s="6"/>
+      <c r="AY139" s="3"/>
+      <c r="AZ139" s="3"/>
+      <c r="BA139" s="3"/>
+      <c r="BB139" s="3"/>
       <c r="BC139" s="6"/>
-      <c r="BD139" s="3"/>
-      <c r="BE139" s="3"/>
-      <c r="BF139" s="3"/>
-      <c r="BG139" s="3"/>
+      <c r="BD139" s="6"/>
+      <c r="BE139" s="6"/>
+      <c r="BF139" s="6"/>
+      <c r="BG139" s="6"/>
       <c r="BH139" s="3"/>
       <c r="BI139" s="3"/>
       <c r="BJ139" s="3"/>
@@ -10024,8 +10597,12 @@
       <c r="BL139" s="3"/>
       <c r="BM139" s="3"/>
       <c r="BN139" s="3"/>
-    </row>
-    <row r="140" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO139" s="3"/>
+      <c r="BP139" s="3"/>
+      <c r="BQ139" s="3"/>
+      <c r="BR139" s="3"/>
+    </row>
+    <row r="140" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -10074,15 +10651,15 @@
       <c r="AV140" s="3"/>
       <c r="AW140" s="3"/>
       <c r="AX140" s="3"/>
-      <c r="AY140" s="6"/>
-      <c r="AZ140" s="6"/>
-      <c r="BA140" s="6"/>
-      <c r="BB140" s="6"/>
+      <c r="AY140" s="3"/>
+      <c r="AZ140" s="3"/>
+      <c r="BA140" s="3"/>
+      <c r="BB140" s="3"/>
       <c r="BC140" s="6"/>
-      <c r="BD140" s="3"/>
-      <c r="BE140" s="3"/>
-      <c r="BF140" s="3"/>
-      <c r="BG140" s="3"/>
+      <c r="BD140" s="6"/>
+      <c r="BE140" s="6"/>
+      <c r="BF140" s="6"/>
+      <c r="BG140" s="6"/>
       <c r="BH140" s="3"/>
       <c r="BI140" s="3"/>
       <c r="BJ140" s="3"/>
@@ -10090,8 +10667,12 @@
       <c r="BL140" s="3"/>
       <c r="BM140" s="3"/>
       <c r="BN140" s="3"/>
-    </row>
-    <row r="141" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO140" s="3"/>
+      <c r="BP140" s="3"/>
+      <c r="BQ140" s="3"/>
+      <c r="BR140" s="3"/>
+    </row>
+    <row r="141" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -10140,15 +10721,15 @@
       <c r="AV141" s="3"/>
       <c r="AW141" s="3"/>
       <c r="AX141" s="3"/>
-      <c r="AY141" s="6"/>
-      <c r="AZ141" s="6"/>
-      <c r="BA141" s="6"/>
-      <c r="BB141" s="6"/>
+      <c r="AY141" s="3"/>
+      <c r="AZ141" s="3"/>
+      <c r="BA141" s="3"/>
+      <c r="BB141" s="3"/>
       <c r="BC141" s="6"/>
-      <c r="BD141" s="3"/>
-      <c r="BE141" s="3"/>
-      <c r="BF141" s="3"/>
-      <c r="BG141" s="3"/>
+      <c r="BD141" s="6"/>
+      <c r="BE141" s="6"/>
+      <c r="BF141" s="6"/>
+      <c r="BG141" s="6"/>
       <c r="BH141" s="3"/>
       <c r="BI141" s="3"/>
       <c r="BJ141" s="3"/>
@@ -10156,8 +10737,12 @@
       <c r="BL141" s="3"/>
       <c r="BM141" s="3"/>
       <c r="BN141" s="3"/>
-    </row>
-    <row r="142" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO141" s="3"/>
+      <c r="BP141" s="3"/>
+      <c r="BQ141" s="3"/>
+      <c r="BR141" s="3"/>
+    </row>
+    <row r="142" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -10222,8 +10807,12 @@
       <c r="BL142" s="3"/>
       <c r="BM142" s="3"/>
       <c r="BN142" s="3"/>
-    </row>
-    <row r="143" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO142" s="3"/>
+      <c r="BP142" s="3"/>
+      <c r="BQ142" s="3"/>
+      <c r="BR142" s="3"/>
+    </row>
+    <row r="143" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -10288,8 +10877,12 @@
       <c r="BL143" s="3"/>
       <c r="BM143" s="3"/>
       <c r="BN143" s="3"/>
-    </row>
-    <row r="144" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO143" s="3"/>
+      <c r="BP143" s="3"/>
+      <c r="BQ143" s="3"/>
+      <c r="BR143" s="3"/>
+    </row>
+    <row r="144" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -10354,8 +10947,12 @@
       <c r="BL144" s="3"/>
       <c r="BM144" s="3"/>
       <c r="BN144" s="3"/>
-    </row>
-    <row r="145" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO144" s="3"/>
+      <c r="BP144" s="3"/>
+      <c r="BQ144" s="3"/>
+      <c r="BR144" s="3"/>
+    </row>
+    <row r="145" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -10420,8 +11017,12 @@
       <c r="BL145" s="3"/>
       <c r="BM145" s="3"/>
       <c r="BN145" s="3"/>
-    </row>
-    <row r="146" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO145" s="3"/>
+      <c r="BP145" s="3"/>
+      <c r="BQ145" s="3"/>
+      <c r="BR145" s="3"/>
+    </row>
+    <row r="146" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -10486,8 +11087,12 @@
       <c r="BL146" s="3"/>
       <c r="BM146" s="3"/>
       <c r="BN146" s="3"/>
-    </row>
-    <row r="147" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO146" s="3"/>
+      <c r="BP146" s="3"/>
+      <c r="BQ146" s="3"/>
+      <c r="BR146" s="3"/>
+    </row>
+    <row r="147" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -10552,8 +11157,12 @@
       <c r="BL147" s="3"/>
       <c r="BM147" s="3"/>
       <c r="BN147" s="3"/>
-    </row>
-    <row r="148" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO147" s="3"/>
+      <c r="BP147" s="3"/>
+      <c r="BQ147" s="3"/>
+      <c r="BR147" s="3"/>
+    </row>
+    <row r="148" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -10618,8 +11227,12 @@
       <c r="BL148" s="3"/>
       <c r="BM148" s="3"/>
       <c r="BN148" s="3"/>
-    </row>
-    <row r="149" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO148" s="3"/>
+      <c r="BP148" s="3"/>
+      <c r="BQ148" s="3"/>
+      <c r="BR148" s="3"/>
+    </row>
+    <row r="149" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -10684,8 +11297,12 @@
       <c r="BL149" s="3"/>
       <c r="BM149" s="3"/>
       <c r="BN149" s="3"/>
-    </row>
-    <row r="150" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO149" s="3"/>
+      <c r="BP149" s="3"/>
+      <c r="BQ149" s="3"/>
+      <c r="BR149" s="3"/>
+    </row>
+    <row r="150" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -10750,8 +11367,12 @@
       <c r="BL150" s="3"/>
       <c r="BM150" s="3"/>
       <c r="BN150" s="3"/>
-    </row>
-    <row r="151" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO150" s="3"/>
+      <c r="BP150" s="3"/>
+      <c r="BQ150" s="3"/>
+      <c r="BR150" s="3"/>
+    </row>
+    <row r="151" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -10816,8 +11437,12 @@
       <c r="BL151" s="3"/>
       <c r="BM151" s="3"/>
       <c r="BN151" s="3"/>
-    </row>
-    <row r="152" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO151" s="3"/>
+      <c r="BP151" s="3"/>
+      <c r="BQ151" s="3"/>
+      <c r="BR151" s="3"/>
+    </row>
+    <row r="152" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -10882,8 +11507,12 @@
       <c r="BL152" s="3"/>
       <c r="BM152" s="3"/>
       <c r="BN152" s="3"/>
-    </row>
-    <row r="153" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO152" s="3"/>
+      <c r="BP152" s="3"/>
+      <c r="BQ152" s="3"/>
+      <c r="BR152" s="3"/>
+    </row>
+    <row r="153" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -10948,8 +11577,12 @@
       <c r="BL153" s="3"/>
       <c r="BM153" s="3"/>
       <c r="BN153" s="3"/>
-    </row>
-    <row r="154" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO153" s="3"/>
+      <c r="BP153" s="3"/>
+      <c r="BQ153" s="3"/>
+      <c r="BR153" s="3"/>
+    </row>
+    <row r="154" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -11014,8 +11647,12 @@
       <c r="BL154" s="3"/>
       <c r="BM154" s="3"/>
       <c r="BN154" s="3"/>
-    </row>
-    <row r="155" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO154" s="3"/>
+      <c r="BP154" s="3"/>
+      <c r="BQ154" s="3"/>
+      <c r="BR154" s="3"/>
+    </row>
+    <row r="155" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -11080,8 +11717,12 @@
       <c r="BL155" s="3"/>
       <c r="BM155" s="3"/>
       <c r="BN155" s="3"/>
-    </row>
-    <row r="156" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO155" s="3"/>
+      <c r="BP155" s="3"/>
+      <c r="BQ155" s="3"/>
+      <c r="BR155" s="3"/>
+    </row>
+    <row r="156" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -11146,8 +11787,12 @@
       <c r="BL156" s="3"/>
       <c r="BM156" s="3"/>
       <c r="BN156" s="3"/>
-    </row>
-    <row r="157" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO156" s="3"/>
+      <c r="BP156" s="3"/>
+      <c r="BQ156" s="3"/>
+      <c r="BR156" s="3"/>
+    </row>
+    <row r="157" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -11212,8 +11857,12 @@
       <c r="BL157" s="3"/>
       <c r="BM157" s="3"/>
       <c r="BN157" s="3"/>
-    </row>
-    <row r="158" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO157" s="3"/>
+      <c r="BP157" s="3"/>
+      <c r="BQ157" s="3"/>
+      <c r="BR157" s="3"/>
+    </row>
+    <row r="158" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -11278,8 +11927,12 @@
       <c r="BL158" s="3"/>
       <c r="BM158" s="3"/>
       <c r="BN158" s="3"/>
-    </row>
-    <row r="159" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO158" s="3"/>
+      <c r="BP158" s="3"/>
+      <c r="BQ158" s="3"/>
+      <c r="BR158" s="3"/>
+    </row>
+    <row r="159" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -11344,8 +11997,12 @@
       <c r="BL159" s="3"/>
       <c r="BM159" s="3"/>
       <c r="BN159" s="3"/>
-    </row>
-    <row r="160" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO159" s="3"/>
+      <c r="BP159" s="3"/>
+      <c r="BQ159" s="3"/>
+      <c r="BR159" s="3"/>
+    </row>
+    <row r="160" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -11410,8 +12067,12 @@
       <c r="BL160" s="3"/>
       <c r="BM160" s="3"/>
       <c r="BN160" s="3"/>
-    </row>
-    <row r="161" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO160" s="3"/>
+      <c r="BP160" s="3"/>
+      <c r="BQ160" s="3"/>
+      <c r="BR160" s="3"/>
+    </row>
+    <row r="161" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -11476,8 +12137,12 @@
       <c r="BL161" s="3"/>
       <c r="BM161" s="3"/>
       <c r="BN161" s="3"/>
-    </row>
-    <row r="162" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO161" s="3"/>
+      <c r="BP161" s="3"/>
+      <c r="BQ161" s="3"/>
+      <c r="BR161" s="3"/>
+    </row>
+    <row r="162" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -11542,8 +12207,12 @@
       <c r="BL162" s="3"/>
       <c r="BM162" s="3"/>
       <c r="BN162" s="3"/>
-    </row>
-    <row r="163" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO162" s="3"/>
+      <c r="BP162" s="3"/>
+      <c r="BQ162" s="3"/>
+      <c r="BR162" s="3"/>
+    </row>
+    <row r="163" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -11608,8 +12277,12 @@
       <c r="BL163" s="3"/>
       <c r="BM163" s="3"/>
       <c r="BN163" s="3"/>
-    </row>
-    <row r="164" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO163" s="3"/>
+      <c r="BP163" s="3"/>
+      <c r="BQ163" s="3"/>
+      <c r="BR163" s="3"/>
+    </row>
+    <row r="164" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -11674,8 +12347,12 @@
       <c r="BL164" s="3"/>
       <c r="BM164" s="3"/>
       <c r="BN164" s="3"/>
-    </row>
-    <row r="165" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO164" s="3"/>
+      <c r="BP164" s="3"/>
+      <c r="BQ164" s="3"/>
+      <c r="BR164" s="3"/>
+    </row>
+    <row r="165" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -11740,8 +12417,12 @@
       <c r="BL165" s="3"/>
       <c r="BM165" s="3"/>
       <c r="BN165" s="3"/>
-    </row>
-    <row r="166" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO165" s="3"/>
+      <c r="BP165" s="3"/>
+      <c r="BQ165" s="3"/>
+      <c r="BR165" s="3"/>
+    </row>
+    <row r="166" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -11806,8 +12487,12 @@
       <c r="BL166" s="3"/>
       <c r="BM166" s="3"/>
       <c r="BN166" s="3"/>
-    </row>
-    <row r="167" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO166" s="3"/>
+      <c r="BP166" s="3"/>
+      <c r="BQ166" s="3"/>
+      <c r="BR166" s="3"/>
+    </row>
+    <row r="167" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -11872,8 +12557,12 @@
       <c r="BL167" s="3"/>
       <c r="BM167" s="3"/>
       <c r="BN167" s="3"/>
-    </row>
-    <row r="168" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO167" s="3"/>
+      <c r="BP167" s="3"/>
+      <c r="BQ167" s="3"/>
+      <c r="BR167" s="3"/>
+    </row>
+    <row r="168" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -11938,8 +12627,12 @@
       <c r="BL168" s="3"/>
       <c r="BM168" s="3"/>
       <c r="BN168" s="3"/>
-    </row>
-    <row r="169" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO168" s="3"/>
+      <c r="BP168" s="3"/>
+      <c r="BQ168" s="3"/>
+      <c r="BR168" s="3"/>
+    </row>
+    <row r="169" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -12004,8 +12697,12 @@
       <c r="BL169" s="3"/>
       <c r="BM169" s="3"/>
       <c r="BN169" s="3"/>
-    </row>
-    <row r="170" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO169" s="3"/>
+      <c r="BP169" s="3"/>
+      <c r="BQ169" s="3"/>
+      <c r="BR169" s="3"/>
+    </row>
+    <row r="170" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -12070,8 +12767,12 @@
       <c r="BL170" s="3"/>
       <c r="BM170" s="3"/>
       <c r="BN170" s="3"/>
-    </row>
-    <row r="171" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO170" s="3"/>
+      <c r="BP170" s="3"/>
+      <c r="BQ170" s="3"/>
+      <c r="BR170" s="3"/>
+    </row>
+    <row r="171" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -12136,8 +12837,12 @@
       <c r="BL171" s="3"/>
       <c r="BM171" s="3"/>
       <c r="BN171" s="3"/>
-    </row>
-    <row r="172" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO171" s="3"/>
+      <c r="BP171" s="3"/>
+      <c r="BQ171" s="3"/>
+      <c r="BR171" s="3"/>
+    </row>
+    <row r="172" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -12202,8 +12907,12 @@
       <c r="BL172" s="3"/>
       <c r="BM172" s="3"/>
       <c r="BN172" s="3"/>
-    </row>
-    <row r="173" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO172" s="3"/>
+      <c r="BP172" s="3"/>
+      <c r="BQ172" s="3"/>
+      <c r="BR172" s="3"/>
+    </row>
+    <row r="173" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -12268,8 +12977,12 @@
       <c r="BL173" s="3"/>
       <c r="BM173" s="3"/>
       <c r="BN173" s="3"/>
-    </row>
-    <row r="174" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO173" s="3"/>
+      <c r="BP173" s="3"/>
+      <c r="BQ173" s="3"/>
+      <c r="BR173" s="3"/>
+    </row>
+    <row r="174" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -12334,8 +13047,12 @@
       <c r="BL174" s="3"/>
       <c r="BM174" s="3"/>
       <c r="BN174" s="3"/>
-    </row>
-    <row r="175" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO174" s="3"/>
+      <c r="BP174" s="3"/>
+      <c r="BQ174" s="3"/>
+      <c r="BR174" s="3"/>
+    </row>
+    <row r="175" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -12400,8 +13117,12 @@
       <c r="BL175" s="3"/>
       <c r="BM175" s="3"/>
       <c r="BN175" s="3"/>
-    </row>
-    <row r="176" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO175" s="3"/>
+      <c r="BP175" s="3"/>
+      <c r="BQ175" s="3"/>
+      <c r="BR175" s="3"/>
+    </row>
+    <row r="176" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -12466,8 +13187,12 @@
       <c r="BL176" s="3"/>
       <c r="BM176" s="3"/>
       <c r="BN176" s="3"/>
-    </row>
-    <row r="177" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO176" s="3"/>
+      <c r="BP176" s="3"/>
+      <c r="BQ176" s="3"/>
+      <c r="BR176" s="3"/>
+    </row>
+    <row r="177" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -12532,8 +13257,12 @@
       <c r="BL177" s="3"/>
       <c r="BM177" s="3"/>
       <c r="BN177" s="3"/>
-    </row>
-    <row r="178" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO177" s="3"/>
+      <c r="BP177" s="3"/>
+      <c r="BQ177" s="3"/>
+      <c r="BR177" s="3"/>
+    </row>
+    <row r="178" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -12598,8 +13327,12 @@
       <c r="BL178" s="3"/>
       <c r="BM178" s="3"/>
       <c r="BN178" s="3"/>
-    </row>
-    <row r="179" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO178" s="3"/>
+      <c r="BP178" s="3"/>
+      <c r="BQ178" s="3"/>
+      <c r="BR178" s="3"/>
+    </row>
+    <row r="179" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -12664,8 +13397,12 @@
       <c r="BL179" s="3"/>
       <c r="BM179" s="3"/>
       <c r="BN179" s="3"/>
-    </row>
-    <row r="180" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO179" s="3"/>
+      <c r="BP179" s="3"/>
+      <c r="BQ179" s="3"/>
+      <c r="BR179" s="3"/>
+    </row>
+    <row r="180" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -12730,8 +13467,12 @@
       <c r="BL180" s="3"/>
       <c r="BM180" s="3"/>
       <c r="BN180" s="3"/>
-    </row>
-    <row r="181" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO180" s="3"/>
+      <c r="BP180" s="3"/>
+      <c r="BQ180" s="3"/>
+      <c r="BR180" s="3"/>
+    </row>
+    <row r="181" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -12796,8 +13537,12 @@
       <c r="BL181" s="3"/>
       <c r="BM181" s="3"/>
       <c r="BN181" s="3"/>
-    </row>
-    <row r="182" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO181" s="3"/>
+      <c r="BP181" s="3"/>
+      <c r="BQ181" s="3"/>
+      <c r="BR181" s="3"/>
+    </row>
+    <row r="182" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -12862,8 +13607,12 @@
       <c r="BL182" s="3"/>
       <c r="BM182" s="3"/>
       <c r="BN182" s="3"/>
-    </row>
-    <row r="183" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO182" s="3"/>
+      <c r="BP182" s="3"/>
+      <c r="BQ182" s="3"/>
+      <c r="BR182" s="3"/>
+    </row>
+    <row r="183" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -12928,8 +13677,12 @@
       <c r="BL183" s="3"/>
       <c r="BM183" s="3"/>
       <c r="BN183" s="3"/>
-    </row>
-    <row r="184" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO183" s="3"/>
+      <c r="BP183" s="3"/>
+      <c r="BQ183" s="3"/>
+      <c r="BR183" s="3"/>
+    </row>
+    <row r="184" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -12994,8 +13747,12 @@
       <c r="BL184" s="3"/>
       <c r="BM184" s="3"/>
       <c r="BN184" s="3"/>
-    </row>
-    <row r="185" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO184" s="3"/>
+      <c r="BP184" s="3"/>
+      <c r="BQ184" s="3"/>
+      <c r="BR184" s="3"/>
+    </row>
+    <row r="185" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -13060,8 +13817,12 @@
       <c r="BL185" s="3"/>
       <c r="BM185" s="3"/>
       <c r="BN185" s="3"/>
-    </row>
-    <row r="186" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO185" s="3"/>
+      <c r="BP185" s="3"/>
+      <c r="BQ185" s="3"/>
+      <c r="BR185" s="3"/>
+    </row>
+    <row r="186" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -13126,8 +13887,12 @@
       <c r="BL186" s="3"/>
       <c r="BM186" s="3"/>
       <c r="BN186" s="3"/>
-    </row>
-    <row r="187" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO186" s="3"/>
+      <c r="BP186" s="3"/>
+      <c r="BQ186" s="3"/>
+      <c r="BR186" s="3"/>
+    </row>
+    <row r="187" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -13192,8 +13957,12 @@
       <c r="BL187" s="3"/>
       <c r="BM187" s="3"/>
       <c r="BN187" s="3"/>
-    </row>
-    <row r="188" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO187" s="3"/>
+      <c r="BP187" s="3"/>
+      <c r="BQ187" s="3"/>
+      <c r="BR187" s="3"/>
+    </row>
+    <row r="188" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -13258,8 +14027,12 @@
       <c r="BL188" s="3"/>
       <c r="BM188" s="3"/>
       <c r="BN188" s="3"/>
-    </row>
-    <row r="189" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO188" s="3"/>
+      <c r="BP188" s="3"/>
+      <c r="BQ188" s="3"/>
+      <c r="BR188" s="3"/>
+    </row>
+    <row r="189" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -13324,8 +14097,12 @@
       <c r="BL189" s="3"/>
       <c r="BM189" s="3"/>
       <c r="BN189" s="3"/>
-    </row>
-    <row r="190" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO189" s="3"/>
+      <c r="BP189" s="3"/>
+      <c r="BQ189" s="3"/>
+      <c r="BR189" s="3"/>
+    </row>
+    <row r="190" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -13390,8 +14167,12 @@
       <c r="BL190" s="3"/>
       <c r="BM190" s="3"/>
       <c r="BN190" s="3"/>
-    </row>
-    <row r="191" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO190" s="3"/>
+      <c r="BP190" s="3"/>
+      <c r="BQ190" s="3"/>
+      <c r="BR190" s="3"/>
+    </row>
+    <row r="191" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -13456,8 +14237,12 @@
       <c r="BL191" s="3"/>
       <c r="BM191" s="3"/>
       <c r="BN191" s="3"/>
-    </row>
-    <row r="192" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO191" s="3"/>
+      <c r="BP191" s="3"/>
+      <c r="BQ191" s="3"/>
+      <c r="BR191" s="3"/>
+    </row>
+    <row r="192" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -13522,8 +14307,12 @@
       <c r="BL192" s="3"/>
       <c r="BM192" s="3"/>
       <c r="BN192" s="3"/>
-    </row>
-    <row r="193" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO192" s="3"/>
+      <c r="BP192" s="3"/>
+      <c r="BQ192" s="3"/>
+      <c r="BR192" s="3"/>
+    </row>
+    <row r="193" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -13588,8 +14377,12 @@
       <c r="BL193" s="3"/>
       <c r="BM193" s="3"/>
       <c r="BN193" s="3"/>
-    </row>
-    <row r="194" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO193" s="3"/>
+      <c r="BP193" s="3"/>
+      <c r="BQ193" s="3"/>
+      <c r="BR193" s="3"/>
+    </row>
+    <row r="194" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -13654,8 +14447,12 @@
       <c r="BL194" s="3"/>
       <c r="BM194" s="3"/>
       <c r="BN194" s="3"/>
-    </row>
-    <row r="195" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO194" s="3"/>
+      <c r="BP194" s="3"/>
+      <c r="BQ194" s="3"/>
+      <c r="BR194" s="3"/>
+    </row>
+    <row r="195" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -13720,8 +14517,12 @@
       <c r="BL195" s="3"/>
       <c r="BM195" s="3"/>
       <c r="BN195" s="3"/>
-    </row>
-    <row r="196" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO195" s="3"/>
+      <c r="BP195" s="3"/>
+      <c r="BQ195" s="3"/>
+      <c r="BR195" s="3"/>
+    </row>
+    <row r="196" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -13786,8 +14587,12 @@
       <c r="BL196" s="3"/>
       <c r="BM196" s="3"/>
       <c r="BN196" s="3"/>
-    </row>
-    <row r="197" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO196" s="3"/>
+      <c r="BP196" s="3"/>
+      <c r="BQ196" s="3"/>
+      <c r="BR196" s="3"/>
+    </row>
+    <row r="197" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -13852,8 +14657,12 @@
       <c r="BL197" s="3"/>
       <c r="BM197" s="3"/>
       <c r="BN197" s="3"/>
-    </row>
-    <row r="198" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO197" s="3"/>
+      <c r="BP197" s="3"/>
+      <c r="BQ197" s="3"/>
+      <c r="BR197" s="3"/>
+    </row>
+    <row r="198" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -13918,8 +14727,12 @@
       <c r="BL198" s="3"/>
       <c r="BM198" s="3"/>
       <c r="BN198" s="3"/>
-    </row>
-    <row r="199" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO198" s="3"/>
+      <c r="BP198" s="3"/>
+      <c r="BQ198" s="3"/>
+      <c r="BR198" s="3"/>
+    </row>
+    <row r="199" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -13984,8 +14797,12 @@
       <c r="BL199" s="3"/>
       <c r="BM199" s="3"/>
       <c r="BN199" s="3"/>
-    </row>
-    <row r="200" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO199" s="3"/>
+      <c r="BP199" s="3"/>
+      <c r="BQ199" s="3"/>
+      <c r="BR199" s="3"/>
+    </row>
+    <row r="200" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -14050,8 +14867,12 @@
       <c r="BL200" s="3"/>
       <c r="BM200" s="3"/>
       <c r="BN200" s="3"/>
-    </row>
-    <row r="201" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO200" s="3"/>
+      <c r="BP200" s="3"/>
+      <c r="BQ200" s="3"/>
+      <c r="BR200" s="3"/>
+    </row>
+    <row r="201" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -14116,8 +14937,12 @@
       <c r="BL201" s="3"/>
       <c r="BM201" s="3"/>
       <c r="BN201" s="3"/>
-    </row>
-    <row r="202" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO201" s="3"/>
+      <c r="BP201" s="3"/>
+      <c r="BQ201" s="3"/>
+      <c r="BR201" s="3"/>
+    </row>
+    <row r="202" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -14182,8 +15007,12 @@
       <c r="BL202" s="3"/>
       <c r="BM202" s="3"/>
       <c r="BN202" s="3"/>
-    </row>
-    <row r="203" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO202" s="3"/>
+      <c r="BP202" s="3"/>
+      <c r="BQ202" s="3"/>
+      <c r="BR202" s="3"/>
+    </row>
+    <row r="203" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -14248,8 +15077,12 @@
       <c r="BL203" s="3"/>
       <c r="BM203" s="3"/>
       <c r="BN203" s="3"/>
-    </row>
-    <row r="204" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO203" s="3"/>
+      <c r="BP203" s="3"/>
+      <c r="BQ203" s="3"/>
+      <c r="BR203" s="3"/>
+    </row>
+    <row r="204" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -14314,8 +15147,12 @@
       <c r="BL204" s="3"/>
       <c r="BM204" s="3"/>
       <c r="BN204" s="3"/>
-    </row>
-    <row r="205" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO204" s="3"/>
+      <c r="BP204" s="3"/>
+      <c r="BQ204" s="3"/>
+      <c r="BR204" s="3"/>
+    </row>
+    <row r="205" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -14380,8 +15217,12 @@
       <c r="BL205" s="3"/>
       <c r="BM205" s="3"/>
       <c r="BN205" s="3"/>
-    </row>
-    <row r="206" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO205" s="3"/>
+      <c r="BP205" s="3"/>
+      <c r="BQ205" s="3"/>
+      <c r="BR205" s="3"/>
+    </row>
+    <row r="206" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -14446,8 +15287,12 @@
       <c r="BL206" s="3"/>
       <c r="BM206" s="3"/>
       <c r="BN206" s="3"/>
-    </row>
-    <row r="207" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO206" s="3"/>
+      <c r="BP206" s="3"/>
+      <c r="BQ206" s="3"/>
+      <c r="BR206" s="3"/>
+    </row>
+    <row r="207" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -14512,8 +15357,12 @@
       <c r="BL207" s="3"/>
       <c r="BM207" s="3"/>
       <c r="BN207" s="3"/>
-    </row>
-    <row r="208" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO207" s="3"/>
+      <c r="BP207" s="3"/>
+      <c r="BQ207" s="3"/>
+      <c r="BR207" s="3"/>
+    </row>
+    <row r="208" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -14578,8 +15427,12 @@
       <c r="BL208" s="3"/>
       <c r="BM208" s="3"/>
       <c r="BN208" s="3"/>
-    </row>
-    <row r="209" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO208" s="3"/>
+      <c r="BP208" s="3"/>
+      <c r="BQ208" s="3"/>
+      <c r="BR208" s="3"/>
+    </row>
+    <row r="209" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -14644,8 +15497,12 @@
       <c r="BL209" s="3"/>
       <c r="BM209" s="3"/>
       <c r="BN209" s="3"/>
-    </row>
-    <row r="210" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO209" s="3"/>
+      <c r="BP209" s="3"/>
+      <c r="BQ209" s="3"/>
+      <c r="BR209" s="3"/>
+    </row>
+    <row r="210" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -14710,8 +15567,12 @@
       <c r="BL210" s="3"/>
       <c r="BM210" s="3"/>
       <c r="BN210" s="3"/>
-    </row>
-    <row r="211" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO210" s="3"/>
+      <c r="BP210" s="3"/>
+      <c r="BQ210" s="3"/>
+      <c r="BR210" s="3"/>
+    </row>
+    <row r="211" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -14776,8 +15637,12 @@
       <c r="BL211" s="3"/>
       <c r="BM211" s="3"/>
       <c r="BN211" s="3"/>
-    </row>
-    <row r="212" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO211" s="3"/>
+      <c r="BP211" s="3"/>
+      <c r="BQ211" s="3"/>
+      <c r="BR211" s="3"/>
+    </row>
+    <row r="212" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -14842,8 +15707,12 @@
       <c r="BL212" s="3"/>
       <c r="BM212" s="3"/>
       <c r="BN212" s="3"/>
-    </row>
-    <row r="213" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO212" s="3"/>
+      <c r="BP212" s="3"/>
+      <c r="BQ212" s="3"/>
+      <c r="BR212" s="3"/>
+    </row>
+    <row r="213" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -14908,8 +15777,12 @@
       <c r="BL213" s="3"/>
       <c r="BM213" s="3"/>
       <c r="BN213" s="3"/>
-    </row>
-    <row r="214" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO213" s="3"/>
+      <c r="BP213" s="3"/>
+      <c r="BQ213" s="3"/>
+      <c r="BR213" s="3"/>
+    </row>
+    <row r="214" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -14974,8 +15847,12 @@
       <c r="BL214" s="3"/>
       <c r="BM214" s="3"/>
       <c r="BN214" s="3"/>
-    </row>
-    <row r="215" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO214" s="3"/>
+      <c r="BP214" s="3"/>
+      <c r="BQ214" s="3"/>
+      <c r="BR214" s="3"/>
+    </row>
+    <row r="215" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -15040,8 +15917,12 @@
       <c r="BL215" s="3"/>
       <c r="BM215" s="3"/>
       <c r="BN215" s="3"/>
-    </row>
-    <row r="216" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO215" s="3"/>
+      <c r="BP215" s="3"/>
+      <c r="BQ215" s="3"/>
+      <c r="BR215" s="3"/>
+    </row>
+    <row r="216" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -15106,8 +15987,12 @@
       <c r="BL216" s="3"/>
       <c r="BM216" s="3"/>
       <c r="BN216" s="3"/>
-    </row>
-    <row r="217" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO216" s="3"/>
+      <c r="BP216" s="3"/>
+      <c r="BQ216" s="3"/>
+      <c r="BR216" s="3"/>
+    </row>
+    <row r="217" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -15172,8 +16057,12 @@
       <c r="BL217" s="3"/>
       <c r="BM217" s="3"/>
       <c r="BN217" s="3"/>
-    </row>
-    <row r="218" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO217" s="3"/>
+      <c r="BP217" s="3"/>
+      <c r="BQ217" s="3"/>
+      <c r="BR217" s="3"/>
+    </row>
+    <row r="218" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -15238,8 +16127,12 @@
       <c r="BL218" s="3"/>
       <c r="BM218" s="3"/>
       <c r="BN218" s="3"/>
-    </row>
-    <row r="219" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO218" s="3"/>
+      <c r="BP218" s="3"/>
+      <c r="BQ218" s="3"/>
+      <c r="BR218" s="3"/>
+    </row>
+    <row r="219" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -15304,8 +16197,12 @@
       <c r="BL219" s="3"/>
       <c r="BM219" s="3"/>
       <c r="BN219" s="3"/>
-    </row>
-    <row r="220" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO219" s="3"/>
+      <c r="BP219" s="3"/>
+      <c r="BQ219" s="3"/>
+      <c r="BR219" s="3"/>
+    </row>
+    <row r="220" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -15370,8 +16267,12 @@
       <c r="BL220" s="3"/>
       <c r="BM220" s="3"/>
       <c r="BN220" s="3"/>
-    </row>
-    <row r="221" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO220" s="3"/>
+      <c r="BP220" s="3"/>
+      <c r="BQ220" s="3"/>
+      <c r="BR220" s="3"/>
+    </row>
+    <row r="221" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -15436,8 +16337,12 @@
       <c r="BL221" s="3"/>
       <c r="BM221" s="3"/>
       <c r="BN221" s="3"/>
-    </row>
-    <row r="222" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO221" s="3"/>
+      <c r="BP221" s="3"/>
+      <c r="BQ221" s="3"/>
+      <c r="BR221" s="3"/>
+    </row>
+    <row r="222" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -15502,8 +16407,12 @@
       <c r="BL222" s="3"/>
       <c r="BM222" s="3"/>
       <c r="BN222" s="3"/>
-    </row>
-    <row r="223" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO222" s="3"/>
+      <c r="BP222" s="3"/>
+      <c r="BQ222" s="3"/>
+      <c r="BR222" s="3"/>
+    </row>
+    <row r="223" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -15568,8 +16477,12 @@
       <c r="BL223" s="3"/>
       <c r="BM223" s="3"/>
       <c r="BN223" s="3"/>
-    </row>
-    <row r="224" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO223" s="3"/>
+      <c r="BP223" s="3"/>
+      <c r="BQ223" s="3"/>
+      <c r="BR223" s="3"/>
+    </row>
+    <row r="224" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -15634,8 +16547,12 @@
       <c r="BL224" s="3"/>
       <c r="BM224" s="3"/>
       <c r="BN224" s="3"/>
-    </row>
-    <row r="225" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO224" s="3"/>
+      <c r="BP224" s="3"/>
+      <c r="BQ224" s="3"/>
+      <c r="BR224" s="3"/>
+    </row>
+    <row r="225" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -15700,8 +16617,12 @@
       <c r="BL225" s="3"/>
       <c r="BM225" s="3"/>
       <c r="BN225" s="3"/>
-    </row>
-    <row r="226" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO225" s="3"/>
+      <c r="BP225" s="3"/>
+      <c r="BQ225" s="3"/>
+      <c r="BR225" s="3"/>
+    </row>
+    <row r="226" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -15766,8 +16687,12 @@
       <c r="BL226" s="3"/>
       <c r="BM226" s="3"/>
       <c r="BN226" s="3"/>
-    </row>
-    <row r="227" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO226" s="3"/>
+      <c r="BP226" s="3"/>
+      <c r="BQ226" s="3"/>
+      <c r="BR226" s="3"/>
+    </row>
+    <row r="227" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -15832,8 +16757,12 @@
       <c r="BL227" s="3"/>
       <c r="BM227" s="3"/>
       <c r="BN227" s="3"/>
-    </row>
-    <row r="228" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO227" s="3"/>
+      <c r="BP227" s="3"/>
+      <c r="BQ227" s="3"/>
+      <c r="BR227" s="3"/>
+    </row>
+    <row r="228" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -15898,8 +16827,12 @@
       <c r="BL228" s="3"/>
       <c r="BM228" s="3"/>
       <c r="BN228" s="3"/>
-    </row>
-    <row r="229" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO228" s="3"/>
+      <c r="BP228" s="3"/>
+      <c r="BQ228" s="3"/>
+      <c r="BR228" s="3"/>
+    </row>
+    <row r="229" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -15964,8 +16897,12 @@
       <c r="BL229" s="3"/>
       <c r="BM229" s="3"/>
       <c r="BN229" s="3"/>
-    </row>
-    <row r="230" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO229" s="3"/>
+      <c r="BP229" s="3"/>
+      <c r="BQ229" s="3"/>
+      <c r="BR229" s="3"/>
+    </row>
+    <row r="230" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -16030,8 +16967,12 @@
       <c r="BL230" s="3"/>
       <c r="BM230" s="3"/>
       <c r="BN230" s="3"/>
-    </row>
-    <row r="231" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO230" s="3"/>
+      <c r="BP230" s="3"/>
+      <c r="BQ230" s="3"/>
+      <c r="BR230" s="3"/>
+    </row>
+    <row r="231" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -16096,8 +17037,12 @@
       <c r="BL231" s="3"/>
       <c r="BM231" s="3"/>
       <c r="BN231" s="3"/>
-    </row>
-    <row r="232" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO231" s="3"/>
+      <c r="BP231" s="3"/>
+      <c r="BQ231" s="3"/>
+      <c r="BR231" s="3"/>
+    </row>
+    <row r="232" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -16162,8 +17107,12 @@
       <c r="BL232" s="3"/>
       <c r="BM232" s="3"/>
       <c r="BN232" s="3"/>
-    </row>
-    <row r="233" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO232" s="3"/>
+      <c r="BP232" s="3"/>
+      <c r="BQ232" s="3"/>
+      <c r="BR232" s="3"/>
+    </row>
+    <row r="233" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -16228,8 +17177,12 @@
       <c r="BL233" s="3"/>
       <c r="BM233" s="3"/>
       <c r="BN233" s="3"/>
-    </row>
-    <row r="234" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO233" s="3"/>
+      <c r="BP233" s="3"/>
+      <c r="BQ233" s="3"/>
+      <c r="BR233" s="3"/>
+    </row>
+    <row r="234" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -16294,8 +17247,12 @@
       <c r="BL234" s="3"/>
       <c r="BM234" s="3"/>
       <c r="BN234" s="3"/>
-    </row>
-    <row r="235" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO234" s="3"/>
+      <c r="BP234" s="3"/>
+      <c r="BQ234" s="3"/>
+      <c r="BR234" s="3"/>
+    </row>
+    <row r="235" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -16360,8 +17317,12 @@
       <c r="BL235" s="3"/>
       <c r="BM235" s="3"/>
       <c r="BN235" s="3"/>
-    </row>
-    <row r="236" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO235" s="3"/>
+      <c r="BP235" s="3"/>
+      <c r="BQ235" s="3"/>
+      <c r="BR235" s="3"/>
+    </row>
+    <row r="236" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -16426,8 +17387,12 @@
       <c r="BL236" s="3"/>
       <c r="BM236" s="3"/>
       <c r="BN236" s="3"/>
-    </row>
-    <row r="237" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO236" s="3"/>
+      <c r="BP236" s="3"/>
+      <c r="BQ236" s="3"/>
+      <c r="BR236" s="3"/>
+    </row>
+    <row r="237" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -16492,8 +17457,12 @@
       <c r="BL237" s="3"/>
       <c r="BM237" s="3"/>
       <c r="BN237" s="3"/>
-    </row>
-    <row r="238" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO237" s="3"/>
+      <c r="BP237" s="3"/>
+      <c r="BQ237" s="3"/>
+      <c r="BR237" s="3"/>
+    </row>
+    <row r="238" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -16558,8 +17527,12 @@
       <c r="BL238" s="3"/>
       <c r="BM238" s="3"/>
       <c r="BN238" s="3"/>
-    </row>
-    <row r="239" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO238" s="3"/>
+      <c r="BP238" s="3"/>
+      <c r="BQ238" s="3"/>
+      <c r="BR238" s="3"/>
+    </row>
+    <row r="239" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -16624,8 +17597,12 @@
       <c r="BL239" s="3"/>
       <c r="BM239" s="3"/>
       <c r="BN239" s="3"/>
-    </row>
-    <row r="240" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO239" s="3"/>
+      <c r="BP239" s="3"/>
+      <c r="BQ239" s="3"/>
+      <c r="BR239" s="3"/>
+    </row>
+    <row r="240" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -16690,8 +17667,12 @@
       <c r="BL240" s="3"/>
       <c r="BM240" s="3"/>
       <c r="BN240" s="3"/>
-    </row>
-    <row r="241" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO240" s="3"/>
+      <c r="BP240" s="3"/>
+      <c r="BQ240" s="3"/>
+      <c r="BR240" s="3"/>
+    </row>
+    <row r="241" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -16756,8 +17737,12 @@
       <c r="BL241" s="3"/>
       <c r="BM241" s="3"/>
       <c r="BN241" s="3"/>
-    </row>
-    <row r="242" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO241" s="3"/>
+      <c r="BP241" s="3"/>
+      <c r="BQ241" s="3"/>
+      <c r="BR241" s="3"/>
+    </row>
+    <row r="242" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -16822,8 +17807,12 @@
       <c r="BL242" s="3"/>
       <c r="BM242" s="3"/>
       <c r="BN242" s="3"/>
-    </row>
-    <row r="243" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO242" s="3"/>
+      <c r="BP242" s="3"/>
+      <c r="BQ242" s="3"/>
+      <c r="BR242" s="3"/>
+    </row>
+    <row r="243" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -16888,8 +17877,12 @@
       <c r="BL243" s="3"/>
       <c r="BM243" s="3"/>
       <c r="BN243" s="3"/>
-    </row>
-    <row r="244" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO243" s="3"/>
+      <c r="BP243" s="3"/>
+      <c r="BQ243" s="3"/>
+      <c r="BR243" s="3"/>
+    </row>
+    <row r="244" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -16954,8 +17947,12 @@
       <c r="BL244" s="3"/>
       <c r="BM244" s="3"/>
       <c r="BN244" s="3"/>
-    </row>
-    <row r="245" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO244" s="3"/>
+      <c r="BP244" s="3"/>
+      <c r="BQ244" s="3"/>
+      <c r="BR244" s="3"/>
+    </row>
+    <row r="245" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -17020,8 +18017,12 @@
       <c r="BL245" s="3"/>
       <c r="BM245" s="3"/>
       <c r="BN245" s="3"/>
-    </row>
-    <row r="246" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO245" s="3"/>
+      <c r="BP245" s="3"/>
+      <c r="BQ245" s="3"/>
+      <c r="BR245" s="3"/>
+    </row>
+    <row r="246" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -17086,8 +18087,12 @@
       <c r="BL246" s="3"/>
       <c r="BM246" s="3"/>
       <c r="BN246" s="3"/>
-    </row>
-    <row r="247" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO246" s="3"/>
+      <c r="BP246" s="3"/>
+      <c r="BQ246" s="3"/>
+      <c r="BR246" s="3"/>
+    </row>
+    <row r="247" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -17152,8 +18157,12 @@
       <c r="BL247" s="3"/>
       <c r="BM247" s="3"/>
       <c r="BN247" s="3"/>
-    </row>
-    <row r="248" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO247" s="3"/>
+      <c r="BP247" s="3"/>
+      <c r="BQ247" s="3"/>
+      <c r="BR247" s="3"/>
+    </row>
+    <row r="248" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -17218,8 +18227,12 @@
       <c r="BL248" s="3"/>
       <c r="BM248" s="3"/>
       <c r="BN248" s="3"/>
-    </row>
-    <row r="249" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO248" s="3"/>
+      <c r="BP248" s="3"/>
+      <c r="BQ248" s="3"/>
+      <c r="BR248" s="3"/>
+    </row>
+    <row r="249" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -17284,8 +18297,12 @@
       <c r="BL249" s="3"/>
       <c r="BM249" s="3"/>
       <c r="BN249" s="3"/>
-    </row>
-    <row r="250" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO249" s="3"/>
+      <c r="BP249" s="3"/>
+      <c r="BQ249" s="3"/>
+      <c r="BR249" s="3"/>
+    </row>
+    <row r="250" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -17350,8 +18367,12 @@
       <c r="BL250" s="3"/>
       <c r="BM250" s="3"/>
       <c r="BN250" s="3"/>
-    </row>
-    <row r="251" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO250" s="3"/>
+      <c r="BP250" s="3"/>
+      <c r="BQ250" s="3"/>
+      <c r="BR250" s="3"/>
+    </row>
+    <row r="251" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -17416,8 +18437,12 @@
       <c r="BL251" s="3"/>
       <c r="BM251" s="3"/>
       <c r="BN251" s="3"/>
-    </row>
-    <row r="252" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO251" s="3"/>
+      <c r="BP251" s="3"/>
+      <c r="BQ251" s="3"/>
+      <c r="BR251" s="3"/>
+    </row>
+    <row r="252" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -17482,8 +18507,12 @@
       <c r="BL252" s="3"/>
       <c r="BM252" s="3"/>
       <c r="BN252" s="3"/>
-    </row>
-    <row r="253" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO252" s="3"/>
+      <c r="BP252" s="3"/>
+      <c r="BQ252" s="3"/>
+      <c r="BR252" s="3"/>
+    </row>
+    <row r="253" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -17548,8 +18577,12 @@
       <c r="BL253" s="3"/>
       <c r="BM253" s="3"/>
       <c r="BN253" s="3"/>
-    </row>
-    <row r="254" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO253" s="3"/>
+      <c r="BP253" s="3"/>
+      <c r="BQ253" s="3"/>
+      <c r="BR253" s="3"/>
+    </row>
+    <row r="254" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -17614,8 +18647,12 @@
       <c r="BL254" s="3"/>
       <c r="BM254" s="3"/>
       <c r="BN254" s="3"/>
-    </row>
-    <row r="255" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO254" s="3"/>
+      <c r="BP254" s="3"/>
+      <c r="BQ254" s="3"/>
+      <c r="BR254" s="3"/>
+    </row>
+    <row r="255" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -17680,8 +18717,12 @@
       <c r="BL255" s="3"/>
       <c r="BM255" s="3"/>
       <c r="BN255" s="3"/>
-    </row>
-    <row r="256" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO255" s="3"/>
+      <c r="BP255" s="3"/>
+      <c r="BQ255" s="3"/>
+      <c r="BR255" s="3"/>
+    </row>
+    <row r="256" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -17746,8 +18787,12 @@
       <c r="BL256" s="3"/>
       <c r="BM256" s="3"/>
       <c r="BN256" s="3"/>
-    </row>
-    <row r="257" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO256" s="3"/>
+      <c r="BP256" s="3"/>
+      <c r="BQ256" s="3"/>
+      <c r="BR256" s="3"/>
+    </row>
+    <row r="257" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -17812,8 +18857,12 @@
       <c r="BL257" s="3"/>
       <c r="BM257" s="3"/>
       <c r="BN257" s="3"/>
-    </row>
-    <row r="258" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO257" s="3"/>
+      <c r="BP257" s="3"/>
+      <c r="BQ257" s="3"/>
+      <c r="BR257" s="3"/>
+    </row>
+    <row r="258" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -17878,8 +18927,12 @@
       <c r="BL258" s="3"/>
       <c r="BM258" s="3"/>
       <c r="BN258" s="3"/>
-    </row>
-    <row r="259" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO258" s="3"/>
+      <c r="BP258" s="3"/>
+      <c r="BQ258" s="3"/>
+      <c r="BR258" s="3"/>
+    </row>
+    <row r="259" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -17944,8 +18997,12 @@
       <c r="BL259" s="3"/>
       <c r="BM259" s="3"/>
       <c r="BN259" s="3"/>
-    </row>
-    <row r="260" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO259" s="3"/>
+      <c r="BP259" s="3"/>
+      <c r="BQ259" s="3"/>
+      <c r="BR259" s="3"/>
+    </row>
+    <row r="260" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -18010,8 +19067,12 @@
       <c r="BL260" s="3"/>
       <c r="BM260" s="3"/>
       <c r="BN260" s="3"/>
-    </row>
-    <row r="261" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO260" s="3"/>
+      <c r="BP260" s="3"/>
+      <c r="BQ260" s="3"/>
+      <c r="BR260" s="3"/>
+    </row>
+    <row r="261" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -18076,8 +19137,12 @@
       <c r="BL261" s="3"/>
       <c r="BM261" s="3"/>
       <c r="BN261" s="3"/>
-    </row>
-    <row r="262" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO261" s="3"/>
+      <c r="BP261" s="3"/>
+      <c r="BQ261" s="3"/>
+      <c r="BR261" s="3"/>
+    </row>
+    <row r="262" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -18142,8 +19207,12 @@
       <c r="BL262" s="3"/>
       <c r="BM262" s="3"/>
       <c r="BN262" s="3"/>
-    </row>
-    <row r="263" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO262" s="3"/>
+      <c r="BP262" s="3"/>
+      <c r="BQ262" s="3"/>
+      <c r="BR262" s="3"/>
+    </row>
+    <row r="263" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -18208,8 +19277,12 @@
       <c r="BL263" s="3"/>
       <c r="BM263" s="3"/>
       <c r="BN263" s="3"/>
-    </row>
-    <row r="264" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO263" s="3"/>
+      <c r="BP263" s="3"/>
+      <c r="BQ263" s="3"/>
+      <c r="BR263" s="3"/>
+    </row>
+    <row r="264" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -18274,8 +19347,12 @@
       <c r="BL264" s="3"/>
       <c r="BM264" s="3"/>
       <c r="BN264" s="3"/>
-    </row>
-    <row r="265" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO264" s="3"/>
+      <c r="BP264" s="3"/>
+      <c r="BQ264" s="3"/>
+      <c r="BR264" s="3"/>
+    </row>
+    <row r="265" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -18340,8 +19417,12 @@
       <c r="BL265" s="3"/>
       <c r="BM265" s="3"/>
       <c r="BN265" s="3"/>
-    </row>
-    <row r="266" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO265" s="3"/>
+      <c r="BP265" s="3"/>
+      <c r="BQ265" s="3"/>
+      <c r="BR265" s="3"/>
+    </row>
+    <row r="266" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -18406,8 +19487,12 @@
       <c r="BL266" s="3"/>
       <c r="BM266" s="3"/>
       <c r="BN266" s="3"/>
-    </row>
-    <row r="267" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO266" s="3"/>
+      <c r="BP266" s="3"/>
+      <c r="BQ266" s="3"/>
+      <c r="BR266" s="3"/>
+    </row>
+    <row r="267" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -18472,8 +19557,12 @@
       <c r="BL267" s="3"/>
       <c r="BM267" s="3"/>
       <c r="BN267" s="3"/>
-    </row>
-    <row r="268" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO267" s="3"/>
+      <c r="BP267" s="3"/>
+      <c r="BQ267" s="3"/>
+      <c r="BR267" s="3"/>
+    </row>
+    <row r="268" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -18538,8 +19627,12 @@
       <c r="BL268" s="3"/>
       <c r="BM268" s="3"/>
       <c r="BN268" s="3"/>
-    </row>
-    <row r="269" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO268" s="3"/>
+      <c r="BP268" s="3"/>
+      <c r="BQ268" s="3"/>
+      <c r="BR268" s="3"/>
+    </row>
+    <row r="269" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -18604,8 +19697,12 @@
       <c r="BL269" s="3"/>
       <c r="BM269" s="3"/>
       <c r="BN269" s="3"/>
-    </row>
-    <row r="270" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO269" s="3"/>
+      <c r="BP269" s="3"/>
+      <c r="BQ269" s="3"/>
+      <c r="BR269" s="3"/>
+    </row>
+    <row r="270" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -18670,8 +19767,12 @@
       <c r="BL270" s="3"/>
       <c r="BM270" s="3"/>
       <c r="BN270" s="3"/>
-    </row>
-    <row r="271" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO270" s="3"/>
+      <c r="BP270" s="3"/>
+      <c r="BQ270" s="3"/>
+      <c r="BR270" s="3"/>
+    </row>
+    <row r="271" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -18736,8 +19837,12 @@
       <c r="BL271" s="3"/>
       <c r="BM271" s="3"/>
       <c r="BN271" s="3"/>
-    </row>
-    <row r="272" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO271" s="3"/>
+      <c r="BP271" s="3"/>
+      <c r="BQ271" s="3"/>
+      <c r="BR271" s="3"/>
+    </row>
+    <row r="272" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -18802,8 +19907,12 @@
       <c r="BL272" s="3"/>
       <c r="BM272" s="3"/>
       <c r="BN272" s="3"/>
-    </row>
-    <row r="273" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO272" s="3"/>
+      <c r="BP272" s="3"/>
+      <c r="BQ272" s="3"/>
+      <c r="BR272" s="3"/>
+    </row>
+    <row r="273" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -18868,8 +19977,12 @@
       <c r="BL273" s="3"/>
       <c r="BM273" s="3"/>
       <c r="BN273" s="3"/>
-    </row>
-    <row r="274" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO273" s="3"/>
+      <c r="BP273" s="3"/>
+      <c r="BQ273" s="3"/>
+      <c r="BR273" s="3"/>
+    </row>
+    <row r="274" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -18934,8 +20047,12 @@
       <c r="BL274" s="3"/>
       <c r="BM274" s="3"/>
       <c r="BN274" s="3"/>
-    </row>
-    <row r="275" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO274" s="3"/>
+      <c r="BP274" s="3"/>
+      <c r="BQ274" s="3"/>
+      <c r="BR274" s="3"/>
+    </row>
+    <row r="275" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -19000,8 +20117,12 @@
       <c r="BL275" s="3"/>
       <c r="BM275" s="3"/>
       <c r="BN275" s="3"/>
-    </row>
-    <row r="276" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO275" s="3"/>
+      <c r="BP275" s="3"/>
+      <c r="BQ275" s="3"/>
+      <c r="BR275" s="3"/>
+    </row>
+    <row r="276" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -19066,8 +20187,12 @@
       <c r="BL276" s="3"/>
       <c r="BM276" s="3"/>
       <c r="BN276" s="3"/>
-    </row>
-    <row r="277" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO276" s="3"/>
+      <c r="BP276" s="3"/>
+      <c r="BQ276" s="3"/>
+      <c r="BR276" s="3"/>
+    </row>
+    <row r="277" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -19132,8 +20257,12 @@
       <c r="BL277" s="3"/>
       <c r="BM277" s="3"/>
       <c r="BN277" s="3"/>
-    </row>
-    <row r="278" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO277" s="3"/>
+      <c r="BP277" s="3"/>
+      <c r="BQ277" s="3"/>
+      <c r="BR277" s="3"/>
+    </row>
+    <row r="278" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -19198,8 +20327,12 @@
       <c r="BL278" s="3"/>
       <c r="BM278" s="3"/>
       <c r="BN278" s="3"/>
-    </row>
-    <row r="279" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO278" s="3"/>
+      <c r="BP278" s="3"/>
+      <c r="BQ278" s="3"/>
+      <c r="BR278" s="3"/>
+    </row>
+    <row r="279" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -19264,8 +20397,12 @@
       <c r="BL279" s="3"/>
       <c r="BM279" s="3"/>
       <c r="BN279" s="3"/>
-    </row>
-    <row r="280" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO279" s="3"/>
+      <c r="BP279" s="3"/>
+      <c r="BQ279" s="3"/>
+      <c r="BR279" s="3"/>
+    </row>
+    <row r="280" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -19330,8 +20467,12 @@
       <c r="BL280" s="3"/>
       <c r="BM280" s="3"/>
       <c r="BN280" s="3"/>
-    </row>
-    <row r="281" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO280" s="3"/>
+      <c r="BP280" s="3"/>
+      <c r="BQ280" s="3"/>
+      <c r="BR280" s="3"/>
+    </row>
+    <row r="281" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -19396,8 +20537,12 @@
       <c r="BL281" s="3"/>
       <c r="BM281" s="3"/>
       <c r="BN281" s="3"/>
-    </row>
-    <row r="282" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO281" s="3"/>
+      <c r="BP281" s="3"/>
+      <c r="BQ281" s="3"/>
+      <c r="BR281" s="3"/>
+    </row>
+    <row r="282" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -19462,8 +20607,12 @@
       <c r="BL282" s="3"/>
       <c r="BM282" s="3"/>
       <c r="BN282" s="3"/>
-    </row>
-    <row r="283" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO282" s="3"/>
+      <c r="BP282" s="3"/>
+      <c r="BQ282" s="3"/>
+      <c r="BR282" s="3"/>
+    </row>
+    <row r="283" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -19528,8 +20677,12 @@
       <c r="BL283" s="3"/>
       <c r="BM283" s="3"/>
       <c r="BN283" s="3"/>
-    </row>
-    <row r="284" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO283" s="3"/>
+      <c r="BP283" s="3"/>
+      <c r="BQ283" s="3"/>
+      <c r="BR283" s="3"/>
+    </row>
+    <row r="284" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -19594,8 +20747,12 @@
       <c r="BL284" s="3"/>
       <c r="BM284" s="3"/>
       <c r="BN284" s="3"/>
-    </row>
-    <row r="285" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO284" s="3"/>
+      <c r="BP284" s="3"/>
+      <c r="BQ284" s="3"/>
+      <c r="BR284" s="3"/>
+    </row>
+    <row r="285" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -19660,8 +20817,12 @@
       <c r="BL285" s="3"/>
       <c r="BM285" s="3"/>
       <c r="BN285" s="3"/>
-    </row>
-    <row r="286" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO285" s="3"/>
+      <c r="BP285" s="3"/>
+      <c r="BQ285" s="3"/>
+      <c r="BR285" s="3"/>
+    </row>
+    <row r="286" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -19726,8 +20887,12 @@
       <c r="BL286" s="3"/>
       <c r="BM286" s="3"/>
       <c r="BN286" s="3"/>
-    </row>
-    <row r="287" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO286" s="3"/>
+      <c r="BP286" s="3"/>
+      <c r="BQ286" s="3"/>
+      <c r="BR286" s="3"/>
+    </row>
+    <row r="287" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -19792,8 +20957,12 @@
       <c r="BL287" s="3"/>
       <c r="BM287" s="3"/>
       <c r="BN287" s="3"/>
-    </row>
-    <row r="288" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO287" s="3"/>
+      <c r="BP287" s="3"/>
+      <c r="BQ287" s="3"/>
+      <c r="BR287" s="3"/>
+    </row>
+    <row r="288" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -19858,8 +21027,12 @@
       <c r="BL288" s="3"/>
       <c r="BM288" s="3"/>
       <c r="BN288" s="3"/>
-    </row>
-    <row r="289" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO288" s="3"/>
+      <c r="BP288" s="3"/>
+      <c r="BQ288" s="3"/>
+      <c r="BR288" s="3"/>
+    </row>
+    <row r="289" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -19924,8 +21097,12 @@
       <c r="BL289" s="3"/>
       <c r="BM289" s="3"/>
       <c r="BN289" s="3"/>
-    </row>
-    <row r="290" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO289" s="3"/>
+      <c r="BP289" s="3"/>
+      <c r="BQ289" s="3"/>
+      <c r="BR289" s="3"/>
+    </row>
+    <row r="290" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -19990,8 +21167,12 @@
       <c r="BL290" s="3"/>
       <c r="BM290" s="3"/>
       <c r="BN290" s="3"/>
-    </row>
-    <row r="291" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO290" s="3"/>
+      <c r="BP290" s="3"/>
+      <c r="BQ290" s="3"/>
+      <c r="BR290" s="3"/>
+    </row>
+    <row r="291" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -20056,8 +21237,12 @@
       <c r="BL291" s="3"/>
       <c r="BM291" s="3"/>
       <c r="BN291" s="3"/>
-    </row>
-    <row r="292" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO291" s="3"/>
+      <c r="BP291" s="3"/>
+      <c r="BQ291" s="3"/>
+      <c r="BR291" s="3"/>
+    </row>
+    <row r="292" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -20122,8 +21307,12 @@
       <c r="BL292" s="3"/>
       <c r="BM292" s="3"/>
       <c r="BN292" s="3"/>
-    </row>
-    <row r="293" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO292" s="3"/>
+      <c r="BP292" s="3"/>
+      <c r="BQ292" s="3"/>
+      <c r="BR292" s="3"/>
+    </row>
+    <row r="293" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -20188,8 +21377,12 @@
       <c r="BL293" s="3"/>
       <c r="BM293" s="3"/>
       <c r="BN293" s="3"/>
-    </row>
-    <row r="294" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO293" s="3"/>
+      <c r="BP293" s="3"/>
+      <c r="BQ293" s="3"/>
+      <c r="BR293" s="3"/>
+    </row>
+    <row r="294" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -20254,8 +21447,12 @@
       <c r="BL294" s="3"/>
       <c r="BM294" s="3"/>
       <c r="BN294" s="3"/>
-    </row>
-    <row r="295" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO294" s="3"/>
+      <c r="BP294" s="3"/>
+      <c r="BQ294" s="3"/>
+      <c r="BR294" s="3"/>
+    </row>
+    <row r="295" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -20320,8 +21517,12 @@
       <c r="BL295" s="3"/>
       <c r="BM295" s="3"/>
       <c r="BN295" s="3"/>
-    </row>
-    <row r="296" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO295" s="3"/>
+      <c r="BP295" s="3"/>
+      <c r="BQ295" s="3"/>
+      <c r="BR295" s="3"/>
+    </row>
+    <row r="296" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -20386,8 +21587,12 @@
       <c r="BL296" s="3"/>
       <c r="BM296" s="3"/>
       <c r="BN296" s="3"/>
-    </row>
-    <row r="297" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO296" s="3"/>
+      <c r="BP296" s="3"/>
+      <c r="BQ296" s="3"/>
+      <c r="BR296" s="3"/>
+    </row>
+    <row r="297" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -20452,8 +21657,12 @@
       <c r="BL297" s="3"/>
       <c r="BM297" s="3"/>
       <c r="BN297" s="3"/>
-    </row>
-    <row r="298" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO297" s="3"/>
+      <c r="BP297" s="3"/>
+      <c r="BQ297" s="3"/>
+      <c r="BR297" s="3"/>
+    </row>
+    <row r="298" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -20518,8 +21727,12 @@
       <c r="BL298" s="3"/>
       <c r="BM298" s="3"/>
       <c r="BN298" s="3"/>
-    </row>
-    <row r="299" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO298" s="3"/>
+      <c r="BP298" s="3"/>
+      <c r="BQ298" s="3"/>
+      <c r="BR298" s="3"/>
+    </row>
+    <row r="299" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -20584,8 +21797,12 @@
       <c r="BL299" s="3"/>
       <c r="BM299" s="3"/>
       <c r="BN299" s="3"/>
-    </row>
-    <row r="300" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO299" s="3"/>
+      <c r="BP299" s="3"/>
+      <c r="BQ299" s="3"/>
+      <c r="BR299" s="3"/>
+    </row>
+    <row r="300" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -20650,8 +21867,12 @@
       <c r="BL300" s="3"/>
       <c r="BM300" s="3"/>
       <c r="BN300" s="3"/>
-    </row>
-    <row r="301" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO300" s="3"/>
+      <c r="BP300" s="3"/>
+      <c r="BQ300" s="3"/>
+      <c r="BR300" s="3"/>
+    </row>
+    <row r="301" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -20716,8 +21937,12 @@
       <c r="BL301" s="3"/>
       <c r="BM301" s="3"/>
       <c r="BN301" s="3"/>
-    </row>
-    <row r="302" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO301" s="3"/>
+      <c r="BP301" s="3"/>
+      <c r="BQ301" s="3"/>
+      <c r="BR301" s="3"/>
+    </row>
+    <row r="302" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -20782,8 +22007,12 @@
       <c r="BL302" s="3"/>
       <c r="BM302" s="3"/>
       <c r="BN302" s="3"/>
-    </row>
-    <row r="303" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO302" s="3"/>
+      <c r="BP302" s="3"/>
+      <c r="BQ302" s="3"/>
+      <c r="BR302" s="3"/>
+    </row>
+    <row r="303" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -20848,8 +22077,12 @@
       <c r="BL303" s="3"/>
       <c r="BM303" s="3"/>
       <c r="BN303" s="3"/>
-    </row>
-    <row r="304" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO303" s="3"/>
+      <c r="BP303" s="3"/>
+      <c r="BQ303" s="3"/>
+      <c r="BR303" s="3"/>
+    </row>
+    <row r="304" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -20914,8 +22147,12 @@
       <c r="BL304" s="3"/>
       <c r="BM304" s="3"/>
       <c r="BN304" s="3"/>
-    </row>
-    <row r="305" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO304" s="3"/>
+      <c r="BP304" s="3"/>
+      <c r="BQ304" s="3"/>
+      <c r="BR304" s="3"/>
+    </row>
+    <row r="305" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -20980,8 +22217,12 @@
       <c r="BL305" s="3"/>
       <c r="BM305" s="3"/>
       <c r="BN305" s="3"/>
-    </row>
-    <row r="306" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO305" s="3"/>
+      <c r="BP305" s="3"/>
+      <c r="BQ305" s="3"/>
+      <c r="BR305" s="3"/>
+    </row>
+    <row r="306" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -21046,8 +22287,12 @@
       <c r="BL306" s="3"/>
       <c r="BM306" s="3"/>
       <c r="BN306" s="3"/>
-    </row>
-    <row r="307" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO306" s="3"/>
+      <c r="BP306" s="3"/>
+      <c r="BQ306" s="3"/>
+      <c r="BR306" s="3"/>
+    </row>
+    <row r="307" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -21112,8 +22357,12 @@
       <c r="BL307" s="3"/>
       <c r="BM307" s="3"/>
       <c r="BN307" s="3"/>
-    </row>
-    <row r="308" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO307" s="3"/>
+      <c r="BP307" s="3"/>
+      <c r="BQ307" s="3"/>
+      <c r="BR307" s="3"/>
+    </row>
+    <row r="308" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -21178,8 +22427,12 @@
       <c r="BL308" s="3"/>
       <c r="BM308" s="3"/>
       <c r="BN308" s="3"/>
-    </row>
-    <row r="309" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO308" s="3"/>
+      <c r="BP308" s="3"/>
+      <c r="BQ308" s="3"/>
+      <c r="BR308" s="3"/>
+    </row>
+    <row r="309" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -21244,8 +22497,12 @@
       <c r="BL309" s="3"/>
       <c r="BM309" s="3"/>
       <c r="BN309" s="3"/>
-    </row>
-    <row r="310" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO309" s="3"/>
+      <c r="BP309" s="3"/>
+      <c r="BQ309" s="3"/>
+      <c r="BR309" s="3"/>
+    </row>
+    <row r="310" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -21310,8 +22567,12 @@
       <c r="BL310" s="3"/>
       <c r="BM310" s="3"/>
       <c r="BN310" s="3"/>
-    </row>
-    <row r="311" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO310" s="3"/>
+      <c r="BP310" s="3"/>
+      <c r="BQ310" s="3"/>
+      <c r="BR310" s="3"/>
+    </row>
+    <row r="311" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -21376,8 +22637,12 @@
       <c r="BL311" s="3"/>
       <c r="BM311" s="3"/>
       <c r="BN311" s="3"/>
-    </row>
-    <row r="312" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO311" s="3"/>
+      <c r="BP311" s="3"/>
+      <c r="BQ311" s="3"/>
+      <c r="BR311" s="3"/>
+    </row>
+    <row r="312" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -21442,8 +22707,12 @@
       <c r="BL312" s="3"/>
       <c r="BM312" s="3"/>
       <c r="BN312" s="3"/>
-    </row>
-    <row r="313" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO312" s="3"/>
+      <c r="BP312" s="3"/>
+      <c r="BQ312" s="3"/>
+      <c r="BR312" s="3"/>
+    </row>
+    <row r="313" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -21508,8 +22777,12 @@
       <c r="BL313" s="3"/>
       <c r="BM313" s="3"/>
       <c r="BN313" s="3"/>
-    </row>
-    <row r="314" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO313" s="3"/>
+      <c r="BP313" s="3"/>
+      <c r="BQ313" s="3"/>
+      <c r="BR313" s="3"/>
+    </row>
+    <row r="314" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -21574,8 +22847,12 @@
       <c r="BL314" s="3"/>
       <c r="BM314" s="3"/>
       <c r="BN314" s="3"/>
-    </row>
-    <row r="315" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO314" s="3"/>
+      <c r="BP314" s="3"/>
+      <c r="BQ314" s="3"/>
+      <c r="BR314" s="3"/>
+    </row>
+    <row r="315" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -21640,8 +22917,12 @@
       <c r="BL315" s="3"/>
       <c r="BM315" s="3"/>
       <c r="BN315" s="3"/>
-    </row>
-    <row r="316" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO315" s="3"/>
+      <c r="BP315" s="3"/>
+      <c r="BQ315" s="3"/>
+      <c r="BR315" s="3"/>
+    </row>
+    <row r="316" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -21706,8 +22987,12 @@
       <c r="BL316" s="3"/>
       <c r="BM316" s="3"/>
       <c r="BN316" s="3"/>
-    </row>
-    <row r="317" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO316" s="3"/>
+      <c r="BP316" s="3"/>
+      <c r="BQ316" s="3"/>
+      <c r="BR316" s="3"/>
+    </row>
+    <row r="317" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -21772,8 +23057,12 @@
       <c r="BL317" s="3"/>
       <c r="BM317" s="3"/>
       <c r="BN317" s="3"/>
-    </row>
-    <row r="318" spans="3:66" x14ac:dyDescent="0.2">
+      <c r="BO317" s="3"/>
+      <c r="BP317" s="3"/>
+      <c r="BQ317" s="3"/>
+      <c r="BR317" s="3"/>
+    </row>
+    <row r="318" spans="3:70" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -21838,6 +23127,10 @@
       <c r="BL318" s="3"/>
       <c r="BM318" s="3"/>
       <c r="BN318" s="3"/>
+      <c r="BO318" s="3"/>
+      <c r="BP318" s="3"/>
+      <c r="BQ318" s="3"/>
+      <c r="BR318" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
